--- a/physik/svphysik.xlsx
+++ b/physik/svphysik.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Übersicht" sheetId="1" r:id="Ra0fff5dc053448a0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gesamtplan Physik" sheetId="2" r:id="R995ec4d7e5a44428"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Physik 7" sheetId="3" r:id="R85efe047f0ab4a64"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Physik 8" sheetId="4" r:id="R63d4341e2dba4c66"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Physik 9" sheetId="5" r:id="R64adf585f3e44990"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Physik 10" sheetId="6" r:id="R4701a496c458424d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Astronomie 10" sheetId="7" r:id="Rb2dda9fec54d4913"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quellen" sheetId="8" r:id="R2e02c7e3f51e44ed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Übersicht" sheetId="1" r:id="Rd6c2765e854a452d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gesamtplan Physik" sheetId="2" r:id="Rb486fcc6283d47d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Physik 7" sheetId="3" r:id="R54eb322bbaba4137"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Physik 8" sheetId="4" r:id="R55906025aec74ba6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Physik 9" sheetId="5" r:id="Rb06684665ed64a9c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Physik 10" sheetId="6" r:id="R8df82953b64f454e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Astronomie 10" sheetId="7" r:id="R12522782c7ec4058"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quellen" sheetId="8" r:id="Rc4e5e0f42c984d95"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -962,7 +962,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R119824900c964f42"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R72860fcbacb44250"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1476,7 +1476,7 @@
     <x:mergeCell ref="A3:H3"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb100f990b1b54e92"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbb7d8a48b4f34861"/>
 </x:worksheet>
 </file>
 
@@ -1613,13 +1613,13 @@
         <x:v>keiner</x:v>
       </x:c>
       <x:c r="K5" s="57" t="str">
-        <x:v>ph_k7_st01_was_ist_physik_beobachten_und_beschreiben</x:v>
+        <x:v>ph_k7_st01_was_ist_physik</x:v>
       </x:c>
       <x:c r="L5" s="57" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/096_physik_titelseite.jpg</x:v>
       </x:c>
       <x:c r="M5" s="156" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_01_was_ist_physik.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st01_was_ist_physik_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N5" s="157" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st01_was_ist_physik_beobachten_und_beschreiben_orga.html","Vorbereitung öffnen")</x:f>
@@ -1658,13 +1658,13 @@
         <x:v>Reaktionszeitmessung mit Taster und LED als Vergleichsstation</x:v>
       </x:c>
       <x:c r="K6" s="60" t="str">
-        <x:v>ph_k7_st02_messen_und_protokollieren_die_reaktionszeit</x:v>
+        <x:v>ph_k7_st02_messen_und_protokollieren</x:v>
       </x:c>
       <x:c r="L6" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/074_messgeraete.jpg</x:v>
       </x:c>
       <x:c r="M6" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_02_messen_und_protokollieren.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st02_messen_und_protokollieren_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N6" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st02_messen_und_protokollieren_die_reaktionszeit_orga.html","Vorbereitung öffnen")</x:f>
@@ -1703,13 +1703,13 @@
         <x:v>keiner</x:v>
       </x:c>
       <x:c r="K7" s="60" t="str">
-        <x:v>ph_k7_st03_lichtquellen_und_die_geradlinige_ausbreitung_des_lichts</x:v>
+        <x:v>ph_k7_st03_lichtquellen_und_lichtausbreitung</x:v>
       </x:c>
       <x:c r="L7" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/034_arduino_licht_optik.jpg</x:v>
       </x:c>
       <x:c r="M7" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_03_lichtquellen_und_lichtausbreitung.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st03_lichtquellen_und_lichtausbreitung_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N7" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st03_lichtquellen_und_die_geradlinige_ausbreitung_des_lichts_orga.html","Vorbereitung öffnen")</x:f>
@@ -1748,13 +1748,13 @@
         <x:v>Helligkeitsmessung in Kernschatten, Halbschatten und beleuchteter Fläche (Lehrerdemonstration)</x:v>
       </x:c>
       <x:c r="K8" s="60" t="str">
-        <x:v>ph_k7_st04_licht_und_schatten_kernschatten_und_halbschatten</x:v>
+        <x:v>ph_k7_st04_licht_und_schatten</x:v>
       </x:c>
       <x:c r="L8" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/034_arduino_licht_optik.jpg</x:v>
       </x:c>
       <x:c r="M8" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_04_licht_und_schatten.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st04_licht_und_schatten_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N8" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st04_licht_und_schatten_kernschatten_und_halbschatten_orga.html","Vorbereitung öffnen")</x:f>
@@ -1793,13 +1793,13 @@
         <x:v>keiner</x:v>
       </x:c>
       <x:c r="K9" s="60" t="str">
-        <x:v>ph_k7_st05_mondphasen_und_finsternisse_schatten_im_weltall</x:v>
+        <x:v>ph_k7_st05_mondphasen</x:v>
       </x:c>
       <x:c r="L9" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/009_mondphasen.jpg</x:v>
       </x:c>
       <x:c r="M9" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_05_mondphasen_und_finsternisse.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st05_mondphasen_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N9" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st05_mondphasen_und_finsternisse_schatten_im_weltall_orga.html","Vorbereitung öffnen")</x:f>
@@ -1838,13 +1838,13 @@
         <x:v>keiner</x:v>
       </x:c>
       <x:c r="K10" s="60" t="str">
-        <x:v>ph_k7_st06_reflexion_und_das_spiegelgesetz_lichtstrahlen_andern_die_richtung</x:v>
+        <x:v>ph_k7_st06_reflexion</x:v>
       </x:c>
       <x:c r="L10" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/035_reflexion_spiegel.jpg</x:v>
       </x:c>
       <x:c r="M10" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_06_reflexion_spiegelgesetz.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st06_reflexion_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N10" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st06_reflexion_und_das_spiegelgesetz_lichtstrahlen_andern_die_richtung_orga.html","Vorbereitung öffnen")</x:f>
@@ -1883,13 +1883,13 @@
         <x:v>keiner</x:v>
       </x:c>
       <x:c r="K11" s="60" t="str">
-        <x:v>ph_k7_st07_spiegelbilder_wie_entsteht_das_bild_im_spiegel</x:v>
+        <x:v>ph_k7_st07_spiegelbilder</x:v>
       </x:c>
       <x:c r="L11" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/035_reflexion_spiegel.jpg</x:v>
       </x:c>
       <x:c r="M11" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_07_spiegelbilder.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st07_spiegelbilder_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N11" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st07_spiegelbilder_wie_entsteht_das_bild_im_spiegel_orga.html","Vorbereitung öffnen")</x:f>
@@ -1928,13 +1928,13 @@
         <x:v>keiner</x:v>
       </x:c>
       <x:c r="K12" s="60" t="str">
-        <x:v>ph_k7_st08_brechung_und_linsen_licht_andert_die_richtung_in_glas</x:v>
+        <x:v>ph_k7_st08_brechung</x:v>
       </x:c>
       <x:c r="L12" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/006_lichtbrechung.jpg</x:v>
       </x:c>
       <x:c r="M12" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_08_brechung_linsen.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st08_brechung_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N12" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st08_brechung_und_linsen_licht_andert_die_richtung_in_glas_orga.html","Vorbereitung öffnen")</x:f>
@@ -1973,13 +1973,13 @@
         <x:v>keiner</x:v>
       </x:c>
       <x:c r="K13" s="60" t="str">
-        <x:v>ph_k7_st09_warme_und_temperatur_zwei_verschiedene_groen</x:v>
+        <x:v>ph_k7_st09_waerme</x:v>
       </x:c>
       <x:c r="L13" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/026_temperatur_waerme.jpg</x:v>
       </x:c>
       <x:c r="M13" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_09_waerme_temperatur.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st09_waerme_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N13" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st09_warme_und_temperatur_zwei_verschiedene_groen_orga.html","Vorbereitung öffnen")</x:f>
@@ -2018,13 +2018,13 @@
         <x:v>keiner</x:v>
       </x:c>
       <x:c r="K14" s="60" t="str">
-        <x:v>ph_k7_st10_warmeleitung_und_warmestrahlung_wie_warme_sich_ausbreitet</x:v>
+        <x:v>ph_k7_st10_waermeleitung</x:v>
       </x:c>
       <x:c r="L14" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/042_radioaktivitaet.jpg</x:v>
       </x:c>
       <x:c r="M14" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_10_waermeleitung_waermestrahlung.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st10_waermeleitung_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N14" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st10_warmeleitung_und_warmestrahlung_wie_warme_sich_ausbreitet_orga.html","Vorbereitung öffnen")</x:f>
@@ -2063,13 +2063,13 @@
         <x:v>nein</x:v>
       </x:c>
       <x:c r="K15" s="60" t="str">
-        <x:v>ph_k7_st11_der_stromkreis_und_der_schalter</x:v>
+        <x:v>ph_k7_st11_stromkreis</x:v>
       </x:c>
       <x:c r="L15" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/001_stromkreis.jpg</x:v>
       </x:c>
       <x:c r="M15" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_11_stromkreis.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st11_stromkreis_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N15" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st11_der_stromkreis_und_der_schalter_orga.html","Vorbereitung öffnen")</x:f>
@@ -2108,13 +2108,13 @@
         <x:v>nein</x:v>
       </x:c>
       <x:c r="K16" s="60" t="str">
-        <x:v>ph_k7_st12_reihen_und_parallelschaltung</x:v>
+        <x:v>ph_k7_st12_reihen_parallel</x:v>
       </x:c>
       <x:c r="L16" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/012_parallelschaltung.jpg</x:v>
       </x:c>
       <x:c r="M16" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_12_reihen_parallel.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st12_reihen_parallel_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N16" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st12_reihen_und_parallelschaltung_orga.html","Vorbereitung öffnen")</x:f>
@@ -2153,13 +2153,13 @@
         <x:v>nein</x:v>
       </x:c>
       <x:c r="K17" s="60" t="str">
-        <x:v>ph_k7_st13_elektrische_leistung_wie_viel_energie_verbrauchen_gerate</x:v>
+        <x:v>ph_k7_st13_leistung</x:v>
       </x:c>
       <x:c r="L17" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/038_arbeit_leistung.jpg</x:v>
       </x:c>
       <x:c r="M17" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_13_leistung.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st13_leistung_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N17" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st13_elektrische_leistung_wie_viel_energie_verbrauchen_gerate_orga.html","Vorbereitung öffnen")</x:f>
@@ -2198,13 +2198,13 @@
         <x:v>nein</x:v>
       </x:c>
       <x:c r="K18" s="60" t="str">
-        <x:v>ph_k7_st14_sicherheit_im_stromkreis_schutz_vor_uberlastung_und_kurzschluss</x:v>
+        <x:v>ph_k7_st14_sicherheit</x:v>
       </x:c>
       <x:c r="L18" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/001_stromkreis.jpg</x:v>
       </x:c>
       <x:c r="M18" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_14_sicherheit.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st14_sicherheit_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N18" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st14_sicherheit_im_stromkreis_schutz_vor_uberlastung_und_kurzschluss_orga.html","Vorbereitung öffnen")</x:f>
@@ -2243,13 +2243,13 @@
         <x:v>entfällt</x:v>
       </x:c>
       <x:c r="K19" s="60" t="str">
-        <x:v>ph_k7_st19_die_mechanische_arbeit_kraft_mal_weg</x:v>
+        <x:v>ph_k7_st19_mechanische_arbeit</x:v>
       </x:c>
       <x:c r="L19" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/021_kraft_gewicht.jpg</x:v>
       </x:c>
       <x:c r="M19" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_19_mechanische_arbeit.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st19_mechanische_arbeit_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N19" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st19_die_mechanische_arbeit_kraft_mal_weg_orga.html","Vorbereitung öffnen")</x:f>
@@ -2288,13 +2288,13 @@
         <x:v>Automatische Zeitmessung des Hubvorgangs zwischen zwei Höhenschwellen zur Berechnung der Leistung (Lehrerdemonstration)</x:v>
       </x:c>
       <x:c r="K20" s="60" t="str">
-        <x:v>ph_k7_st20_die_leistung_arbeit_pro_zeit</x:v>
+        <x:v>ph_k7_st20_leistung</x:v>
       </x:c>
       <x:c r="L20" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/038_arbeit_leistung.jpg</x:v>
       </x:c>
       <x:c r="M20" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_20_leistung.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st20_leistung_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N20" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st20_die_leistung_arbeit_pro_zeit_orga.html","Vorbereitung öffnen")</x:f>
@@ -2333,13 +2333,13 @@
         <x:v>entfällt</x:v>
       </x:c>
       <x:c r="K21" s="60" t="str">
-        <x:v>ph_k7_st21_energie_und_energieformen_lageenergie_und_bewegungsenergie</x:v>
+        <x:v>ph_k7_st21_energieformen</x:v>
       </x:c>
       <x:c r="L21" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/023_gleichfoermige_bewegung.jpg</x:v>
       </x:c>
       <x:c r="M21" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_21_energieformen.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st21_energieformen_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N21" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st21_energie_und_energieformen_lageenergie_und_bewegungsenergie_orga.html","Vorbereitung öffnen")</x:f>
@@ -2378,13 +2378,13 @@
         <x:v>Helligkeitsmessung zweier Leuchtmittel mit stark unterschiedlicher Leistung bei gleichem Abstand (Lehrerdemonstration)</x:v>
       </x:c>
       <x:c r="K22" s="60" t="str">
-        <x:v>ph_k7_st22_energie_sparen_im_alltag_leuchtmittel_im_vergleich</x:v>
+        <x:v>ph_k7_st22_energiesparen</x:v>
       </x:c>
       <x:c r="L22" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/090_physik_klassenraum.jpg</x:v>
       </x:c>
       <x:c r="M22" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_22_energiesparen.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st22_energiesparen_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N22" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st22_energie_sparen_im_alltag_leuchtmittel_im_vergleich_orga.html","Vorbereitung öffnen")</x:f>
@@ -2423,13 +2423,13 @@
         <x:v>entfällt</x:v>
       </x:c>
       <x:c r="K23" s="60" t="str">
-        <x:v>ph_k7_st23_wiederholung_und_vertiefung_arbeit_leistung_energie</x:v>
+        <x:v>ph_k7_st23_wiederholung</x:v>
       </x:c>
       <x:c r="L23" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/038_arbeit_leistung.jpg</x:v>
       </x:c>
       <x:c r="M23" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_23_wiederholung.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st23_wiederholung_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N23" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st23_wiederholung_und_vertiefung_arbeit_leistung_energie_orga.html","Vorbereitung öffnen")</x:f>
@@ -2468,13 +2468,13 @@
         <x:v>Automatisierte Messung des Wasserstands vor und nach dem Eintauchen eines Körpers zur Bestimmung seines Volumens (Schülerexperiment)</x:v>
       </x:c>
       <x:c r="K24" s="60" t="str">
-        <x:v>ph_k7_st24_masse_volumen_und_dichte</x:v>
+        <x:v>ph_k7_st24_dichte</x:v>
       </x:c>
       <x:c r="L24" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/025_dichte_experiment.jpg</x:v>
       </x:c>
       <x:c r="M24" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_24_dichte.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st24_dichte_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N24" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st24_masse_volumen_und_dichte_orga.html","Vorbereitung öffnen")</x:f>
@@ -2513,13 +2513,13 @@
         <x:v>entfällt</x:v>
       </x:c>
       <x:c r="K25" s="60" t="str">
-        <x:v>ph_k7_st25_auftrieb_warum_schwimmen_manche_dinge</x:v>
+        <x:v>ph_k7_st25_auftrieb</x:v>
       </x:c>
       <x:c r="L25" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/081_auftrieb.jpg</x:v>
       </x:c>
       <x:c r="M25" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_25_auftrieb.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st25_auftrieb_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N25" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st25_auftrieb_warum_schwimmen_manche_dinge_orga.html","Vorbereitung öffnen")</x:f>
@@ -2558,13 +2558,13 @@
         <x:v>entfällt</x:v>
       </x:c>
       <x:c r="K26" s="60" t="str">
-        <x:v>ph_k8_st01_geschwindigkeit_was_bedeutet_schnell</x:v>
+        <x:v>ph_k8_st01_geschwindigkeit</x:v>
       </x:c>
       <x:c r="L26" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/023_gleichfoermige_bewegung.jpg</x:v>
       </x:c>
       <x:c r="M26" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_01_geschwindigkeit.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st01_geschwindigkeit_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N26" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st01_geschwindigkeit_was_bedeutet_schnell_orga.html","Vorbereitung öffnen")</x:f>
@@ -2603,13 +2603,13 @@
         <x:v>Fortlaufende Positionsmessung eines Wagens zur Erstellung eines Weg-Zeit-Diagramms (Lehrerdemonstration)</x:v>
       </x:c>
       <x:c r="K27" s="60" t="str">
-        <x:v>ph_k8_st02_bewegungsarten_und_das_weg_zeit_diagramm</x:v>
+        <x:v>ph_k8_st02_weg_zeit_diagramm</x:v>
       </x:c>
       <x:c r="L27" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/023_gleichfoermige_bewegung.jpg</x:v>
       </x:c>
       <x:c r="M27" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_02_weg_zeit_diagramm.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st02_weg_zeit_diagramm_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N27" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st02_bewegungsarten_und_das_weg_zeit_diagramm_orga.html","Vorbereitung öffnen")</x:f>
@@ -2648,13 +2648,13 @@
         <x:v>entfällt</x:v>
       </x:c>
       <x:c r="K28" s="60" t="str">
-        <x:v>ph_k8_st03_durchschnitts_und_momentangeschwindigkeit</x:v>
+        <x:v>ph_k8_st03_durchschnitt_moment</x:v>
       </x:c>
       <x:c r="L28" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/023_gleichfoermige_bewegung.jpg</x:v>
       </x:c>
       <x:c r="M28" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_03_durchschnitt_moment.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st03_durchschnitt_moment_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N28" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st03_durchschnitts_und_momentangeschwindigkeit_orga.html","Vorbereitung öffnen")</x:f>
@@ -2693,13 +2693,13 @@
         <x:v>Fortlaufende Positionsmessung zur Berechnung der Geschwindigkeitszunahme und daraus der Beschleunigung (Schülerexperiment)</x:v>
       </x:c>
       <x:c r="K29" s="60" t="str">
-        <x:v>ph_k8_st04_beschleunigung_wenn_sich_die_geschwindigkeit_andert</x:v>
+        <x:v>ph_k8_st04_beschleunigung</x:v>
       </x:c>
       <x:c r="L29" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/092_beschleunigung.jpg</x:v>
       </x:c>
       <x:c r="M29" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_04_beschleunigung.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st04_beschleunigung_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N29" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st04_beschleunigung_wenn_sich_die_geschwindigkeit_andert_orga.html","Vorbereitung öffnen")</x:f>
@@ -2744,7 +2744,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/097_formeln_uebersicht.jpg</x:v>
       </x:c>
       <x:c r="M30" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_09_wiederholung_dynamik.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st09_wiederholung_dynamik_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N30" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st09_wiederholung_dynamik_orga.html","Vorbereitung öffnen")</x:f>
@@ -2783,13 +2783,13 @@
         <x:v>Automatisierte Temperaturaufzeichnung beim Erhitzen von Eis bis zum Sieden zur Erstellung einer Erhitzungskurve (Lehrerdemonstration)</x:v>
       </x:c>
       <x:c r="K31" s="60" t="str">
-        <x:v>ph_k8_st10_aggregatzustande</x:v>
+        <x:v>ph_k8_st10_aggregatzustaende</x:v>
       </x:c>
       <x:c r="L31" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/026_temperatur_waerme.jpg</x:v>
       </x:c>
       <x:c r="M31" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_10_aggregatzustaende.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st10_aggregatzustaende_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N31" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st10_aggregatzustande_orga.html","Vorbereitung öffnen")</x:f>
@@ -2828,13 +2828,13 @@
         <x:v>entfällt</x:v>
       </x:c>
       <x:c r="K32" s="60" t="str">
-        <x:v>ph_k8_st11_warmeausdehnung</x:v>
+        <x:v>ph_k8_st11_waermeausdehnung</x:v>
       </x:c>
       <x:c r="L32" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/026_temperatur_waerme.jpg</x:v>
       </x:c>
       <x:c r="M32" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_11_waermeausdehnung.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st11_waermeausdehnung_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N32" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st11_warmeausdehnung_orga.html","Vorbereitung öffnen")</x:f>
@@ -2873,13 +2873,13 @@
         <x:v>Gleichzeitige, automatisierte Temperaturmessung zweier Stoffe zur Bestimmung der unterschiedlichen spezifischen Wärmekapazität (Schülerexperiment)</x:v>
       </x:c>
       <x:c r="K33" s="60" t="str">
-        <x:v>ph_k8_st12_warmemenge_und_spezifische_warmekapazitat</x:v>
+        <x:v>ph_k8_st12_waermekapazitaet</x:v>
       </x:c>
       <x:c r="L33" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/026_temperatur_waerme.jpg</x:v>
       </x:c>
       <x:c r="M33" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_12_waermekapazitaet.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st12_waermekapazitaet_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N33" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st12_warmemenge_und_spezifische_warmekapazitat_orga.html","Vorbereitung öffnen")</x:f>
@@ -2924,7 +2924,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/090_physik_klassenraum.jpg</x:v>
       </x:c>
       <x:c r="M34" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_17_magnetismus.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st17_magnetismus_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N34" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st17_magnetismus_orga.html","Vorbereitung öffnen")</x:f>
@@ -2969,7 +2969,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/018_kompass_erdmagnetfeld.jpg</x:v>
       </x:c>
       <x:c r="M35" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_18_kompass.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st18_kompass_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N35" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st18_kompass_orga.html","Vorbereitung öffnen")</x:f>
@@ -3014,7 +3014,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/019_elektromagnet.jpg</x:v>
       </x:c>
       <x:c r="M36" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_19_elektromagnet.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st19_elektromagnet_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N36" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st19_elektromagnet_orga.html","Vorbereitung öffnen")</x:f>
@@ -3059,7 +3059,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/043_induktion.jpg</x:v>
       </x:c>
       <x:c r="M37" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_20_induktion.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st20_induktion_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N37" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st20_induktion_orga.html","Vorbereitung öffnen")</x:f>
@@ -3104,7 +3104,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/097_formeln_uebersicht.jpg</x:v>
       </x:c>
       <x:c r="M38" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_21_wiederholung_magnetismus.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st21_wiederholung_magnetismus_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N38" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st21_wiederholung_magnetismus_orga.html","Vorbereitung öffnen")</x:f>
@@ -3149,7 +3149,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/005_tafelbild_ohm.jpg</x:v>
       </x:c>
       <x:c r="M39" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_22_ohmsches_gesetz.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st22_ohmsches_gesetz_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N39" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st22_ohmsches_gesetz_orga.html","Vorbereitung öffnen")</x:f>
@@ -3194,7 +3194,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/090_physik_klassenraum.jpg</x:v>
       </x:c>
       <x:c r="M40" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_23_reihe_parallel.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st23_reihe_parallel_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N40" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st23_reihe_parallel_orga.html","Vorbereitung öffnen")</x:f>
@@ -3239,7 +3239,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/038_arbeit_leistung.jpg</x:v>
       </x:c>
       <x:c r="M41" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_24_leistung.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st24_leistung_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N41" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st24_leistung_orga.html","Vorbereitung öffnen")</x:f>
@@ -3284,7 +3284,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/097_formeln_uebersicht.jpg</x:v>
       </x:c>
       <x:c r="M42" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_25_wiederholung_elektrizitaet.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st25_wiederholung_elektrizitaet_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N42" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st25_wiederholung_elektrizitaet_orga.html","Vorbereitung öffnen")</x:f>
@@ -3329,7 +3329,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/006_lichtbrechung.jpg</x:v>
       </x:c>
       <x:c r="M43" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_26_lichtbrechung.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st26_lichtbrechung_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N43" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st26_lichtbrechung_orga.html","Vorbereitung öffnen")</x:f>
@@ -3374,7 +3374,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/093_optische_instrumente.jpg</x:v>
       </x:c>
       <x:c r="M44" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_27_linsen.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st27_linsen_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N44" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st27_linsen_orga.html","Vorbereitung öffnen")</x:f>
@@ -3419,7 +3419,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/093_optische_instrumente.jpg</x:v>
       </x:c>
       <x:c r="M45" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_28_auge.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st28_auge_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N45" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st28_auge_orga.html","Vorbereitung öffnen")</x:f>
@@ -3464,7 +3464,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/097_formeln_uebersicht.jpg</x:v>
       </x:c>
       <x:c r="M46" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_29_wiederholung_optik_vertieft.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st29_wiederholung_optik_vertieft_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N46" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st29_wiederholung_optik_vertieft_orga.html","Vorbereitung öffnen")</x:f>
@@ -3509,7 +3509,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/097_formeln_uebersicht.jpg</x:v>
       </x:c>
       <x:c r="M47" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_30_gesamtwiederholung_klasse_8.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st30_gesamtwiederholung_klasse_8_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N47" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st30_gesamtwiederholung_klasse_8_orga.html","Vorbereitung öffnen")</x:f>
@@ -3554,7 +3554,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/017_magnet_feldlinien.jpg</x:v>
       </x:c>
       <x:c r="M48" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_01_magnetische_pole_und_kraftwirkungen.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st01_magnetische_pole_und_kraftwirkungen_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N48" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st01_magnetische_pole_und_kraftwirkungen_orga.html","Vorbereitung öffnen")</x:f>
@@ -3599,7 +3599,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/017_magnet_feldlinien.jpg</x:v>
       </x:c>
       <x:c r="M49" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_02_magnetfeld_und_feldlinienmodell.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st02_magnetfeld_und_feldlinienmodell_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N49" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st02_magnetfeld_und_feldlinienmodell_orga.html","Vorbereitung öffnen")</x:f>
@@ -3644,7 +3644,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/018_kompass_erdmagnetfeld.jpg</x:v>
       </x:c>
       <x:c r="M50" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_03_erdmagnetfeld_und_kompass.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st03_erdmagnetfeld_und_kompass_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N50" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st03_erdmagnetfeld_und_kompass_orga.html","Vorbereitung öffnen")</x:f>
@@ -3689,7 +3689,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/090_physik_klassenraum.jpg</x:v>
       </x:c>
       <x:c r="M51" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_04_elektrisches_und_magnetisches_feld_vergleichen.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st04_elektrisches_und_magnetisches_feld_vergleichen_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N51" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st04_elektrisches_und_magnetisches_feld_vergleichen_orga.html","Vorbereitung öffnen")</x:f>
@@ -3734,7 +3734,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/019_elektromagnet.jpg</x:v>
       </x:c>
       <x:c r="M52" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_05_elektromagnet_aufbau_und_wirkungsweise.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st05_elektromagnet_aufbau_und_wirkungsweise_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N52" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st05_elektromagnet_aufbau_und_wirkungsweise_orga.html","Vorbereitung öffnen")</x:f>
@@ -3773,13 +3773,13 @@
         <x:v>PWM-Stufen und Hall-Sensor zur relativen Feldmessung nutzen</x:v>
       </x:c>
       <x:c r="K53" s="60" t="str">
-        <x:v>ph_k9_st06_starke_eines_elektromagneten_untersuchen</x:v>
+        <x:v>ph_k9_st06_staerke_eines_elektromagneten_untersuchen</x:v>
       </x:c>
       <x:c r="L53" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/019_elektromagnet.jpg</x:v>
       </x:c>
       <x:c r="M53" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_06_staerke_eines_elektromagneten_untersuchen.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st06_staerke_eines_elektromagneten_untersuchen_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N53" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st06_starke_eines_elektromagneten_untersuchen_orga.html","Vorbereitung öffnen")</x:f>
@@ -3824,7 +3824,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/017_magnet_feldlinien.jpg</x:v>
       </x:c>
       <x:c r="M54" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_07_kraft_auf_einen_stromdurchflossenen_leiter_im_magnetfeld.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st07_kraft_auf_einen_stromdurchflossenen_leiter_im_magnetfeld_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N54" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st07_kraft_auf_einen_stromdurchflossenen_leiter_im_magnetfeld_orga.html","Vorbereitung öffnen")</x:f>
@@ -3869,7 +3869,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/044_generator_motor.jpg</x:v>
       </x:c>
       <x:c r="M55" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_08_elektromotor_elektrische_energie_erzeugt_bewegung.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st08_elektromotor_elektrische_energie_erzeugt_bewegung_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N55" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st08_elektromotor_elektrische_energie_erzeugt_bewegung_orga.html","Vorbereitung öffnen")</x:f>
@@ -3908,13 +3908,13 @@
         <x:v>Relaismodul mit Taster und Status-LED steuern</x:v>
       </x:c>
       <x:c r="K56" s="60" t="str">
-        <x:v>ph_k9_st09_relais_und_elektromagnetischer_turoffner</x:v>
+        <x:v>ph_k9_st09_relais_und_elektromagnetischer_tueroeffner</x:v>
       </x:c>
       <x:c r="L56" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/044_generator_motor.jpg</x:v>
       </x:c>
       <x:c r="M56" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_09_relais_und_elektromagnetischer_tueroeffner.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st09_relais_und_elektromagnetischer_tueroeffner_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N56" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st09_relais_und_elektromagnetischer_turoffner_orga.html","Vorbereitung öffnen")</x:f>
@@ -3959,7 +3959,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/044_generator_motor.jpg</x:v>
       </x:c>
       <x:c r="M57" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_10_lautsprecher_und_anwendungen_des_elektromagnetismus.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st10_lautsprecher_und_anwendungen_des_elektromagnetismus_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N57" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st10_lautsprecher_und_anwendungen_des_elektromagnetismus_orga.html","Vorbereitung öffnen")</x:f>
@@ -4004,7 +4004,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/023_gleichfoermige_bewegung.jpg</x:v>
       </x:c>
       <x:c r="M58" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_11_bewegung_bezugssystem_weg_und_zeit.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st11_bewegung_bezugssystem_weg_und_zeit_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N58" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st11_bewegung_bezugssystem_weg_und_zeit_orga.html","Vorbereitung öffnen")</x:f>
@@ -4049,7 +4049,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/023_gleichfoermige_bewegung.jpg</x:v>
       </x:c>
       <x:c r="M59" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_12_geschwindigkeit_messen_und_berechnen.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st12_geschwindigkeit_messen_und_berechnen_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N59" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st12_geschwindigkeit_messen_und_berechnen_orga.html","Vorbereitung öffnen")</x:f>
@@ -4088,13 +4088,13 @@
         <x:v>Weg-Zeit-Daten mit HC-SR04 protokollieren</x:v>
       </x:c>
       <x:c r="K60" s="60" t="str">
-        <x:v>ph_k9_st13_geradlinig_gleichformige_bewegung_und_s_t_diagramm</x:v>
+        <x:v>ph_k9_st13_geradlinig_gleichfoermige_bewegung_und_s_t_diagramm</x:v>
       </x:c>
       <x:c r="L60" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/023_gleichfoermige_bewegung.jpg</x:v>
       </x:c>
       <x:c r="M60" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_13_geradlinig_gleichfoermige_bewegung_und_s_t_diagramm.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st13_geradlinig_gleichfoermige_bewegung_und_s_t_diagramm_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N60" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st13_geradlinig_gleichformige_bewegung_und_s_t_diagramm_orga.html","Vorbereitung öffnen")</x:f>
@@ -4133,13 +4133,13 @@
         <x:v>—</x:v>
       </x:c>
       <x:c r="K61" s="60" t="str">
-        <x:v>ph_k9_st14_gleichformige_bewegung_gleichungen_und_diagramme_anwenden</x:v>
+        <x:v>ph_k9_st14_gleichfoermige_bewegung_gleichungen_und_diagramme_anwenden</x:v>
       </x:c>
       <x:c r="L61" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/023_gleichfoermige_bewegung.jpg</x:v>
       </x:c>
       <x:c r="M61" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_14_gleichfoermige_bewegung_gleichungen_und_diagramme_anwenden.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st14_gleichfoermige_bewegung_gleichungen_und_diagramme_anwenden_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N61" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st14_gleichformige_bewegung_gleichungen_und_diagramme_anwenden_orga.html","Vorbereitung öffnen")</x:f>
@@ -4178,13 +4178,13 @@
         <x:v>Beschleunigungswerte mit MPU6050 als Rohdaten erfassen</x:v>
       </x:c>
       <x:c r="K62" s="60" t="str">
-        <x:v>ph_k9_st15_beschleunigung_als_anderung_der_geschwindigkeit</x:v>
+        <x:v>ph_k9_st15_beschleunigung_als_aenderung_der_geschwindigkeit</x:v>
       </x:c>
       <x:c r="L62" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/092_beschleunigung.jpg</x:v>
       </x:c>
       <x:c r="M62" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_15_beschleunigung_als_aenderung_der_geschwindigkeit.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st15_beschleunigung_als_aenderung_der_geschwindigkeit_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N62" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st15_beschleunigung_als_anderung_der_geschwindigkeit_orga.html","Vorbereitung öffnen")</x:f>
@@ -4223,13 +4223,13 @@
         <x:v>Beschleunigungsdaten mit MPU6050 aufzeichnen und mitteln</x:v>
       </x:c>
       <x:c r="K63" s="60" t="str">
-        <x:v>ph_k9_st16_geradlinig_gleichmaig_beschleunigte_bewegung</x:v>
+        <x:v>ph_k9_st16_geradlinig_gleichmaessig_beschleunigte_bewegung</x:v>
       </x:c>
       <x:c r="L63" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/023_gleichfoermige_bewegung.jpg</x:v>
       </x:c>
       <x:c r="M63" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_16_geradlinig_gleichmaessig_beschleunigte_bewegung.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st16_geradlinig_gleichmaessig_beschleunigte_bewegung_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N63" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st16_geradlinig_gleichmaig_beschleunigte_bewegung_orga.html","Vorbereitung öffnen")</x:f>
@@ -4274,7 +4274,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/092_beschleunigung.jpg</x:v>
       </x:c>
       <x:c r="M64" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_17_freier_fall_als_beschleunigte_bewegung.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st17_freier_fall_als_beschleunigte_bewegung_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N64" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st17_freier_fall_als_beschleunigte_bewegung_orga.html","Vorbereitung öffnen")</x:f>
@@ -4319,7 +4319,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/023_gleichfoermige_bewegung.jpg</x:v>
       </x:c>
       <x:c r="M65" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_18_bewegungsformen_bewegungsarten_und_verkehrssicherheit.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st18_bewegungsformen_bewegungsarten_und_verkehrssicherheit_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N65" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st18_bewegungsformen_bewegungsarten_und_verkehrssicherheit_orga.html","Vorbereitung öffnen")</x:f>
@@ -4358,13 +4358,13 @@
         <x:v>Kraft mit Wägezelle und HX711 nach Kalibrierung messen</x:v>
       </x:c>
       <x:c r="K66" s="60" t="str">
-        <x:v>ph_k9_st19_kraft_als_wechselwirkung_und_physikalische_groe</x:v>
+        <x:v>ph_k9_st19_kraft_als_wechselwirkung_und_physikalische_groesse</x:v>
       </x:c>
       <x:c r="L66" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/024_newton_krafte.jpg</x:v>
       </x:c>
       <x:c r="M66" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_19_kraft_als_wechselwirkung_und_physikalische_groesse.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st19_kraft_als_wechselwirkung_und_physikalische_groesse_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N66" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st19_kraft_als_wechselwirkung_und_physikalische_groe_orga.html","Vorbereitung öffnen")</x:f>
@@ -4403,13 +4403,13 @@
         <x:v>—</x:v>
       </x:c>
       <x:c r="K67" s="60" t="str">
-        <x:v>ph_k9_st20_erstes_newtonsches_gesetz_tragheit</x:v>
+        <x:v>ph_k9_st20_erstes_newtonsches_gesetz_traegheit</x:v>
       </x:c>
       <x:c r="L67" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/024_newton_krafte.jpg</x:v>
       </x:c>
       <x:c r="M67" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_20_erstes_newtonsches_gesetz_traegheit.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st20_erstes_newtonsches_gesetz_traegheit_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N67" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st20_erstes_newtonsches_gesetz_tragheit_orga.html","Vorbereitung öffnen")</x:f>
@@ -4454,7 +4454,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/092_beschleunigung.jpg</x:v>
       </x:c>
       <x:c r="M68" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_21_zweites_newtonsches_gesetz_kraft_masse_und_beschleunigung.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st21_zweites_newtonsches_gesetz_kraft_masse_und_beschleunigung_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N68" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st21_zweites_newtonsches_gesetz_kraft_masse_und_beschleunigung_orga.html","Vorbereitung öffnen")</x:f>
@@ -4499,7 +4499,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/024_newton_krafte.jpg</x:v>
       </x:c>
       <x:c r="M69" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_22_drittes_newtonsches_gesetz_actio_und_reactio.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st22_drittes_newtonsches_gesetz_actio_und_reactio_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N69" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st22_drittes_newtonsches_gesetz_actio_und_reactio_orga.html","Vorbereitung öffnen")</x:f>
@@ -4544,7 +4544,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/091_gravitation.jpg</x:v>
       </x:c>
       <x:c r="M70" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_23_gravitation_masse_und_gewichtskraft.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st23_gravitation_masse_und_gewichtskraft_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N70" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st23_gravitation_masse_und_gewichtskraft_orga.html","Vorbereitung öffnen")</x:f>
@@ -4583,13 +4583,13 @@
         <x:v>Wahlstationen mit Ultraschall, Lichtschranke oder Wägezelle</x:v>
       </x:c>
       <x:c r="K71" s="60" t="str">
-        <x:v>ph_k9_st24_projekt_und_lernkontrolle_bewegungen_und_krafte_im_alltag</x:v>
+        <x:v>ph_k9_st24_projekt_und_lernkontrolle_bewegungen_und_kraefte_im_alltag</x:v>
       </x:c>
       <x:c r="L71" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/023_gleichfoermige_bewegung.jpg</x:v>
       </x:c>
       <x:c r="M71" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_24_projekt_und_lernkontrolle_bewegungen_und_kraefte_im_alltag.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st24_projekt_und_lernkontrolle_bewegungen_und_kraefte_im_alltag_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N71" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st24_projekt_und_lernkontrolle_bewegungen_und_krafte_im_alltag_orga.html","Vorbereitung öffnen")</x:f>
@@ -4628,13 +4628,13 @@
         <x:v>Magnetfeld mit linearem Hall-Sensor erfassen</x:v>
       </x:c>
       <x:c r="K72" s="60" t="str">
-        <x:v>ph_k10_st01_magnetische_pole_krafte_und_erdmagnetfeld</x:v>
+        <x:v>ph_k10_st01_magnetische_pole_kraefte_und_erdmagnetfeld</x:v>
       </x:c>
       <x:c r="L72" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/018_kompass_erdmagnetfeld.jpg</x:v>
       </x:c>
       <x:c r="M72" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_01_magnetische_pole_kraefte_und_erdmagnetfeld.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st01_magnetische_pole_kraefte_und_erdmagnetfeld_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N72" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st01_magnetische_pole_krafte_und_erdmagnetfeld_orga.html","Vorbereitung öffnen")</x:f>
@@ -4679,7 +4679,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/090_physik_klassenraum.jpg</x:v>
       </x:c>
       <x:c r="M73" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_02_elektrisches_und_magnetisches_feld_vergleichen.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st02_elektrisches_und_magnetisches_feld_vergleichen_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N73" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st02_elektrisches_und_magnetisches_feld_vergleichen_orga.html","Vorbereitung öffnen")</x:f>
@@ -4718,13 +4718,13 @@
         <x:v>zeitgesteuerte Ansteuerung über MOSFET-Modul und Strommessung</x:v>
       </x:c>
       <x:c r="K74" s="60" t="str">
-        <x:v>ph_k10_st03_elektromagnet_windungszahl_stromstarke_und_eisenkern</x:v>
+        <x:v>ph_k10_st03_elektromagnet_windungszahl_stromstaerke_und_eisenkern</x:v>
       </x:c>
       <x:c r="L74" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/019_elektromagnet.jpg</x:v>
       </x:c>
       <x:c r="M74" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_03_elektromagnet_windungszahl_stromstaerke_und_eisenkern.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st03_elektromagnet_windungszahl_stromstaerke_und_eisenkern_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N74" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st03_elektromagnet_windungszahl_stromstarke_und_eisenkern_orga.html","Vorbereitung öffnen")</x:f>
@@ -4769,7 +4769,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/019_elektromagnet.jpg</x:v>
       </x:c>
       <x:c r="M75" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_04_kraft_auf_einen_stromdurchflossenen_leiter.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st04_kraft_auf_einen_stromdurchflossenen_leiter_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N75" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st04_kraft_auf_einen_stromdurchflossenen_leiter_orga.html","Vorbereitung öffnen")</x:f>
@@ -4814,7 +4814,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/044_generator_motor.jpg</x:v>
       </x:c>
       <x:c r="M76" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_05_elektromotor_lautsprecher_und_relais.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st05_elektromotor_lautsprecher_und_relais_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N76" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st05_elektromotor_lautsprecher_und_relais_orga.html","Vorbereitung öffnen")</x:f>
@@ -4859,7 +4859,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/043_induktion.jpg</x:v>
       </x:c>
       <x:c r="M77" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_06_elektromagnetische_induktion.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st06_elektromagnetische_induktion_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N77" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st06_elektromagnetische_induktion_orga.html","Vorbereitung öffnen")</x:f>
@@ -4904,7 +4904,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/044_generator_motor.jpg</x:v>
       </x:c>
       <x:c r="M78" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_07_generator_und_wechselspannung.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st07_generator_und_wechselspannung_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N78" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st07_generator_und_wechselspannung_orga.html","Vorbereitung öffnen")</x:f>
@@ -4949,7 +4949,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/045_transformator.jpg</x:v>
       </x:c>
       <x:c r="M79" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_08_transformator_und_stromverbundnetz.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st08_transformator_und_stromverbundnetz_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N79" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st08_transformator_und_stromverbundnetz_orga.html","Vorbereitung öffnen")</x:f>
@@ -4994,7 +4994,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/023_gleichfoermige_bewegung.jpg</x:v>
       </x:c>
       <x:c r="M80" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_09_bewegung_bezugssystem_weg_zeit_und_geschwindigkeit.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st09_bewegung_bezugssystem_weg_zeit_und_geschwindigkeit_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N80" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st09_bewegung_bezugssystem_weg_zeit_und_geschwindigkeit_orga.html","Vorbereitung öffnen")</x:f>
@@ -5033,13 +5033,13 @@
         <x:v>Ultraschall-Datenlogger</x:v>
       </x:c>
       <x:c r="K81" s="60" t="str">
-        <x:v>ph_k10_st10_geradlinig_gleichformige_bewegung_und_diagramme</x:v>
+        <x:v>ph_k10_st10_geradlinig_gleichfoermige_bewegung_und_diagramme</x:v>
       </x:c>
       <x:c r="L81" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/023_gleichfoermige_bewegung.jpg</x:v>
       </x:c>
       <x:c r="M81" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_10_geradlinig_gleichfoermige_bewegung_und_diagramme.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st10_geradlinig_gleichfoermige_bewegung_und_diagramme_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N81" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st10_geradlinig_gleichformige_bewegung_und_diagramme_orga.html","Vorbereitung öffnen")</x:f>
@@ -5078,13 +5078,13 @@
         <x:v>Ultraschall-Datenlogger</x:v>
       </x:c>
       <x:c r="K82" s="60" t="str">
-        <x:v>ph_k10_st11_geradlinig_gleichmaig_beschleunigte_bewegung</x:v>
+        <x:v>ph_k10_st11_geradlinig_gleichmaessig_beschleunigte_bewegung</x:v>
       </x:c>
       <x:c r="L82" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/023_gleichfoermige_bewegung.jpg</x:v>
       </x:c>
       <x:c r="M82" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_11_geradlinig_gleichmaessig_beschleunigte_bewegung.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st11_geradlinig_gleichmaessig_beschleunigte_bewegung_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N82" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st11_geradlinig_gleichmaig_beschleunigte_bewegung_orga.html","Vorbereitung öffnen")</x:f>
@@ -5129,7 +5129,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/092_beschleunigung.jpg</x:v>
       </x:c>
       <x:c r="M83" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_12_freier_fall.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st12_freier_fall_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N83" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st12_freier_fall_orga.html","Vorbereitung öffnen")</x:f>
@@ -5168,13 +5168,13 @@
         <x:v>nein</x:v>
       </x:c>
       <x:c r="K84" s="60" t="str">
-        <x:v>ph_k10_st13_erstes_newtonsches_gesetz_und_tragheit</x:v>
+        <x:v>ph_k10_st13_erstes_newtonsches_gesetz_und_traegheit</x:v>
       </x:c>
       <x:c r="L84" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/024_newton_krafte.jpg</x:v>
       </x:c>
       <x:c r="M84" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_13_erstes_newtonsches_gesetz_und_traegheit.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st13_erstes_newtonsches_gesetz_und_traegheit_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N84" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st13_erstes_newtonsches_gesetz_und_tragheit_orga.html","Vorbereitung öffnen")</x:f>
@@ -5219,7 +5219,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/024_newton_krafte.jpg</x:v>
       </x:c>
       <x:c r="M85" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_14_zweites_newtonsches_gesetz_f_m_a.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st14_zweites_newtonsches_gesetz_f_m_a_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N85" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st14_zweites_newtonsches_gesetz_f_m_a_orga.html","Vorbereitung öffnen")</x:f>
@@ -5264,7 +5264,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/024_newton_krafte.jpg</x:v>
       </x:c>
       <x:c r="M86" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_15_drittes_newtonsches_gesetz_actio_und_reactio.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st15_drittes_newtonsches_gesetz_actio_und_reactio_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N86" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st15_drittes_newtonsches_gesetz_actio_und_reactio_orga.html","Vorbereitung öffnen")</x:f>
@@ -5309,7 +5309,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/004_sonnensystem.jpg</x:v>
       </x:c>
       <x:c r="M87" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_16_gravitation_gewichtskraft_und_planetenbewegung.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st16_gravitation_gewichtskraft_und_planetenbewegung_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N87" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st16_gravitation_gewichtskraft_und_planetenbewegung_orga.html","Vorbereitung öffnen")</x:f>
@@ -5348,13 +5348,13 @@
         <x:v>Drehzahlmessung mit Hall-Sensor</x:v>
       </x:c>
       <x:c r="K88" s="60" t="str">
-        <x:v>ph_k10_st17_gleichformige_kreisbewegung</x:v>
+        <x:v>ph_k10_st17_gleichfoermige_kreisbewegung</x:v>
       </x:c>
       <x:c r="L88" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/023_gleichfoermige_bewegung.jpg</x:v>
       </x:c>
       <x:c r="M88" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_17_gleichfoermige_kreisbewegung.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st17_gleichfoermige_kreisbewegung_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N88" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st17_gleichformige_kreisbewegung_orga.html","Vorbereitung öffnen")</x:f>
@@ -5393,13 +5393,13 @@
         <x:v>Abstandssensor zeichnet Schwingung auf</x:v>
       </x:c>
       <x:c r="K89" s="60" t="str">
-        <x:v>ph_k10_st18_schwingungen_und_ihre_kenngroen</x:v>
+        <x:v>ph_k10_st18_schwingungen_und_ihre_kenngroessen</x:v>
       </x:c>
       <x:c r="L89" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/094_schwingung_welle.jpg</x:v>
       </x:c>
       <x:c r="M89" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_18_schwingungen_und_ihre_kenngroessen.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st18_schwingungen_und_ihre_kenngroessen_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N89" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st18_schwingungen_und_ihre_kenngroen_orga.html","Vorbereitung öffnen")</x:f>
@@ -5444,7 +5444,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/094_schwingung_welle.jpg</x:v>
       </x:c>
       <x:c r="M90" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_19_schwingungsdauer_des_fadenpendels.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st19_schwingungsdauer_des_fadenpendels_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N90" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st19_schwingungsdauer_des_fadenpendels_orga.html","Vorbereitung öffnen")</x:f>
@@ -5489,7 +5489,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/094_schwingung_welle.jpg</x:v>
       </x:c>
       <x:c r="M91" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_20_wellen_als_ausbreitung_von_schwingungen.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st20_wellen_als_ausbreitung_von_schwingungen_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N91" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st20_wellen_als_ausbreitung_von_schwingungen_orga.html","Vorbereitung öffnen")</x:f>
@@ -5528,13 +5528,13 @@
         <x:v>Piezo-Ausgabe und Mikrofonmodul</x:v>
       </x:c>
       <x:c r="K92" s="60" t="str">
-        <x:v>ph_k10_st21_schall_frequenz_tonhohe_und_larmschutz</x:v>
+        <x:v>ph_k10_st21_schall_frequenz_tonhoehe_und_laermschutz</x:v>
       </x:c>
       <x:c r="L92" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/031_schall_wellen.jpg</x:v>
       </x:c>
       <x:c r="M92" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_21_schall_frequenz_tonhoehe_und_laermschutz.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st21_schall_frequenz_tonhoehe_und_laermschutz_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N92" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st21_schall_frequenz_tonhohe_und_larmschutz_orga.html","Vorbereitung öffnen")</x:f>
@@ -5573,13 +5573,13 @@
         <x:v>Kraftsensor und Wegsensor</x:v>
       </x:c>
       <x:c r="K93" s="60" t="str">
-        <x:v>ph_k10_st22_arbeit_energieformen_und_energie_als_zustandsgroe</x:v>
+        <x:v>ph_k10_st22_arbeit_energieformen_und_energie_als_zustandsgroesse</x:v>
       </x:c>
       <x:c r="L93" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/038_arbeit_leistung.jpg</x:v>
       </x:c>
       <x:c r="M93" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_22_arbeit_energieformen_und_energie_als_zustandsgroesse.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st22_arbeit_energieformen_und_energie_als_zustandsgroesse_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N93" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st22_arbeit_energieformen_und_energie_als_zustandsgroe_orga.html","Vorbereitung öffnen")</x:f>
@@ -5624,7 +5624,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/036_energie_formen.jpg</x:v>
       </x:c>
       <x:c r="M94" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_23_allgemeiner_energieerhaltungssatz.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st23_allgemeiner_energieerhaltungssatz_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N94" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st23_allgemeiner_energieerhaltungssatz_orga.html","Vorbereitung öffnen")</x:f>
@@ -5669,7 +5669,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/064_elektrische_energie.jpg</x:v>
       </x:c>
       <x:c r="M95" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_24_wirkungsgrad_und_versorgung_mit_elektrischer_energie.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st24_wirkungsgrad_und_versorgung_mit_elektrischer_energie_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N95" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st24_wirkungsgrad_und_versorgung_mit_elektrischer_energie_orga.html","Vorbereitung öffnen")</x:f>
@@ -5714,7 +5714,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/042_radioaktivitaet.jpg</x:v>
       </x:c>
       <x:c r="M96" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_25_atomkern_und_nuklidschreibweise.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st25_atomkern_und_nuklidschreibweise_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N96" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st25_atomkern_und_nuklidschreibweise_orga.html","Vorbereitung öffnen")</x:f>
@@ -5759,7 +5759,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/042_radioaktivitaet.jpg</x:v>
       </x:c>
       <x:c r="M97" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_26_und_strahlung_eigenschaften_nachweis_und_abschirmung.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st26_und_strahlung_eigenschaften_nachweis_und_abschirmung_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N97" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st26_und_strahlung_eigenschaften_nachweis_und_abschirmung_orga.html","Vorbereitung öffnen")</x:f>
@@ -5804,7 +5804,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/042_radioaktivitaet.jpg</x:v>
       </x:c>
       <x:c r="M98" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_27_radioaktiver_zerfall_und_halbwertszeit.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st27_radioaktiver_zerfall_und_halbwertszeit_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N98" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st27_radioaktiver_zerfall_und_halbwertszeit_orga.html","Vorbereitung öffnen")</x:f>
@@ -5849,11 +5849,74 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/054_sonne_aufbau.jpg</x:v>
       </x:c>
       <x:c r="M99" s="160" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_28_anwendungen_strahlenschutz_kernspaltung_und_kernfusion.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st28_anwendungen_strahlenschutz_kernspaltung_und_kernfusion_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N99" s="161" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st28_anwendungen_strahlenschutz_kernspaltung_und_kernfusion_orga.html","Vorbereitung öffnen")</x:f>
       </x:c>
+    </x:row>
+    <x:row r="100">
+      <x:c r="M100" s="51"/>
+    </x:row>
+    <x:row r="101">
+      <x:c r="M101" s="51"/>
+    </x:row>
+    <x:row r="102">
+      <x:c r="M102" s="51"/>
+    </x:row>
+    <x:row r="103">
+      <x:c r="M103" s="51"/>
+    </x:row>
+    <x:row r="104">
+      <x:c r="M104" s="51"/>
+    </x:row>
+    <x:row r="105">
+      <x:c r="M105" s="51"/>
+    </x:row>
+    <x:row r="106">
+      <x:c r="M106" s="51"/>
+    </x:row>
+    <x:row r="107">
+      <x:c r="M107" s="51"/>
+    </x:row>
+    <x:row r="108">
+      <x:c r="M108" s="51"/>
+    </x:row>
+    <x:row r="109">
+      <x:c r="M109" s="51"/>
+    </x:row>
+    <x:row r="110">
+      <x:c r="M110" s="51"/>
+    </x:row>
+    <x:row r="111">
+      <x:c r="M111" s="51"/>
+    </x:row>
+    <x:row r="112">
+      <x:c r="M112" s="51"/>
+    </x:row>
+    <x:row r="113">
+      <x:c r="M113" s="51"/>
+    </x:row>
+    <x:row r="114">
+      <x:c r="M114" s="51"/>
+    </x:row>
+    <x:row r="115">
+      <x:c r="M115" s="51"/>
+    </x:row>
+    <x:row r="116">
+      <x:c r="M116" s="51"/>
+    </x:row>
+    <x:row r="117">
+      <x:c r="M117" s="51"/>
+    </x:row>
+    <x:row r="118">
+      <x:c r="M118" s="51"/>
+    </x:row>
+    <x:row r="119">
+      <x:c r="M119" s="51"/>
+    </x:row>
+    <x:row r="120">
+      <x:c r="M120" s="51"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -5862,7 +5925,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8f9586a887be459a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R28473391f4874eca"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6000,13 +6063,13 @@
         <x:v>keiner</x:v>
       </x:c>
       <x:c r="K5" s="57" t="str">
-        <x:v>ph_k7_st01_was_ist_physik_beobachten_und_beschreiben</x:v>
+        <x:v>ph_k7_st01_was_ist_physik</x:v>
       </x:c>
       <x:c r="L5" s="57" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/096_physik_titelseite.jpg</x:v>
       </x:c>
       <x:c r="M5" s="156" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_01_was_ist_physik.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st01_was_ist_physik_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N5" s="157" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st01_was_ist_physik_beobachten_und_beschreiben_orga.html","Vorbereitung öffnen")</x:f>
@@ -6045,13 +6108,13 @@
         <x:v>Reaktionszeitmessung mit Taster und LED als Vergleichsstation</x:v>
       </x:c>
       <x:c r="K6" s="60" t="str">
-        <x:v>ph_k7_st02_messen_und_protokollieren_die_reaktionszeit</x:v>
+        <x:v>ph_k7_st02_messen_und_protokollieren</x:v>
       </x:c>
       <x:c r="L6" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/074_messgeraete.jpg</x:v>
       </x:c>
       <x:c r="M6" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_02_messen_und_protokollieren.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st02_messen_und_protokollieren_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N6" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st02_messen_und_protokollieren_die_reaktionszeit_orga.html","Vorbereitung öffnen")</x:f>
@@ -6090,13 +6153,13 @@
         <x:v>keiner</x:v>
       </x:c>
       <x:c r="K7" s="60" t="str">
-        <x:v>ph_k7_st03_lichtquellen_und_die_geradlinige_ausbreitung_des_lichts</x:v>
+        <x:v>ph_k7_st03_lichtquellen_und_lichtausbreitung</x:v>
       </x:c>
       <x:c r="L7" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/034_arduino_licht_optik.jpg</x:v>
       </x:c>
       <x:c r="M7" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_03_lichtquellen_und_lichtausbreitung.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st03_lichtquellen_und_lichtausbreitung_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N7" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st03_lichtquellen_und_die_geradlinige_ausbreitung_des_lichts_orga.html","Vorbereitung öffnen")</x:f>
@@ -6135,13 +6198,13 @@
         <x:v>Helligkeitsmessung in Kernschatten, Halbschatten und beleuchteter Fläche (Lehrerdemonstration)</x:v>
       </x:c>
       <x:c r="K8" s="60" t="str">
-        <x:v>ph_k7_st04_licht_und_schatten_kernschatten_und_halbschatten</x:v>
+        <x:v>ph_k7_st04_licht_und_schatten</x:v>
       </x:c>
       <x:c r="L8" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/034_arduino_licht_optik.jpg</x:v>
       </x:c>
       <x:c r="M8" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_04_licht_und_schatten.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st04_licht_und_schatten_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N8" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st04_licht_und_schatten_kernschatten_und_halbschatten_orga.html","Vorbereitung öffnen")</x:f>
@@ -6180,13 +6243,13 @@
         <x:v>keiner</x:v>
       </x:c>
       <x:c r="K9" s="60" t="str">
-        <x:v>ph_k7_st05_mondphasen_und_finsternisse_schatten_im_weltall</x:v>
+        <x:v>ph_k7_st05_mondphasen</x:v>
       </x:c>
       <x:c r="L9" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/009_mondphasen.jpg</x:v>
       </x:c>
       <x:c r="M9" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_05_mondphasen_und_finsternisse.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st05_mondphasen_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N9" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st05_mondphasen_und_finsternisse_schatten_im_weltall_orga.html","Vorbereitung öffnen")</x:f>
@@ -6225,13 +6288,13 @@
         <x:v>keiner</x:v>
       </x:c>
       <x:c r="K10" s="60" t="str">
-        <x:v>ph_k7_st06_reflexion_und_das_spiegelgesetz_lichtstrahlen_andern_die_richtung</x:v>
+        <x:v>ph_k7_st06_reflexion</x:v>
       </x:c>
       <x:c r="L10" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/035_reflexion_spiegel.jpg</x:v>
       </x:c>
       <x:c r="M10" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_06_reflexion_spiegelgesetz.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st06_reflexion_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N10" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st06_reflexion_und_das_spiegelgesetz_lichtstrahlen_andern_die_richtung_orga.html","Vorbereitung öffnen")</x:f>
@@ -6270,13 +6333,13 @@
         <x:v>keiner</x:v>
       </x:c>
       <x:c r="K11" s="60" t="str">
-        <x:v>ph_k7_st07_spiegelbilder_wie_entsteht_das_bild_im_spiegel</x:v>
+        <x:v>ph_k7_st07_spiegelbilder</x:v>
       </x:c>
       <x:c r="L11" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/035_reflexion_spiegel.jpg</x:v>
       </x:c>
       <x:c r="M11" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_07_spiegelbilder.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st07_spiegelbilder_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N11" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st07_spiegelbilder_wie_entsteht_das_bild_im_spiegel_orga.html","Vorbereitung öffnen")</x:f>
@@ -6315,13 +6378,13 @@
         <x:v>keiner</x:v>
       </x:c>
       <x:c r="K12" s="60" t="str">
-        <x:v>ph_k7_st08_brechung_und_linsen_licht_andert_die_richtung_in_glas</x:v>
+        <x:v>ph_k7_st08_brechung</x:v>
       </x:c>
       <x:c r="L12" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/006_lichtbrechung.jpg</x:v>
       </x:c>
       <x:c r="M12" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_08_brechung_linsen.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st08_brechung_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N12" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st08_brechung_und_linsen_licht_andert_die_richtung_in_glas_orga.html","Vorbereitung öffnen")</x:f>
@@ -6360,13 +6423,13 @@
         <x:v>keiner</x:v>
       </x:c>
       <x:c r="K13" s="60" t="str">
-        <x:v>ph_k7_st09_warme_und_temperatur_zwei_verschiedene_groen</x:v>
+        <x:v>ph_k7_st09_waerme</x:v>
       </x:c>
       <x:c r="L13" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/026_temperatur_waerme.jpg</x:v>
       </x:c>
       <x:c r="M13" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_09_waerme_temperatur.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st09_waerme_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N13" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st09_warme_und_temperatur_zwei_verschiedene_groen_orga.html","Vorbereitung öffnen")</x:f>
@@ -6405,13 +6468,13 @@
         <x:v>keiner</x:v>
       </x:c>
       <x:c r="K14" s="60" t="str">
-        <x:v>ph_k7_st10_warmeleitung_und_warmestrahlung_wie_warme_sich_ausbreitet</x:v>
+        <x:v>ph_k7_st10_waermeleitung</x:v>
       </x:c>
       <x:c r="L14" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/042_radioaktivitaet.jpg</x:v>
       </x:c>
       <x:c r="M14" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_10_waermeleitung_waermestrahlung.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st10_waermeleitung_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N14" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st10_warmeleitung_und_warmestrahlung_wie_warme_sich_ausbreitet_orga.html","Vorbereitung öffnen")</x:f>
@@ -6450,13 +6513,13 @@
         <x:v>nein</x:v>
       </x:c>
       <x:c r="K15" s="60" t="str">
-        <x:v>ph_k7_st11_der_stromkreis_und_der_schalter</x:v>
+        <x:v>ph_k7_st11_stromkreis</x:v>
       </x:c>
       <x:c r="L15" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/001_stromkreis.jpg</x:v>
       </x:c>
       <x:c r="M15" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_11_stromkreis.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st11_stromkreis_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N15" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st11_der_stromkreis_und_der_schalter_orga.html","Vorbereitung öffnen")</x:f>
@@ -6495,13 +6558,13 @@
         <x:v>nein</x:v>
       </x:c>
       <x:c r="K16" s="60" t="str">
-        <x:v>ph_k7_st12_reihen_und_parallelschaltung</x:v>
+        <x:v>ph_k7_st12_reihen_parallel</x:v>
       </x:c>
       <x:c r="L16" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/012_parallelschaltung.jpg</x:v>
       </x:c>
       <x:c r="M16" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_12_reihen_parallel.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st12_reihen_parallel_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N16" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st12_reihen_und_parallelschaltung_orga.html","Vorbereitung öffnen")</x:f>
@@ -6540,13 +6603,13 @@
         <x:v>nein</x:v>
       </x:c>
       <x:c r="K17" s="60" t="str">
-        <x:v>ph_k7_st13_elektrische_leistung_wie_viel_energie_verbrauchen_gerate</x:v>
+        <x:v>ph_k7_st13_leistung</x:v>
       </x:c>
       <x:c r="L17" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/038_arbeit_leistung.jpg</x:v>
       </x:c>
       <x:c r="M17" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_13_leistung.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st13_leistung_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N17" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st13_elektrische_leistung_wie_viel_energie_verbrauchen_gerate_orga.html","Vorbereitung öffnen")</x:f>
@@ -6585,13 +6648,13 @@
         <x:v>nein</x:v>
       </x:c>
       <x:c r="K18" s="60" t="str">
-        <x:v>ph_k7_st14_sicherheit_im_stromkreis_schutz_vor_uberlastung_und_kurzschluss</x:v>
+        <x:v>ph_k7_st14_sicherheit</x:v>
       </x:c>
       <x:c r="L18" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/001_stromkreis.jpg</x:v>
       </x:c>
       <x:c r="M18" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_14_sicherheit.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st14_sicherheit_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N18" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st14_sicherheit_im_stromkreis_schutz_vor_uberlastung_und_kurzschluss_orga.html","Vorbereitung öffnen")</x:f>
@@ -6630,13 +6693,13 @@
         <x:v>entfällt</x:v>
       </x:c>
       <x:c r="K19" s="60" t="str">
-        <x:v>ph_k7_st19_die_mechanische_arbeit_kraft_mal_weg</x:v>
+        <x:v>ph_k7_st19_mechanische_arbeit</x:v>
       </x:c>
       <x:c r="L19" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/021_kraft_gewicht.jpg</x:v>
       </x:c>
       <x:c r="M19" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_19_mechanische_arbeit.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st19_mechanische_arbeit_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N19" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st19_die_mechanische_arbeit_kraft_mal_weg_orga.html","Vorbereitung öffnen")</x:f>
@@ -6675,13 +6738,13 @@
         <x:v>Automatische Zeitmessung des Hubvorgangs zwischen zwei Höhenschwellen zur Berechnung der Leistung (Lehrerdemonstration)</x:v>
       </x:c>
       <x:c r="K20" s="60" t="str">
-        <x:v>ph_k7_st20_die_leistung_arbeit_pro_zeit</x:v>
+        <x:v>ph_k7_st20_leistung</x:v>
       </x:c>
       <x:c r="L20" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/038_arbeit_leistung.jpg</x:v>
       </x:c>
       <x:c r="M20" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_20_leistung.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st20_leistung_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N20" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st20_die_leistung_arbeit_pro_zeit_orga.html","Vorbereitung öffnen")</x:f>
@@ -6720,13 +6783,13 @@
         <x:v>entfällt</x:v>
       </x:c>
       <x:c r="K21" s="60" t="str">
-        <x:v>ph_k7_st21_energie_und_energieformen_lageenergie_und_bewegungsenergie</x:v>
+        <x:v>ph_k7_st21_energieformen</x:v>
       </x:c>
       <x:c r="L21" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/023_gleichfoermige_bewegung.jpg</x:v>
       </x:c>
       <x:c r="M21" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_21_energieformen.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st21_energieformen_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N21" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st21_energie_und_energieformen_lageenergie_und_bewegungsenergie_orga.html","Vorbereitung öffnen")</x:f>
@@ -6765,13 +6828,13 @@
         <x:v>Helligkeitsmessung zweier Leuchtmittel mit stark unterschiedlicher Leistung bei gleichem Abstand (Lehrerdemonstration)</x:v>
       </x:c>
       <x:c r="K22" s="60" t="str">
-        <x:v>ph_k7_st22_energie_sparen_im_alltag_leuchtmittel_im_vergleich</x:v>
+        <x:v>ph_k7_st22_energiesparen</x:v>
       </x:c>
       <x:c r="L22" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/090_physik_klassenraum.jpg</x:v>
       </x:c>
       <x:c r="M22" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_22_energiesparen.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st22_energiesparen_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N22" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st22_energie_sparen_im_alltag_leuchtmittel_im_vergleich_orga.html","Vorbereitung öffnen")</x:f>
@@ -6810,13 +6873,13 @@
         <x:v>entfällt</x:v>
       </x:c>
       <x:c r="K23" s="60" t="str">
-        <x:v>ph_k7_st23_wiederholung_und_vertiefung_arbeit_leistung_energie</x:v>
+        <x:v>ph_k7_st23_wiederholung</x:v>
       </x:c>
       <x:c r="L23" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/038_arbeit_leistung.jpg</x:v>
       </x:c>
       <x:c r="M23" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_23_wiederholung.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st23_wiederholung_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N23" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st23_wiederholung_und_vertiefung_arbeit_leistung_energie_orga.html","Vorbereitung öffnen")</x:f>
@@ -6855,13 +6918,13 @@
         <x:v>Automatisierte Messung des Wasserstands vor und nach dem Eintauchen eines Körpers zur Bestimmung seines Volumens (Schülerexperiment)</x:v>
       </x:c>
       <x:c r="K24" s="60" t="str">
-        <x:v>ph_k7_st24_masse_volumen_und_dichte</x:v>
+        <x:v>ph_k7_st24_dichte</x:v>
       </x:c>
       <x:c r="L24" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/025_dichte_experiment.jpg</x:v>
       </x:c>
       <x:c r="M24" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_24_dichte.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st24_dichte_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N24" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st24_masse_volumen_und_dichte_orga.html","Vorbereitung öffnen")</x:f>
@@ -6900,17 +6963,302 @@
         <x:v>entfällt</x:v>
       </x:c>
       <x:c r="K25" s="63" t="str">
-        <x:v>ph_k7_st25_auftrieb_warum_schwimmen_manche_dinge</x:v>
+        <x:v>ph_k7_st25_auftrieb</x:v>
       </x:c>
       <x:c r="L25" s="63" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/081_auftrieb.jpg</x:v>
       </x:c>
       <x:c r="M25" s="160" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_25_auftrieb.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st25_auftrieb_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N25" s="161" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st25_auftrieb_warum_schwimmen_manche_dinge_orga.html","Vorbereitung öffnen")</x:f>
       </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="M26" s="51"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="M27" s="51"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="M28" s="51"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="M29" s="51"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="M30" s="51"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="M31" s="51"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="M32" s="51"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="M33" s="51"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="M34" s="51"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="M35" s="51"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="M36" s="51"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="M37" s="51"/>
+    </x:row>
+    <x:row r="38">
+      <x:c r="M38" s="51"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="M39" s="51"/>
+    </x:row>
+    <x:row r="40">
+      <x:c r="M40" s="51"/>
+    </x:row>
+    <x:row r="41">
+      <x:c r="M41" s="51"/>
+    </x:row>
+    <x:row r="42">
+      <x:c r="M42" s="51"/>
+    </x:row>
+    <x:row r="43">
+      <x:c r="M43" s="51"/>
+    </x:row>
+    <x:row r="44">
+      <x:c r="M44" s="51"/>
+    </x:row>
+    <x:row r="45">
+      <x:c r="M45" s="51"/>
+    </x:row>
+    <x:row r="46">
+      <x:c r="M46" s="51"/>
+    </x:row>
+    <x:row r="47">
+      <x:c r="M47" s="51"/>
+    </x:row>
+    <x:row r="48">
+      <x:c r="M48" s="51"/>
+    </x:row>
+    <x:row r="49">
+      <x:c r="M49" s="51"/>
+    </x:row>
+    <x:row r="50">
+      <x:c r="M50" s="51"/>
+    </x:row>
+    <x:row r="51">
+      <x:c r="M51" s="51"/>
+    </x:row>
+    <x:row r="52">
+      <x:c r="M52" s="51"/>
+    </x:row>
+    <x:row r="53">
+      <x:c r="M53" s="51"/>
+    </x:row>
+    <x:row r="54">
+      <x:c r="M54" s="51"/>
+    </x:row>
+    <x:row r="55">
+      <x:c r="M55" s="51"/>
+    </x:row>
+    <x:row r="56">
+      <x:c r="M56" s="51"/>
+    </x:row>
+    <x:row r="57">
+      <x:c r="M57" s="51"/>
+    </x:row>
+    <x:row r="58">
+      <x:c r="M58" s="51"/>
+    </x:row>
+    <x:row r="59">
+      <x:c r="M59" s="51"/>
+    </x:row>
+    <x:row r="60">
+      <x:c r="M60" s="51"/>
+    </x:row>
+    <x:row r="61">
+      <x:c r="M61" s="51"/>
+    </x:row>
+    <x:row r="62">
+      <x:c r="M62" s="51"/>
+    </x:row>
+    <x:row r="63">
+      <x:c r="M63" s="51"/>
+    </x:row>
+    <x:row r="64">
+      <x:c r="M64" s="51"/>
+    </x:row>
+    <x:row r="65">
+      <x:c r="M65" s="51"/>
+    </x:row>
+    <x:row r="66">
+      <x:c r="M66" s="51"/>
+    </x:row>
+    <x:row r="67">
+      <x:c r="M67" s="51"/>
+    </x:row>
+    <x:row r="68">
+      <x:c r="M68" s="51"/>
+    </x:row>
+    <x:row r="69">
+      <x:c r="M69" s="51"/>
+    </x:row>
+    <x:row r="70">
+      <x:c r="M70" s="51"/>
+    </x:row>
+    <x:row r="71">
+      <x:c r="M71" s="51"/>
+    </x:row>
+    <x:row r="72">
+      <x:c r="M72" s="51"/>
+    </x:row>
+    <x:row r="73">
+      <x:c r="M73" s="51"/>
+    </x:row>
+    <x:row r="74">
+      <x:c r="M74" s="51"/>
+    </x:row>
+    <x:row r="75">
+      <x:c r="M75" s="51"/>
+    </x:row>
+    <x:row r="76">
+      <x:c r="M76" s="51"/>
+    </x:row>
+    <x:row r="77">
+      <x:c r="M77" s="51"/>
+    </x:row>
+    <x:row r="78">
+      <x:c r="M78" s="51"/>
+    </x:row>
+    <x:row r="79">
+      <x:c r="M79" s="51"/>
+    </x:row>
+    <x:row r="80">
+      <x:c r="M80" s="51"/>
+    </x:row>
+    <x:row r="81">
+      <x:c r="M81" s="51"/>
+    </x:row>
+    <x:row r="82">
+      <x:c r="M82" s="51"/>
+    </x:row>
+    <x:row r="83">
+      <x:c r="M83" s="51"/>
+    </x:row>
+    <x:row r="84">
+      <x:c r="M84" s="51"/>
+    </x:row>
+    <x:row r="85">
+      <x:c r="M85" s="51"/>
+    </x:row>
+    <x:row r="86">
+      <x:c r="M86" s="51"/>
+    </x:row>
+    <x:row r="87">
+      <x:c r="M87" s="51"/>
+    </x:row>
+    <x:row r="88">
+      <x:c r="M88" s="51"/>
+    </x:row>
+    <x:row r="89">
+      <x:c r="M89" s="51"/>
+    </x:row>
+    <x:row r="90">
+      <x:c r="M90" s="51"/>
+    </x:row>
+    <x:row r="91">
+      <x:c r="M91" s="51"/>
+    </x:row>
+    <x:row r="92">
+      <x:c r="M92" s="51"/>
+    </x:row>
+    <x:row r="93">
+      <x:c r="M93" s="51"/>
+    </x:row>
+    <x:row r="94">
+      <x:c r="M94" s="51"/>
+    </x:row>
+    <x:row r="95">
+      <x:c r="M95" s="51"/>
+    </x:row>
+    <x:row r="96">
+      <x:c r="M96" s="51"/>
+    </x:row>
+    <x:row r="97">
+      <x:c r="M97" s="51"/>
+    </x:row>
+    <x:row r="98">
+      <x:c r="M98" s="51"/>
+    </x:row>
+    <x:row r="99">
+      <x:c r="M99" s="51"/>
+    </x:row>
+    <x:row r="100">
+      <x:c r="M100" s="51"/>
+    </x:row>
+    <x:row r="101">
+      <x:c r="M101" s="51"/>
+    </x:row>
+    <x:row r="102">
+      <x:c r="M102" s="51"/>
+    </x:row>
+    <x:row r="103">
+      <x:c r="M103" s="51"/>
+    </x:row>
+    <x:row r="104">
+      <x:c r="M104" s="51"/>
+    </x:row>
+    <x:row r="105">
+      <x:c r="M105" s="51"/>
+    </x:row>
+    <x:row r="106">
+      <x:c r="M106" s="51"/>
+    </x:row>
+    <x:row r="107">
+      <x:c r="M107" s="51"/>
+    </x:row>
+    <x:row r="108">
+      <x:c r="M108" s="51"/>
+    </x:row>
+    <x:row r="109">
+      <x:c r="M109" s="51"/>
+    </x:row>
+    <x:row r="110">
+      <x:c r="M110" s="51"/>
+    </x:row>
+    <x:row r="111">
+      <x:c r="M111" s="51"/>
+    </x:row>
+    <x:row r="112">
+      <x:c r="M112" s="51"/>
+    </x:row>
+    <x:row r="113">
+      <x:c r="M113" s="51"/>
+    </x:row>
+    <x:row r="114">
+      <x:c r="M114" s="51"/>
+    </x:row>
+    <x:row r="115">
+      <x:c r="M115" s="51"/>
+    </x:row>
+    <x:row r="116">
+      <x:c r="M116" s="51"/>
+    </x:row>
+    <x:row r="117">
+      <x:c r="M117" s="51"/>
+    </x:row>
+    <x:row r="118">
+      <x:c r="M118" s="51"/>
+    </x:row>
+    <x:row r="119">
+      <x:c r="M119" s="51"/>
+    </x:row>
+    <x:row r="120">
+      <x:c r="M120" s="51"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -6919,7 +7267,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R88382ea432784924"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R59022c507f2747c1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7057,13 +7405,13 @@
         <x:v>entfällt</x:v>
       </x:c>
       <x:c r="K5" s="57" t="str">
-        <x:v>ph_k8_st01_geschwindigkeit_was_bedeutet_schnell</x:v>
+        <x:v>ph_k8_st01_geschwindigkeit</x:v>
       </x:c>
       <x:c r="L5" s="57" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/023_gleichfoermige_bewegung.jpg</x:v>
       </x:c>
       <x:c r="M5" s="156" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_01_geschwindigkeit.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st01_geschwindigkeit_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N5" s="157" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st01_geschwindigkeit_was_bedeutet_schnell_orga.html","Vorbereitung öffnen")</x:f>
@@ -7102,13 +7450,13 @@
         <x:v>Fortlaufende Positionsmessung eines Wagens zur Erstellung eines Weg-Zeit-Diagramms (Lehrerdemonstration)</x:v>
       </x:c>
       <x:c r="K6" s="60" t="str">
-        <x:v>ph_k8_st02_bewegungsarten_und_das_weg_zeit_diagramm</x:v>
+        <x:v>ph_k8_st02_weg_zeit_diagramm</x:v>
       </x:c>
       <x:c r="L6" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/023_gleichfoermige_bewegung.jpg</x:v>
       </x:c>
       <x:c r="M6" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_02_weg_zeit_diagramm.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st02_weg_zeit_diagramm_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N6" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st02_bewegungsarten_und_das_weg_zeit_diagramm_orga.html","Vorbereitung öffnen")</x:f>
@@ -7147,13 +7495,13 @@
         <x:v>entfällt</x:v>
       </x:c>
       <x:c r="K7" s="60" t="str">
-        <x:v>ph_k8_st03_durchschnitts_und_momentangeschwindigkeit</x:v>
+        <x:v>ph_k8_st03_durchschnitt_moment</x:v>
       </x:c>
       <x:c r="L7" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/023_gleichfoermige_bewegung.jpg</x:v>
       </x:c>
       <x:c r="M7" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_03_durchschnitt_moment.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st03_durchschnitt_moment_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N7" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st03_durchschnitts_und_momentangeschwindigkeit_orga.html","Vorbereitung öffnen")</x:f>
@@ -7192,13 +7540,13 @@
         <x:v>Fortlaufende Positionsmessung zur Berechnung der Geschwindigkeitszunahme und daraus der Beschleunigung (Schülerexperiment)</x:v>
       </x:c>
       <x:c r="K8" s="60" t="str">
-        <x:v>ph_k8_st04_beschleunigung_wenn_sich_die_geschwindigkeit_andert</x:v>
+        <x:v>ph_k8_st04_beschleunigung</x:v>
       </x:c>
       <x:c r="L8" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/092_beschleunigung.jpg</x:v>
       </x:c>
       <x:c r="M8" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_04_beschleunigung.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st04_beschleunigung_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N8" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st04_beschleunigung_wenn_sich_die_geschwindigkeit_andert_orga.html","Vorbereitung öffnen")</x:f>
@@ -7243,7 +7591,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/097_formeln_uebersicht.jpg</x:v>
       </x:c>
       <x:c r="M9" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_09_wiederholung_dynamik.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st09_wiederholung_dynamik_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N9" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st09_wiederholung_dynamik_orga.html","Vorbereitung öffnen")</x:f>
@@ -7282,13 +7630,13 @@
         <x:v>Automatisierte Temperaturaufzeichnung beim Erhitzen von Eis bis zum Sieden zur Erstellung einer Erhitzungskurve (Lehrerdemonstration)</x:v>
       </x:c>
       <x:c r="K10" s="60" t="str">
-        <x:v>ph_k8_st10_aggregatzustande</x:v>
+        <x:v>ph_k8_st10_aggregatzustaende</x:v>
       </x:c>
       <x:c r="L10" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/026_temperatur_waerme.jpg</x:v>
       </x:c>
       <x:c r="M10" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_10_aggregatzustaende.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st10_aggregatzustaende_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N10" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st10_aggregatzustande_orga.html","Vorbereitung öffnen")</x:f>
@@ -7327,13 +7675,13 @@
         <x:v>entfällt</x:v>
       </x:c>
       <x:c r="K11" s="60" t="str">
-        <x:v>ph_k8_st11_warmeausdehnung</x:v>
+        <x:v>ph_k8_st11_waermeausdehnung</x:v>
       </x:c>
       <x:c r="L11" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/026_temperatur_waerme.jpg</x:v>
       </x:c>
       <x:c r="M11" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_11_waermeausdehnung.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st11_waermeausdehnung_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N11" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st11_warmeausdehnung_orga.html","Vorbereitung öffnen")</x:f>
@@ -7372,13 +7720,13 @@
         <x:v>Gleichzeitige, automatisierte Temperaturmessung zweier Stoffe zur Bestimmung der unterschiedlichen spezifischen Wärmekapazität (Schülerexperiment)</x:v>
       </x:c>
       <x:c r="K12" s="60" t="str">
-        <x:v>ph_k8_st12_warmemenge_und_spezifische_warmekapazitat</x:v>
+        <x:v>ph_k8_st12_waermekapazitaet</x:v>
       </x:c>
       <x:c r="L12" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/026_temperatur_waerme.jpg</x:v>
       </x:c>
       <x:c r="M12" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_12_waermekapazitaet.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st12_waermekapazitaet_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N12" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st12_warmemenge_und_spezifische_warmekapazitat_orga.html","Vorbereitung öffnen")</x:f>
@@ -7423,7 +7771,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/090_physik_klassenraum.jpg</x:v>
       </x:c>
       <x:c r="M13" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_17_magnetismus.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st17_magnetismus_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N13" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st17_magnetismus_orga.html","Vorbereitung öffnen")</x:f>
@@ -7468,7 +7816,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/018_kompass_erdmagnetfeld.jpg</x:v>
       </x:c>
       <x:c r="M14" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_18_kompass.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st18_kompass_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N14" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st18_kompass_orga.html","Vorbereitung öffnen")</x:f>
@@ -7513,7 +7861,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/019_elektromagnet.jpg</x:v>
       </x:c>
       <x:c r="M15" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_19_elektromagnet.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st19_elektromagnet_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N15" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st19_elektromagnet_orga.html","Vorbereitung öffnen")</x:f>
@@ -7558,7 +7906,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/043_induktion.jpg</x:v>
       </x:c>
       <x:c r="M16" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_20_induktion.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st20_induktion_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N16" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st20_induktion_orga.html","Vorbereitung öffnen")</x:f>
@@ -7603,7 +7951,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/097_formeln_uebersicht.jpg</x:v>
       </x:c>
       <x:c r="M17" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_21_wiederholung_magnetismus.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st21_wiederholung_magnetismus_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N17" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st21_wiederholung_magnetismus_orga.html","Vorbereitung öffnen")</x:f>
@@ -7648,7 +7996,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/005_tafelbild_ohm.jpg</x:v>
       </x:c>
       <x:c r="M18" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_22_ohmsches_gesetz.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st22_ohmsches_gesetz_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N18" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st22_ohmsches_gesetz_orga.html","Vorbereitung öffnen")</x:f>
@@ -7693,7 +8041,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/090_physik_klassenraum.jpg</x:v>
       </x:c>
       <x:c r="M19" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_23_reihe_parallel.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st23_reihe_parallel_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N19" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st23_reihe_parallel_orga.html","Vorbereitung öffnen")</x:f>
@@ -7738,7 +8086,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/038_arbeit_leistung.jpg</x:v>
       </x:c>
       <x:c r="M20" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_24_leistung.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st24_leistung_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N20" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st24_leistung_orga.html","Vorbereitung öffnen")</x:f>
@@ -7783,7 +8131,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/097_formeln_uebersicht.jpg</x:v>
       </x:c>
       <x:c r="M21" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_25_wiederholung_elektrizitaet.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st25_wiederholung_elektrizitaet_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N21" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st25_wiederholung_elektrizitaet_orga.html","Vorbereitung öffnen")</x:f>
@@ -7828,7 +8176,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/006_lichtbrechung.jpg</x:v>
       </x:c>
       <x:c r="M22" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_26_lichtbrechung.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st26_lichtbrechung_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N22" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st26_lichtbrechung_orga.html","Vorbereitung öffnen")</x:f>
@@ -7873,7 +8221,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/093_optische_instrumente.jpg</x:v>
       </x:c>
       <x:c r="M23" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_27_linsen.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st27_linsen_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N23" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st27_linsen_orga.html","Vorbereitung öffnen")</x:f>
@@ -7918,7 +8266,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/093_optische_instrumente.jpg</x:v>
       </x:c>
       <x:c r="M24" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_28_auge.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st28_auge_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N24" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st28_auge_orga.html","Vorbereitung öffnen")</x:f>
@@ -7963,7 +8311,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/097_formeln_uebersicht.jpg</x:v>
       </x:c>
       <x:c r="M25" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_29_wiederholung_optik_vertieft.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st29_wiederholung_optik_vertieft_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N25" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st29_wiederholung_optik_vertieft_orga.html","Vorbereitung öffnen")</x:f>
@@ -8008,11 +8356,293 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/097_formeln_uebersicht.jpg</x:v>
       </x:c>
       <x:c r="M26" s="160" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_30_gesamtwiederholung_klasse_8.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st30_gesamtwiederholung_klasse_8_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N26" s="161" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st30_gesamtwiederholung_klasse_8_orga.html","Vorbereitung öffnen")</x:f>
       </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="M27" s="51"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="M28" s="51"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="M29" s="51"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="M30" s="51"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="M31" s="51"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="M32" s="51"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="M33" s="51"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="M34" s="51"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="M35" s="51"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="M36" s="51"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="M37" s="51"/>
+    </x:row>
+    <x:row r="38">
+      <x:c r="M38" s="51"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="M39" s="51"/>
+    </x:row>
+    <x:row r="40">
+      <x:c r="M40" s="51"/>
+    </x:row>
+    <x:row r="41">
+      <x:c r="M41" s="51"/>
+    </x:row>
+    <x:row r="42">
+      <x:c r="M42" s="51"/>
+    </x:row>
+    <x:row r="43">
+      <x:c r="M43" s="51"/>
+    </x:row>
+    <x:row r="44">
+      <x:c r="M44" s="51"/>
+    </x:row>
+    <x:row r="45">
+      <x:c r="M45" s="51"/>
+    </x:row>
+    <x:row r="46">
+      <x:c r="M46" s="51"/>
+    </x:row>
+    <x:row r="47">
+      <x:c r="M47" s="51"/>
+    </x:row>
+    <x:row r="48">
+      <x:c r="M48" s="51"/>
+    </x:row>
+    <x:row r="49">
+      <x:c r="M49" s="51"/>
+    </x:row>
+    <x:row r="50">
+      <x:c r="M50" s="51"/>
+    </x:row>
+    <x:row r="51">
+      <x:c r="M51" s="51"/>
+    </x:row>
+    <x:row r="52">
+      <x:c r="M52" s="51"/>
+    </x:row>
+    <x:row r="53">
+      <x:c r="M53" s="51"/>
+    </x:row>
+    <x:row r="54">
+      <x:c r="M54" s="51"/>
+    </x:row>
+    <x:row r="55">
+      <x:c r="M55" s="51"/>
+    </x:row>
+    <x:row r="56">
+      <x:c r="M56" s="51"/>
+    </x:row>
+    <x:row r="57">
+      <x:c r="M57" s="51"/>
+    </x:row>
+    <x:row r="58">
+      <x:c r="M58" s="51"/>
+    </x:row>
+    <x:row r="59">
+      <x:c r="M59" s="51"/>
+    </x:row>
+    <x:row r="60">
+      <x:c r="M60" s="51"/>
+    </x:row>
+    <x:row r="61">
+      <x:c r="M61" s="51"/>
+    </x:row>
+    <x:row r="62">
+      <x:c r="M62" s="51"/>
+    </x:row>
+    <x:row r="63">
+      <x:c r="M63" s="51"/>
+    </x:row>
+    <x:row r="64">
+      <x:c r="M64" s="51"/>
+    </x:row>
+    <x:row r="65">
+      <x:c r="M65" s="51"/>
+    </x:row>
+    <x:row r="66">
+      <x:c r="M66" s="51"/>
+    </x:row>
+    <x:row r="67">
+      <x:c r="M67" s="51"/>
+    </x:row>
+    <x:row r="68">
+      <x:c r="M68" s="51"/>
+    </x:row>
+    <x:row r="69">
+      <x:c r="M69" s="51"/>
+    </x:row>
+    <x:row r="70">
+      <x:c r="M70" s="51"/>
+    </x:row>
+    <x:row r="71">
+      <x:c r="M71" s="51"/>
+    </x:row>
+    <x:row r="72">
+      <x:c r="M72" s="51"/>
+    </x:row>
+    <x:row r="73">
+      <x:c r="M73" s="51"/>
+    </x:row>
+    <x:row r="74">
+      <x:c r="M74" s="51"/>
+    </x:row>
+    <x:row r="75">
+      <x:c r="M75" s="51"/>
+    </x:row>
+    <x:row r="76">
+      <x:c r="M76" s="51"/>
+    </x:row>
+    <x:row r="77">
+      <x:c r="M77" s="51"/>
+    </x:row>
+    <x:row r="78">
+      <x:c r="M78" s="51"/>
+    </x:row>
+    <x:row r="79">
+      <x:c r="M79" s="51"/>
+    </x:row>
+    <x:row r="80">
+      <x:c r="M80" s="51"/>
+    </x:row>
+    <x:row r="81">
+      <x:c r="M81" s="51"/>
+    </x:row>
+    <x:row r="82">
+      <x:c r="M82" s="51"/>
+    </x:row>
+    <x:row r="83">
+      <x:c r="M83" s="51"/>
+    </x:row>
+    <x:row r="84">
+      <x:c r="M84" s="51"/>
+    </x:row>
+    <x:row r="85">
+      <x:c r="M85" s="51"/>
+    </x:row>
+    <x:row r="86">
+      <x:c r="M86" s="51"/>
+    </x:row>
+    <x:row r="87">
+      <x:c r="M87" s="51"/>
+    </x:row>
+    <x:row r="88">
+      <x:c r="M88" s="51"/>
+    </x:row>
+    <x:row r="89">
+      <x:c r="M89" s="51"/>
+    </x:row>
+    <x:row r="90">
+      <x:c r="M90" s="51"/>
+    </x:row>
+    <x:row r="91">
+      <x:c r="M91" s="51"/>
+    </x:row>
+    <x:row r="92">
+      <x:c r="M92" s="51"/>
+    </x:row>
+    <x:row r="93">
+      <x:c r="M93" s="51"/>
+    </x:row>
+    <x:row r="94">
+      <x:c r="M94" s="51"/>
+    </x:row>
+    <x:row r="95">
+      <x:c r="M95" s="51"/>
+    </x:row>
+    <x:row r="96">
+      <x:c r="M96" s="51"/>
+    </x:row>
+    <x:row r="97">
+      <x:c r="M97" s="51"/>
+    </x:row>
+    <x:row r="98">
+      <x:c r="M98" s="51"/>
+    </x:row>
+    <x:row r="99">
+      <x:c r="M99" s="51"/>
+    </x:row>
+    <x:row r="100">
+      <x:c r="M100" s="51"/>
+    </x:row>
+    <x:row r="101">
+      <x:c r="M101" s="51"/>
+    </x:row>
+    <x:row r="102">
+      <x:c r="M102" s="51"/>
+    </x:row>
+    <x:row r="103">
+      <x:c r="M103" s="51"/>
+    </x:row>
+    <x:row r="104">
+      <x:c r="M104" s="51"/>
+    </x:row>
+    <x:row r="105">
+      <x:c r="M105" s="51"/>
+    </x:row>
+    <x:row r="106">
+      <x:c r="M106" s="51"/>
+    </x:row>
+    <x:row r="107">
+      <x:c r="M107" s="51"/>
+    </x:row>
+    <x:row r="108">
+      <x:c r="M108" s="51"/>
+    </x:row>
+    <x:row r="109">
+      <x:c r="M109" s="51"/>
+    </x:row>
+    <x:row r="110">
+      <x:c r="M110" s="51"/>
+    </x:row>
+    <x:row r="111">
+      <x:c r="M111" s="51"/>
+    </x:row>
+    <x:row r="112">
+      <x:c r="M112" s="51"/>
+    </x:row>
+    <x:row r="113">
+      <x:c r="M113" s="51"/>
+    </x:row>
+    <x:row r="114">
+      <x:c r="M114" s="51"/>
+    </x:row>
+    <x:row r="115">
+      <x:c r="M115" s="51"/>
+    </x:row>
+    <x:row r="116">
+      <x:c r="M116" s="51"/>
+    </x:row>
+    <x:row r="117">
+      <x:c r="M117" s="51"/>
+    </x:row>
+    <x:row r="118">
+      <x:c r="M118" s="51"/>
+    </x:row>
+    <x:row r="119">
+      <x:c r="M119" s="51"/>
+    </x:row>
+    <x:row r="120">
+      <x:c r="M120" s="51"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -8021,7 +8651,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb450b11738dc4ca6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfaa4e41eff2c431a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8165,7 +8795,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/017_magnet_feldlinien.jpg</x:v>
       </x:c>
       <x:c r="M5" s="156" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_01_magnetische_pole_und_kraftwirkungen.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st01_magnetische_pole_und_kraftwirkungen_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N5" s="157" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st01_magnetische_pole_und_kraftwirkungen_orga.html","Vorbereitung öffnen")</x:f>
@@ -8210,7 +8840,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/017_magnet_feldlinien.jpg</x:v>
       </x:c>
       <x:c r="M6" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_02_magnetfeld_und_feldlinienmodell.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st02_magnetfeld_und_feldlinienmodell_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N6" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st02_magnetfeld_und_feldlinienmodell_orga.html","Vorbereitung öffnen")</x:f>
@@ -8255,7 +8885,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/018_kompass_erdmagnetfeld.jpg</x:v>
       </x:c>
       <x:c r="M7" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_03_erdmagnetfeld_und_kompass.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st03_erdmagnetfeld_und_kompass_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N7" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st03_erdmagnetfeld_und_kompass_orga.html","Vorbereitung öffnen")</x:f>
@@ -8300,7 +8930,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/090_physik_klassenraum.jpg</x:v>
       </x:c>
       <x:c r="M8" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_04_elektrisches_und_magnetisches_feld_vergleichen.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st04_elektrisches_und_magnetisches_feld_vergleichen_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N8" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st04_elektrisches_und_magnetisches_feld_vergleichen_orga.html","Vorbereitung öffnen")</x:f>
@@ -8345,7 +8975,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/019_elektromagnet.jpg</x:v>
       </x:c>
       <x:c r="M9" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_05_elektromagnet_aufbau_und_wirkungsweise.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st05_elektromagnet_aufbau_und_wirkungsweise_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N9" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st05_elektromagnet_aufbau_und_wirkungsweise_orga.html","Vorbereitung öffnen")</x:f>
@@ -8384,13 +9014,13 @@
         <x:v>PWM-Stufen und Hall-Sensor zur relativen Feldmessung nutzen</x:v>
       </x:c>
       <x:c r="K10" s="60" t="str">
-        <x:v>ph_k9_st06_starke_eines_elektromagneten_untersuchen</x:v>
+        <x:v>ph_k9_st06_staerke_eines_elektromagneten_untersuchen</x:v>
       </x:c>
       <x:c r="L10" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/019_elektromagnet.jpg</x:v>
       </x:c>
       <x:c r="M10" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_06_staerke_eines_elektromagneten_untersuchen.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st06_staerke_eines_elektromagneten_untersuchen_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N10" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st06_starke_eines_elektromagneten_untersuchen_orga.html","Vorbereitung öffnen")</x:f>
@@ -8435,7 +9065,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/017_magnet_feldlinien.jpg</x:v>
       </x:c>
       <x:c r="M11" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_07_kraft_auf_einen_stromdurchflossenen_leiter_im_magnetfeld.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st07_kraft_auf_einen_stromdurchflossenen_leiter_im_magnetfeld_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N11" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st07_kraft_auf_einen_stromdurchflossenen_leiter_im_magnetfeld_orga.html","Vorbereitung öffnen")</x:f>
@@ -8480,7 +9110,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/044_generator_motor.jpg</x:v>
       </x:c>
       <x:c r="M12" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_08_elektromotor_elektrische_energie_erzeugt_bewegung.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st08_elektromotor_elektrische_energie_erzeugt_bewegung_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N12" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st08_elektromotor_elektrische_energie_erzeugt_bewegung_orga.html","Vorbereitung öffnen")</x:f>
@@ -8519,13 +9149,13 @@
         <x:v>Relaismodul mit Taster und Status-LED steuern</x:v>
       </x:c>
       <x:c r="K13" s="60" t="str">
-        <x:v>ph_k9_st09_relais_und_elektromagnetischer_turoffner</x:v>
+        <x:v>ph_k9_st09_relais_und_elektromagnetischer_tueroeffner</x:v>
       </x:c>
       <x:c r="L13" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/044_generator_motor.jpg</x:v>
       </x:c>
       <x:c r="M13" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_09_relais_und_elektromagnetischer_tueroeffner.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st09_relais_und_elektromagnetischer_tueroeffner_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N13" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st09_relais_und_elektromagnetischer_turoffner_orga.html","Vorbereitung öffnen")</x:f>
@@ -8570,7 +9200,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/044_generator_motor.jpg</x:v>
       </x:c>
       <x:c r="M14" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_10_lautsprecher_und_anwendungen_des_elektromagnetismus.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st10_lautsprecher_und_anwendungen_des_elektromagnetismus_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N14" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st10_lautsprecher_und_anwendungen_des_elektromagnetismus_orga.html","Vorbereitung öffnen")</x:f>
@@ -8615,7 +9245,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/023_gleichfoermige_bewegung.jpg</x:v>
       </x:c>
       <x:c r="M15" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_11_bewegung_bezugssystem_weg_und_zeit.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st11_bewegung_bezugssystem_weg_und_zeit_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N15" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st11_bewegung_bezugssystem_weg_und_zeit_orga.html","Vorbereitung öffnen")</x:f>
@@ -8660,7 +9290,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/023_gleichfoermige_bewegung.jpg</x:v>
       </x:c>
       <x:c r="M16" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_12_geschwindigkeit_messen_und_berechnen.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st12_geschwindigkeit_messen_und_berechnen_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N16" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st12_geschwindigkeit_messen_und_berechnen_orga.html","Vorbereitung öffnen")</x:f>
@@ -8699,13 +9329,13 @@
         <x:v>Weg-Zeit-Daten mit HC-SR04 protokollieren</x:v>
       </x:c>
       <x:c r="K17" s="60" t="str">
-        <x:v>ph_k9_st13_geradlinig_gleichformige_bewegung_und_s_t_diagramm</x:v>
+        <x:v>ph_k9_st13_geradlinig_gleichfoermige_bewegung_und_s_t_diagramm</x:v>
       </x:c>
       <x:c r="L17" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/023_gleichfoermige_bewegung.jpg</x:v>
       </x:c>
       <x:c r="M17" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_13_geradlinig_gleichfoermige_bewegung_und_s_t_diagramm.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st13_geradlinig_gleichfoermige_bewegung_und_s_t_diagramm_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N17" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st13_geradlinig_gleichformige_bewegung_und_s_t_diagramm_orga.html","Vorbereitung öffnen")</x:f>
@@ -8744,13 +9374,13 @@
         <x:v>—</x:v>
       </x:c>
       <x:c r="K18" s="60" t="str">
-        <x:v>ph_k9_st14_gleichformige_bewegung_gleichungen_und_diagramme_anwenden</x:v>
+        <x:v>ph_k9_st14_gleichfoermige_bewegung_gleichungen_und_diagramme_anwenden</x:v>
       </x:c>
       <x:c r="L18" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/023_gleichfoermige_bewegung.jpg</x:v>
       </x:c>
       <x:c r="M18" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_14_gleichfoermige_bewegung_gleichungen_und_diagramme_anwenden.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st14_gleichfoermige_bewegung_gleichungen_und_diagramme_anwenden_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N18" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st14_gleichformige_bewegung_gleichungen_und_diagramme_anwenden_orga.html","Vorbereitung öffnen")</x:f>
@@ -8789,13 +9419,13 @@
         <x:v>Beschleunigungswerte mit MPU6050 als Rohdaten erfassen</x:v>
       </x:c>
       <x:c r="K19" s="60" t="str">
-        <x:v>ph_k9_st15_beschleunigung_als_anderung_der_geschwindigkeit</x:v>
+        <x:v>ph_k9_st15_beschleunigung_als_aenderung_der_geschwindigkeit</x:v>
       </x:c>
       <x:c r="L19" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/092_beschleunigung.jpg</x:v>
       </x:c>
       <x:c r="M19" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_15_beschleunigung_als_aenderung_der_geschwindigkeit.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st15_beschleunigung_als_aenderung_der_geschwindigkeit_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N19" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st15_beschleunigung_als_anderung_der_geschwindigkeit_orga.html","Vorbereitung öffnen")</x:f>
@@ -8834,13 +9464,13 @@
         <x:v>Beschleunigungsdaten mit MPU6050 aufzeichnen und mitteln</x:v>
       </x:c>
       <x:c r="K20" s="60" t="str">
-        <x:v>ph_k9_st16_geradlinig_gleichmaig_beschleunigte_bewegung</x:v>
+        <x:v>ph_k9_st16_geradlinig_gleichmaessig_beschleunigte_bewegung</x:v>
       </x:c>
       <x:c r="L20" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/023_gleichfoermige_bewegung.jpg</x:v>
       </x:c>
       <x:c r="M20" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_16_geradlinig_gleichmaessig_beschleunigte_bewegung.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st16_geradlinig_gleichmaessig_beschleunigte_bewegung_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N20" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st16_geradlinig_gleichmaig_beschleunigte_bewegung_orga.html","Vorbereitung öffnen")</x:f>
@@ -8885,7 +9515,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/092_beschleunigung.jpg</x:v>
       </x:c>
       <x:c r="M21" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_17_freier_fall_als_beschleunigte_bewegung.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st17_freier_fall_als_beschleunigte_bewegung_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N21" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st17_freier_fall_als_beschleunigte_bewegung_orga.html","Vorbereitung öffnen")</x:f>
@@ -8930,7 +9560,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/023_gleichfoermige_bewegung.jpg</x:v>
       </x:c>
       <x:c r="M22" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_18_bewegungsformen_bewegungsarten_und_verkehrssicherheit.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st18_bewegungsformen_bewegungsarten_und_verkehrssicherheit_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N22" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st18_bewegungsformen_bewegungsarten_und_verkehrssicherheit_orga.html","Vorbereitung öffnen")</x:f>
@@ -8969,13 +9599,13 @@
         <x:v>Kraft mit Wägezelle und HX711 nach Kalibrierung messen</x:v>
       </x:c>
       <x:c r="K23" s="60" t="str">
-        <x:v>ph_k9_st19_kraft_als_wechselwirkung_und_physikalische_groe</x:v>
+        <x:v>ph_k9_st19_kraft_als_wechselwirkung_und_physikalische_groesse</x:v>
       </x:c>
       <x:c r="L23" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/024_newton_krafte.jpg</x:v>
       </x:c>
       <x:c r="M23" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_19_kraft_als_wechselwirkung_und_physikalische_groesse.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st19_kraft_als_wechselwirkung_und_physikalische_groesse_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N23" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st19_kraft_als_wechselwirkung_und_physikalische_groe_orga.html","Vorbereitung öffnen")</x:f>
@@ -9014,13 +9644,13 @@
         <x:v>—</x:v>
       </x:c>
       <x:c r="K24" s="60" t="str">
-        <x:v>ph_k9_st20_erstes_newtonsches_gesetz_tragheit</x:v>
+        <x:v>ph_k9_st20_erstes_newtonsches_gesetz_traegheit</x:v>
       </x:c>
       <x:c r="L24" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/024_newton_krafte.jpg</x:v>
       </x:c>
       <x:c r="M24" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_20_erstes_newtonsches_gesetz_traegheit.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st20_erstes_newtonsches_gesetz_traegheit_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N24" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st20_erstes_newtonsches_gesetz_tragheit_orga.html","Vorbereitung öffnen")</x:f>
@@ -9065,7 +9695,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/092_beschleunigung.jpg</x:v>
       </x:c>
       <x:c r="M25" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_21_zweites_newtonsches_gesetz_kraft_masse_und_beschleunigung.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st21_zweites_newtonsches_gesetz_kraft_masse_und_beschleunigung_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N25" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st21_zweites_newtonsches_gesetz_kraft_masse_und_beschleunigung_orga.html","Vorbereitung öffnen")</x:f>
@@ -9110,7 +9740,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/024_newton_krafte.jpg</x:v>
       </x:c>
       <x:c r="M26" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_22_drittes_newtonsches_gesetz_actio_und_reactio.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st22_drittes_newtonsches_gesetz_actio_und_reactio_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N26" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st22_drittes_newtonsches_gesetz_actio_und_reactio_orga.html","Vorbereitung öffnen")</x:f>
@@ -9155,7 +9785,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/091_gravitation.jpg</x:v>
       </x:c>
       <x:c r="M27" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_23_gravitation_masse_und_gewichtskraft.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st23_gravitation_masse_und_gewichtskraft_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N27" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st23_gravitation_masse_und_gewichtskraft_orga.html","Vorbereitung öffnen")</x:f>
@@ -9194,17 +9824,293 @@
         <x:v>Wahlstationen mit Ultraschall, Lichtschranke oder Wägezelle</x:v>
       </x:c>
       <x:c r="K28" s="63" t="str">
-        <x:v>ph_k9_st24_projekt_und_lernkontrolle_bewegungen_und_krafte_im_alltag</x:v>
+        <x:v>ph_k9_st24_projekt_und_lernkontrolle_bewegungen_und_kraefte_im_alltag</x:v>
       </x:c>
       <x:c r="L28" s="63" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/023_gleichfoermige_bewegung.jpg</x:v>
       </x:c>
       <x:c r="M28" s="160" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_24_projekt_und_lernkontrolle_bewegungen_und_kraefte_im_alltag.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st24_projekt_und_lernkontrolle_bewegungen_und_kraefte_im_alltag_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N28" s="161" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st24_projekt_und_lernkontrolle_bewegungen_und_krafte_im_alltag_orga.html","Vorbereitung öffnen")</x:f>
       </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="M29" s="51"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="M30" s="51"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="M31" s="51"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="M32" s="51"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="M33" s="51"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="M34" s="51"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="M35" s="51"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="M36" s="51"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="M37" s="51"/>
+    </x:row>
+    <x:row r="38">
+      <x:c r="M38" s="51"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="M39" s="51"/>
+    </x:row>
+    <x:row r="40">
+      <x:c r="M40" s="51"/>
+    </x:row>
+    <x:row r="41">
+      <x:c r="M41" s="51"/>
+    </x:row>
+    <x:row r="42">
+      <x:c r="M42" s="51"/>
+    </x:row>
+    <x:row r="43">
+      <x:c r="M43" s="51"/>
+    </x:row>
+    <x:row r="44">
+      <x:c r="M44" s="51"/>
+    </x:row>
+    <x:row r="45">
+      <x:c r="M45" s="51"/>
+    </x:row>
+    <x:row r="46">
+      <x:c r="M46" s="51"/>
+    </x:row>
+    <x:row r="47">
+      <x:c r="M47" s="51"/>
+    </x:row>
+    <x:row r="48">
+      <x:c r="M48" s="51"/>
+    </x:row>
+    <x:row r="49">
+      <x:c r="M49" s="51"/>
+    </x:row>
+    <x:row r="50">
+      <x:c r="M50" s="51"/>
+    </x:row>
+    <x:row r="51">
+      <x:c r="M51" s="51"/>
+    </x:row>
+    <x:row r="52">
+      <x:c r="M52" s="51"/>
+    </x:row>
+    <x:row r="53">
+      <x:c r="M53" s="51"/>
+    </x:row>
+    <x:row r="54">
+      <x:c r="M54" s="51"/>
+    </x:row>
+    <x:row r="55">
+      <x:c r="M55" s="51"/>
+    </x:row>
+    <x:row r="56">
+      <x:c r="M56" s="51"/>
+    </x:row>
+    <x:row r="57">
+      <x:c r="M57" s="51"/>
+    </x:row>
+    <x:row r="58">
+      <x:c r="M58" s="51"/>
+    </x:row>
+    <x:row r="59">
+      <x:c r="M59" s="51"/>
+    </x:row>
+    <x:row r="60">
+      <x:c r="M60" s="51"/>
+    </x:row>
+    <x:row r="61">
+      <x:c r="M61" s="51"/>
+    </x:row>
+    <x:row r="62">
+      <x:c r="M62" s="51"/>
+    </x:row>
+    <x:row r="63">
+      <x:c r="M63" s="51"/>
+    </x:row>
+    <x:row r="64">
+      <x:c r="M64" s="51"/>
+    </x:row>
+    <x:row r="65">
+      <x:c r="M65" s="51"/>
+    </x:row>
+    <x:row r="66">
+      <x:c r="M66" s="51"/>
+    </x:row>
+    <x:row r="67">
+      <x:c r="M67" s="51"/>
+    </x:row>
+    <x:row r="68">
+      <x:c r="M68" s="51"/>
+    </x:row>
+    <x:row r="69">
+      <x:c r="M69" s="51"/>
+    </x:row>
+    <x:row r="70">
+      <x:c r="M70" s="51"/>
+    </x:row>
+    <x:row r="71">
+      <x:c r="M71" s="51"/>
+    </x:row>
+    <x:row r="72">
+      <x:c r="M72" s="51"/>
+    </x:row>
+    <x:row r="73">
+      <x:c r="M73" s="51"/>
+    </x:row>
+    <x:row r="74">
+      <x:c r="M74" s="51"/>
+    </x:row>
+    <x:row r="75">
+      <x:c r="M75" s="51"/>
+    </x:row>
+    <x:row r="76">
+      <x:c r="M76" s="51"/>
+    </x:row>
+    <x:row r="77">
+      <x:c r="M77" s="51"/>
+    </x:row>
+    <x:row r="78">
+      <x:c r="M78" s="51"/>
+    </x:row>
+    <x:row r="79">
+      <x:c r="M79" s="51"/>
+    </x:row>
+    <x:row r="80">
+      <x:c r="M80" s="51"/>
+    </x:row>
+    <x:row r="81">
+      <x:c r="M81" s="51"/>
+    </x:row>
+    <x:row r="82">
+      <x:c r="M82" s="51"/>
+    </x:row>
+    <x:row r="83">
+      <x:c r="M83" s="51"/>
+    </x:row>
+    <x:row r="84">
+      <x:c r="M84" s="51"/>
+    </x:row>
+    <x:row r="85">
+      <x:c r="M85" s="51"/>
+    </x:row>
+    <x:row r="86">
+      <x:c r="M86" s="51"/>
+    </x:row>
+    <x:row r="87">
+      <x:c r="M87" s="51"/>
+    </x:row>
+    <x:row r="88">
+      <x:c r="M88" s="51"/>
+    </x:row>
+    <x:row r="89">
+      <x:c r="M89" s="51"/>
+    </x:row>
+    <x:row r="90">
+      <x:c r="M90" s="51"/>
+    </x:row>
+    <x:row r="91">
+      <x:c r="M91" s="51"/>
+    </x:row>
+    <x:row r="92">
+      <x:c r="M92" s="51"/>
+    </x:row>
+    <x:row r="93">
+      <x:c r="M93" s="51"/>
+    </x:row>
+    <x:row r="94">
+      <x:c r="M94" s="51"/>
+    </x:row>
+    <x:row r="95">
+      <x:c r="M95" s="51"/>
+    </x:row>
+    <x:row r="96">
+      <x:c r="M96" s="51"/>
+    </x:row>
+    <x:row r="97">
+      <x:c r="M97" s="51"/>
+    </x:row>
+    <x:row r="98">
+      <x:c r="M98" s="51"/>
+    </x:row>
+    <x:row r="99">
+      <x:c r="M99" s="51"/>
+    </x:row>
+    <x:row r="100">
+      <x:c r="M100" s="51"/>
+    </x:row>
+    <x:row r="101">
+      <x:c r="M101" s="51"/>
+    </x:row>
+    <x:row r="102">
+      <x:c r="M102" s="51"/>
+    </x:row>
+    <x:row r="103">
+      <x:c r="M103" s="51"/>
+    </x:row>
+    <x:row r="104">
+      <x:c r="M104" s="51"/>
+    </x:row>
+    <x:row r="105">
+      <x:c r="M105" s="51"/>
+    </x:row>
+    <x:row r="106">
+      <x:c r="M106" s="51"/>
+    </x:row>
+    <x:row r="107">
+      <x:c r="M107" s="51"/>
+    </x:row>
+    <x:row r="108">
+      <x:c r="M108" s="51"/>
+    </x:row>
+    <x:row r="109">
+      <x:c r="M109" s="51"/>
+    </x:row>
+    <x:row r="110">
+      <x:c r="M110" s="51"/>
+    </x:row>
+    <x:row r="111">
+      <x:c r="M111" s="51"/>
+    </x:row>
+    <x:row r="112">
+      <x:c r="M112" s="51"/>
+    </x:row>
+    <x:row r="113">
+      <x:c r="M113" s="51"/>
+    </x:row>
+    <x:row r="114">
+      <x:c r="M114" s="51"/>
+    </x:row>
+    <x:row r="115">
+      <x:c r="M115" s="51"/>
+    </x:row>
+    <x:row r="116">
+      <x:c r="M116" s="51"/>
+    </x:row>
+    <x:row r="117">
+      <x:c r="M117" s="51"/>
+    </x:row>
+    <x:row r="118">
+      <x:c r="M118" s="51"/>
+    </x:row>
+    <x:row r="119">
+      <x:c r="M119" s="51"/>
+    </x:row>
+    <x:row r="120">
+      <x:c r="M120" s="51"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -9213,7 +10119,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6ce13ec41dae4e61"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdf5d8ef80d69497f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9351,13 +10257,13 @@
         <x:v>Magnetfeld mit linearem Hall-Sensor erfassen</x:v>
       </x:c>
       <x:c r="K5" s="57" t="str">
-        <x:v>ph_k10_st01_magnetische_pole_krafte_und_erdmagnetfeld</x:v>
+        <x:v>ph_k10_st01_magnetische_pole_kraefte_und_erdmagnetfeld</x:v>
       </x:c>
       <x:c r="L5" s="57" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/018_kompass_erdmagnetfeld.jpg</x:v>
       </x:c>
       <x:c r="M5" s="156" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_01_magnetische_pole_kraefte_und_erdmagnetfeld.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st01_magnetische_pole_kraefte_und_erdmagnetfeld_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N5" s="157" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st01_magnetische_pole_krafte_und_erdmagnetfeld_orga.html","Vorbereitung öffnen")</x:f>
@@ -9402,7 +10308,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/090_physik_klassenraum.jpg</x:v>
       </x:c>
       <x:c r="M6" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_02_elektrisches_und_magnetisches_feld_vergleichen.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st02_elektrisches_und_magnetisches_feld_vergleichen_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N6" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st02_elektrisches_und_magnetisches_feld_vergleichen_orga.html","Vorbereitung öffnen")</x:f>
@@ -9441,13 +10347,13 @@
         <x:v>zeitgesteuerte Ansteuerung über MOSFET-Modul und Strommessung</x:v>
       </x:c>
       <x:c r="K7" s="60" t="str">
-        <x:v>ph_k10_st03_elektromagnet_windungszahl_stromstarke_und_eisenkern</x:v>
+        <x:v>ph_k10_st03_elektromagnet_windungszahl_stromstaerke_und_eisenkern</x:v>
       </x:c>
       <x:c r="L7" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/019_elektromagnet.jpg</x:v>
       </x:c>
       <x:c r="M7" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_03_elektromagnet_windungszahl_stromstaerke_und_eisenkern.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st03_elektromagnet_windungszahl_stromstaerke_und_eisenkern_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N7" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st03_elektromagnet_windungszahl_stromstarke_und_eisenkern_orga.html","Vorbereitung öffnen")</x:f>
@@ -9492,7 +10398,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/019_elektromagnet.jpg</x:v>
       </x:c>
       <x:c r="M8" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_04_kraft_auf_einen_stromdurchflossenen_leiter.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st04_kraft_auf_einen_stromdurchflossenen_leiter_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N8" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st04_kraft_auf_einen_stromdurchflossenen_leiter_orga.html","Vorbereitung öffnen")</x:f>
@@ -9537,7 +10443,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/044_generator_motor.jpg</x:v>
       </x:c>
       <x:c r="M9" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_05_elektromotor_lautsprecher_und_relais.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st05_elektromotor_lautsprecher_und_relais_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N9" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st05_elektromotor_lautsprecher_und_relais_orga.html","Vorbereitung öffnen")</x:f>
@@ -9582,7 +10488,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/043_induktion.jpg</x:v>
       </x:c>
       <x:c r="M10" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_06_elektromagnetische_induktion.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st06_elektromagnetische_induktion_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N10" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st06_elektromagnetische_induktion_orga.html","Vorbereitung öffnen")</x:f>
@@ -9627,7 +10533,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/044_generator_motor.jpg</x:v>
       </x:c>
       <x:c r="M11" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_07_generator_und_wechselspannung.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st07_generator_und_wechselspannung_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N11" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st07_generator_und_wechselspannung_orga.html","Vorbereitung öffnen")</x:f>
@@ -9672,7 +10578,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/045_transformator.jpg</x:v>
       </x:c>
       <x:c r="M12" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_08_transformator_und_stromverbundnetz.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st08_transformator_und_stromverbundnetz_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N12" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st08_transformator_und_stromverbundnetz_orga.html","Vorbereitung öffnen")</x:f>
@@ -9717,7 +10623,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/023_gleichfoermige_bewegung.jpg</x:v>
       </x:c>
       <x:c r="M13" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_09_bewegung_bezugssystem_weg_zeit_und_geschwindigkeit.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st09_bewegung_bezugssystem_weg_zeit_und_geschwindigkeit_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N13" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st09_bewegung_bezugssystem_weg_zeit_und_geschwindigkeit_orga.html","Vorbereitung öffnen")</x:f>
@@ -9756,13 +10662,13 @@
         <x:v>Ultraschall-Datenlogger</x:v>
       </x:c>
       <x:c r="K14" s="60" t="str">
-        <x:v>ph_k10_st10_geradlinig_gleichformige_bewegung_und_diagramme</x:v>
+        <x:v>ph_k10_st10_geradlinig_gleichfoermige_bewegung_und_diagramme</x:v>
       </x:c>
       <x:c r="L14" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/023_gleichfoermige_bewegung.jpg</x:v>
       </x:c>
       <x:c r="M14" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_10_geradlinig_gleichfoermige_bewegung_und_diagramme.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st10_geradlinig_gleichfoermige_bewegung_und_diagramme_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N14" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st10_geradlinig_gleichformige_bewegung_und_diagramme_orga.html","Vorbereitung öffnen")</x:f>
@@ -9801,13 +10707,13 @@
         <x:v>Ultraschall-Datenlogger</x:v>
       </x:c>
       <x:c r="K15" s="60" t="str">
-        <x:v>ph_k10_st11_geradlinig_gleichmaig_beschleunigte_bewegung</x:v>
+        <x:v>ph_k10_st11_geradlinig_gleichmaessig_beschleunigte_bewegung</x:v>
       </x:c>
       <x:c r="L15" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/023_gleichfoermige_bewegung.jpg</x:v>
       </x:c>
       <x:c r="M15" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_11_geradlinig_gleichmaessig_beschleunigte_bewegung.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st11_geradlinig_gleichmaessig_beschleunigte_bewegung_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N15" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st11_geradlinig_gleichmaig_beschleunigte_bewegung_orga.html","Vorbereitung öffnen")</x:f>
@@ -9852,7 +10758,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/092_beschleunigung.jpg</x:v>
       </x:c>
       <x:c r="M16" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_12_freier_fall.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st12_freier_fall_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N16" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st12_freier_fall_orga.html","Vorbereitung öffnen")</x:f>
@@ -9891,13 +10797,13 @@
         <x:v>nein</x:v>
       </x:c>
       <x:c r="K17" s="60" t="str">
-        <x:v>ph_k10_st13_erstes_newtonsches_gesetz_und_tragheit</x:v>
+        <x:v>ph_k10_st13_erstes_newtonsches_gesetz_und_traegheit</x:v>
       </x:c>
       <x:c r="L17" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/024_newton_krafte.jpg</x:v>
       </x:c>
       <x:c r="M17" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_13_erstes_newtonsches_gesetz_und_traegheit.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st13_erstes_newtonsches_gesetz_und_traegheit_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N17" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st13_erstes_newtonsches_gesetz_und_tragheit_orga.html","Vorbereitung öffnen")</x:f>
@@ -9942,7 +10848,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/024_newton_krafte.jpg</x:v>
       </x:c>
       <x:c r="M18" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_14_zweites_newtonsches_gesetz_f_m_a.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st14_zweites_newtonsches_gesetz_f_m_a_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N18" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st14_zweites_newtonsches_gesetz_f_m_a_orga.html","Vorbereitung öffnen")</x:f>
@@ -9987,7 +10893,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/024_newton_krafte.jpg</x:v>
       </x:c>
       <x:c r="M19" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_15_drittes_newtonsches_gesetz_actio_und_reactio.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st15_drittes_newtonsches_gesetz_actio_und_reactio_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N19" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st15_drittes_newtonsches_gesetz_actio_und_reactio_orga.html","Vorbereitung öffnen")</x:f>
@@ -10032,7 +10938,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/004_sonnensystem.jpg</x:v>
       </x:c>
       <x:c r="M20" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_16_gravitation_gewichtskraft_und_planetenbewegung.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st16_gravitation_gewichtskraft_und_planetenbewegung_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N20" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st16_gravitation_gewichtskraft_und_planetenbewegung_orga.html","Vorbereitung öffnen")</x:f>
@@ -10071,13 +10977,13 @@
         <x:v>Drehzahlmessung mit Hall-Sensor</x:v>
       </x:c>
       <x:c r="K21" s="60" t="str">
-        <x:v>ph_k10_st17_gleichformige_kreisbewegung</x:v>
+        <x:v>ph_k10_st17_gleichfoermige_kreisbewegung</x:v>
       </x:c>
       <x:c r="L21" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/023_gleichfoermige_bewegung.jpg</x:v>
       </x:c>
       <x:c r="M21" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_17_gleichfoermige_kreisbewegung.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st17_gleichfoermige_kreisbewegung_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N21" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st17_gleichformige_kreisbewegung_orga.html","Vorbereitung öffnen")</x:f>
@@ -10116,13 +11022,13 @@
         <x:v>Abstandssensor zeichnet Schwingung auf</x:v>
       </x:c>
       <x:c r="K22" s="60" t="str">
-        <x:v>ph_k10_st18_schwingungen_und_ihre_kenngroen</x:v>
+        <x:v>ph_k10_st18_schwingungen_und_ihre_kenngroessen</x:v>
       </x:c>
       <x:c r="L22" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/094_schwingung_welle.jpg</x:v>
       </x:c>
       <x:c r="M22" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_18_schwingungen_und_ihre_kenngroessen.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st18_schwingungen_und_ihre_kenngroessen_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N22" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st18_schwingungen_und_ihre_kenngroen_orga.html","Vorbereitung öffnen")</x:f>
@@ -10167,7 +11073,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/094_schwingung_welle.jpg</x:v>
       </x:c>
       <x:c r="M23" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_19_schwingungsdauer_des_fadenpendels.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st19_schwingungsdauer_des_fadenpendels_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N23" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st19_schwingungsdauer_des_fadenpendels_orga.html","Vorbereitung öffnen")</x:f>
@@ -10212,7 +11118,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/094_schwingung_welle.jpg</x:v>
       </x:c>
       <x:c r="M24" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_20_wellen_als_ausbreitung_von_schwingungen.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st20_wellen_als_ausbreitung_von_schwingungen_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N24" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st20_wellen_als_ausbreitung_von_schwingungen_orga.html","Vorbereitung öffnen")</x:f>
@@ -10251,13 +11157,13 @@
         <x:v>Piezo-Ausgabe und Mikrofonmodul</x:v>
       </x:c>
       <x:c r="K25" s="60" t="str">
-        <x:v>ph_k10_st21_schall_frequenz_tonhohe_und_larmschutz</x:v>
+        <x:v>ph_k10_st21_schall_frequenz_tonhoehe_und_laermschutz</x:v>
       </x:c>
       <x:c r="L25" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/031_schall_wellen.jpg</x:v>
       </x:c>
       <x:c r="M25" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_21_schall_frequenz_tonhoehe_und_laermschutz.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st21_schall_frequenz_tonhoehe_und_laermschutz_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N25" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st21_schall_frequenz_tonhohe_und_larmschutz_orga.html","Vorbereitung öffnen")</x:f>
@@ -10296,13 +11202,13 @@
         <x:v>Kraftsensor und Wegsensor</x:v>
       </x:c>
       <x:c r="K26" s="60" t="str">
-        <x:v>ph_k10_st22_arbeit_energieformen_und_energie_als_zustandsgroe</x:v>
+        <x:v>ph_k10_st22_arbeit_energieformen_und_energie_als_zustandsgroesse</x:v>
       </x:c>
       <x:c r="L26" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/038_arbeit_leistung.jpg</x:v>
       </x:c>
       <x:c r="M26" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_22_arbeit_energieformen_und_energie_als_zustandsgroesse.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st22_arbeit_energieformen_und_energie_als_zustandsgroesse_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N26" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st22_arbeit_energieformen_und_energie_als_zustandsgroe_orga.html","Vorbereitung öffnen")</x:f>
@@ -10347,7 +11253,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/036_energie_formen.jpg</x:v>
       </x:c>
       <x:c r="M27" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_23_allgemeiner_energieerhaltungssatz.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st23_allgemeiner_energieerhaltungssatz_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N27" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st23_allgemeiner_energieerhaltungssatz_orga.html","Vorbereitung öffnen")</x:f>
@@ -10392,7 +11298,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/064_elektrische_energie.jpg</x:v>
       </x:c>
       <x:c r="M28" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_24_wirkungsgrad_und_versorgung_mit_elektrischer_energie.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st24_wirkungsgrad_und_versorgung_mit_elektrischer_energie_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N28" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st24_wirkungsgrad_und_versorgung_mit_elektrischer_energie_orga.html","Vorbereitung öffnen")</x:f>
@@ -10437,7 +11343,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/042_radioaktivitaet.jpg</x:v>
       </x:c>
       <x:c r="M29" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_25_atomkern_und_nuklidschreibweise.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st25_atomkern_und_nuklidschreibweise_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N29" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st25_atomkern_und_nuklidschreibweise_orga.html","Vorbereitung öffnen")</x:f>
@@ -10482,7 +11388,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/042_radioaktivitaet.jpg</x:v>
       </x:c>
       <x:c r="M30" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_26_und_strahlung_eigenschaften_nachweis_und_abschirmung.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st26_und_strahlung_eigenschaften_nachweis_und_abschirmung_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N30" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st26_und_strahlung_eigenschaften_nachweis_und_abschirmung_orga.html","Vorbereitung öffnen")</x:f>
@@ -10527,7 +11433,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/042_radioaktivitaet.jpg</x:v>
       </x:c>
       <x:c r="M31" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_27_radioaktiver_zerfall_und_halbwertszeit.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st27_radioaktiver_zerfall_und_halbwertszeit_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N31" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st27_radioaktiver_zerfall_und_halbwertszeit_orga.html","Vorbereitung öffnen")</x:f>
@@ -10572,11 +11478,275 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/054_sonne_aufbau.jpg</x:v>
       </x:c>
       <x:c r="M32" s="160" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_28_anwendungen_strahlenschutz_kernspaltung_und_kernfusion.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st28_anwendungen_strahlenschutz_kernspaltung_und_kernfusion_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N32" s="161" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st28_anwendungen_strahlenschutz_kernspaltung_und_kernfusion_orga.html","Vorbereitung öffnen")</x:f>
       </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="M33" s="51"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="M34" s="51"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="M35" s="51"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="M36" s="51"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="M37" s="51"/>
+    </x:row>
+    <x:row r="38">
+      <x:c r="M38" s="51"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="M39" s="51"/>
+    </x:row>
+    <x:row r="40">
+      <x:c r="M40" s="51"/>
+    </x:row>
+    <x:row r="41">
+      <x:c r="M41" s="51"/>
+    </x:row>
+    <x:row r="42">
+      <x:c r="M42" s="51"/>
+    </x:row>
+    <x:row r="43">
+      <x:c r="M43" s="51"/>
+    </x:row>
+    <x:row r="44">
+      <x:c r="M44" s="51"/>
+    </x:row>
+    <x:row r="45">
+      <x:c r="M45" s="51"/>
+    </x:row>
+    <x:row r="46">
+      <x:c r="M46" s="51"/>
+    </x:row>
+    <x:row r="47">
+      <x:c r="M47" s="51"/>
+    </x:row>
+    <x:row r="48">
+      <x:c r="M48" s="51"/>
+    </x:row>
+    <x:row r="49">
+      <x:c r="M49" s="51"/>
+    </x:row>
+    <x:row r="50">
+      <x:c r="M50" s="51"/>
+    </x:row>
+    <x:row r="51">
+      <x:c r="M51" s="51"/>
+    </x:row>
+    <x:row r="52">
+      <x:c r="M52" s="51"/>
+    </x:row>
+    <x:row r="53">
+      <x:c r="M53" s="51"/>
+    </x:row>
+    <x:row r="54">
+      <x:c r="M54" s="51"/>
+    </x:row>
+    <x:row r="55">
+      <x:c r="M55" s="51"/>
+    </x:row>
+    <x:row r="56">
+      <x:c r="M56" s="51"/>
+    </x:row>
+    <x:row r="57">
+      <x:c r="M57" s="51"/>
+    </x:row>
+    <x:row r="58">
+      <x:c r="M58" s="51"/>
+    </x:row>
+    <x:row r="59">
+      <x:c r="M59" s="51"/>
+    </x:row>
+    <x:row r="60">
+      <x:c r="M60" s="51"/>
+    </x:row>
+    <x:row r="61">
+      <x:c r="M61" s="51"/>
+    </x:row>
+    <x:row r="62">
+      <x:c r="M62" s="51"/>
+    </x:row>
+    <x:row r="63">
+      <x:c r="M63" s="51"/>
+    </x:row>
+    <x:row r="64">
+      <x:c r="M64" s="51"/>
+    </x:row>
+    <x:row r="65">
+      <x:c r="M65" s="51"/>
+    </x:row>
+    <x:row r="66">
+      <x:c r="M66" s="51"/>
+    </x:row>
+    <x:row r="67">
+      <x:c r="M67" s="51"/>
+    </x:row>
+    <x:row r="68">
+      <x:c r="M68" s="51"/>
+    </x:row>
+    <x:row r="69">
+      <x:c r="M69" s="51"/>
+    </x:row>
+    <x:row r="70">
+      <x:c r="M70" s="51"/>
+    </x:row>
+    <x:row r="71">
+      <x:c r="M71" s="51"/>
+    </x:row>
+    <x:row r="72">
+      <x:c r="M72" s="51"/>
+    </x:row>
+    <x:row r="73">
+      <x:c r="M73" s="51"/>
+    </x:row>
+    <x:row r="74">
+      <x:c r="M74" s="51"/>
+    </x:row>
+    <x:row r="75">
+      <x:c r="M75" s="51"/>
+    </x:row>
+    <x:row r="76">
+      <x:c r="M76" s="51"/>
+    </x:row>
+    <x:row r="77">
+      <x:c r="M77" s="51"/>
+    </x:row>
+    <x:row r="78">
+      <x:c r="M78" s="51"/>
+    </x:row>
+    <x:row r="79">
+      <x:c r="M79" s="51"/>
+    </x:row>
+    <x:row r="80">
+      <x:c r="M80" s="51"/>
+    </x:row>
+    <x:row r="81">
+      <x:c r="M81" s="51"/>
+    </x:row>
+    <x:row r="82">
+      <x:c r="M82" s="51"/>
+    </x:row>
+    <x:row r="83">
+      <x:c r="M83" s="51"/>
+    </x:row>
+    <x:row r="84">
+      <x:c r="M84" s="51"/>
+    </x:row>
+    <x:row r="85">
+      <x:c r="M85" s="51"/>
+    </x:row>
+    <x:row r="86">
+      <x:c r="M86" s="51"/>
+    </x:row>
+    <x:row r="87">
+      <x:c r="M87" s="51"/>
+    </x:row>
+    <x:row r="88">
+      <x:c r="M88" s="51"/>
+    </x:row>
+    <x:row r="89">
+      <x:c r="M89" s="51"/>
+    </x:row>
+    <x:row r="90">
+      <x:c r="M90" s="51"/>
+    </x:row>
+    <x:row r="91">
+      <x:c r="M91" s="51"/>
+    </x:row>
+    <x:row r="92">
+      <x:c r="M92" s="51"/>
+    </x:row>
+    <x:row r="93">
+      <x:c r="M93" s="51"/>
+    </x:row>
+    <x:row r="94">
+      <x:c r="M94" s="51"/>
+    </x:row>
+    <x:row r="95">
+      <x:c r="M95" s="51"/>
+    </x:row>
+    <x:row r="96">
+      <x:c r="M96" s="51"/>
+    </x:row>
+    <x:row r="97">
+      <x:c r="M97" s="51"/>
+    </x:row>
+    <x:row r="98">
+      <x:c r="M98" s="51"/>
+    </x:row>
+    <x:row r="99">
+      <x:c r="M99" s="51"/>
+    </x:row>
+    <x:row r="100">
+      <x:c r="M100" s="51"/>
+    </x:row>
+    <x:row r="101">
+      <x:c r="M101" s="51"/>
+    </x:row>
+    <x:row r="102">
+      <x:c r="M102" s="51"/>
+    </x:row>
+    <x:row r="103">
+      <x:c r="M103" s="51"/>
+    </x:row>
+    <x:row r="104">
+      <x:c r="M104" s="51"/>
+    </x:row>
+    <x:row r="105">
+      <x:c r="M105" s="51"/>
+    </x:row>
+    <x:row r="106">
+      <x:c r="M106" s="51"/>
+    </x:row>
+    <x:row r="107">
+      <x:c r="M107" s="51"/>
+    </x:row>
+    <x:row r="108">
+      <x:c r="M108" s="51"/>
+    </x:row>
+    <x:row r="109">
+      <x:c r="M109" s="51"/>
+    </x:row>
+    <x:row r="110">
+      <x:c r="M110" s="51"/>
+    </x:row>
+    <x:row r="111">
+      <x:c r="M111" s="51"/>
+    </x:row>
+    <x:row r="112">
+      <x:c r="M112" s="51"/>
+    </x:row>
+    <x:row r="113">
+      <x:c r="M113" s="51"/>
+    </x:row>
+    <x:row r="114">
+      <x:c r="M114" s="51"/>
+    </x:row>
+    <x:row r="115">
+      <x:c r="M115" s="51"/>
+    </x:row>
+    <x:row r="116">
+      <x:c r="M116" s="51"/>
+    </x:row>
+    <x:row r="117">
+      <x:c r="M117" s="51"/>
+    </x:row>
+    <x:row r="118">
+      <x:c r="M118" s="51"/>
+    </x:row>
+    <x:row r="119">
+      <x:c r="M119" s="51"/>
+    </x:row>
+    <x:row r="120">
+      <x:c r="M120" s="51"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -10585,7 +11755,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4db60e4a693a487b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc37991fb22d3441f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10729,7 +11899,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/084_elektromagnetisches_spektrum.jpg</x:v>
       </x:c>
       <x:c r="M5" s="156" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/as10_stunde_01_astronomie_als_beobachtungswissenschaft_und_elektromagnetisches_spektrum.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/as_k10_st01_astronomie_als_beobachtungswissenschaft_und_elektromagnetisches_spektrum_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N5" s="157" t="e">
         <x:f>HYPERLINK("lehrer/astronomie/as_k10_st01_astronomie_als_beobachtungswissenschaft_und_elektromagnetisches_spektrum_orga.html","Vorbereitung öffnen")</x:f>
@@ -10774,7 +11944,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/049_teleskop.jpg</x:v>
       </x:c>
       <x:c r="M6" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/as10_stunde_02_himmelskugel_horizont_und_orientierung.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/as_k10_st02_himmelskugel_horizont_und_orientierung_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N6" s="159" t="e">
         <x:f>HYPERLINK("lehrer/astronomie/as_k10_st02_himmelskugel_horizont_und_orientierung_orga.html","Vorbereitung öffnen")</x:f>
@@ -10819,7 +11989,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/049_teleskop.jpg</x:v>
       </x:c>
       <x:c r="M7" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/as10_stunde_03_drehbare_sternkarte_und_jahreszeitliche_sternbilder.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/as_k10_st03_drehbare_sternkarte_und_jahreszeitliche_sternbilder_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N7" s="159" t="e">
         <x:f>HYPERLINK("lehrer/astronomie/as_k10_st03_drehbare_sternkarte_und_jahreszeitliche_sternbilder_orga.html","Vorbereitung öffnen")</x:f>
@@ -10864,7 +12034,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/049_teleskop.jpg</x:v>
       </x:c>
       <x:c r="M8" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/as10_stunde_04_polarstern_erdrotation_und_scheinbare_himmelsbewegung.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/as_k10_st04_polarstern_erdrotation_und_scheinbare_himmelsbewegung_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N8" s="159" t="e">
         <x:f>HYPERLINK("lehrer/astronomie/as_k10_st04_polarstern_erdrotation_und_scheinbare_himmelsbewegung_orga.html","Vorbereitung öffnen")</x:f>
@@ -10909,7 +12079,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/049_teleskop.jpg</x:v>
       </x:c>
       <x:c r="M9" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/as10_stunde_05_astronomische_beobachtung_planen_und_dokumentieren.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/as_k10_st05_astronomische_beobachtung_planen_und_dokumentieren_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N9" s="159" t="e">
         <x:f>HYPERLINK("lehrer/astronomie/as_k10_st05_astronomische_beobachtung_planen_und_dokumentieren_orga.html","Vorbereitung öffnen")</x:f>
@@ -10954,7 +12124,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/090_physik_klassenraum.jpg</x:v>
       </x:c>
       <x:c r="M10" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/as10_stunde_06_vom_geozentrischen_zum_heliozentrischen_weltbild_schattenstab.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/as_k10_st06_vom_geozentrischen_zum_heliozentrischen_weltbild_schattenstab_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N10" s="159" t="e">
         <x:f>HYPERLINK("lehrer/astronomie/as_k10_st06_vom_geozentrischen_zum_heliozentrischen_weltbild_schattenstab_orga.html","Vorbereitung öffnen")</x:f>
@@ -10993,13 +12163,13 @@
         <x:v>nein</x:v>
       </x:c>
       <x:c r="K11" s="60" t="str">
-        <x:v>as_k10_st07_entstehung_raumlicher_aufbau_und_klassen_von_himmelskorpern</x:v>
+        <x:v>as_k10_st07_entstehung_raeumlicher_aufbau_und_klassen_von_himmelskoerpern</x:v>
       </x:c>
       <x:c r="L11" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/004_sonnensystem.jpg</x:v>
       </x:c>
       <x:c r="M11" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/as10_stunde_07_entstehung_raeumlicher_aufbau_und_klassen_von_himmelskoerpern.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/as_k10_st07_entstehung_raeumlicher_aufbau_und_klassen_von_himmelskoerpern_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N11" s="159" t="e">
         <x:f>HYPERLINK("lehrer/astronomie/as_k10_st07_entstehung_raumlicher_aufbau_und_klassen_von_himmelskorpern_orga.html","Vorbereitung öffnen")</x:f>
@@ -11038,13 +12208,13 @@
         <x:v>Ultraschallsensor als Distanzanzeige im Modell</x:v>
       </x:c>
       <x:c r="K12" s="60" t="str">
-        <x:v>as_k10_st08_groen_und_entfernungen_im_sonnensystem</x:v>
+        <x:v>as_k10_st08_groessen_und_entfernungen_im_sonnensystem</x:v>
       </x:c>
       <x:c r="L12" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/054_sonne_aufbau.jpg</x:v>
       </x:c>
       <x:c r="M12" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/as10_stunde_08_groessen_und_entfernungen_im_sonnensystem.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/as_k10_st08_groessen_und_entfernungen_im_sonnensystem_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N12" s="159" t="e">
         <x:f>HYPERLINK("lehrer/astronomie/as_k10_st08_groen_und_entfernungen_im_sonnensystem_orga.html","Vorbereitung öffnen")</x:f>
@@ -11089,7 +12259,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/048_jahreszeiten.jpg</x:v>
       </x:c>
       <x:c r="M13" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/as10_stunde_09_erdrotation_erdrevolution_und_jahreszeiten.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/as_k10_st09_erdrotation_erdrevolution_und_jahreszeiten_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N13" s="159" t="e">
         <x:f>HYPERLINK("lehrer/astronomie/as_k10_st09_erdrotation_erdrevolution_und_jahreszeiten_orga.html","Vorbereitung öffnen")</x:f>
@@ -11134,7 +12304,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/009_mondphasen.jpg</x:v>
       </x:c>
       <x:c r="M14" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/as10_stunde_10_mondphasen_und_finsternisse.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/as_k10_st10_mondphasen_und_finsternisse_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N14" s="159" t="e">
         <x:f>HYPERLINK("lehrer/astronomie/as_k10_st10_mondphasen_und_finsternisse_orga.html","Vorbereitung öffnen")</x:f>
@@ -11179,7 +12349,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/055_keplergesetze.jpg</x:v>
       </x:c>
       <x:c r="M15" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/as10_stunde_11_keplersche_gesetze.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/as_k10_st11_keplersche_gesetze_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N15" s="159" t="e">
         <x:f>HYPERLINK("lehrer/astronomie/as_k10_st11_keplersche_gesetze_orga.html","Vorbereitung öffnen")</x:f>
@@ -11224,7 +12394,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/091_gravitation.jpg</x:v>
       </x:c>
       <x:c r="M16" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/as10_stunde_12_gravitation_und_umlaufbahnen.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/as_k10_st12_gravitation_und_umlaufbahnen_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N16" s="159" t="e">
         <x:f>HYPERLINK("lehrer/astronomie/as_k10_st12_gravitation_und_umlaufbahnen_orga.html","Vorbereitung öffnen")</x:f>
@@ -11269,7 +12439,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/054_sonne_aufbau.jpg</x:v>
       </x:c>
       <x:c r="M17" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/as10_stunde_13_aufbau_der_sonne_kernfusion_und_energietransport.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/as_k10_st13_aufbau_der_sonne_kernfusion_und_energietransport_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N17" s="159" t="e">
         <x:f>HYPERLINK("lehrer/astronomie/as_k10_st13_aufbau_der_sonne_kernfusion_und_energietransport_orga.html","Vorbereitung öffnen")</x:f>
@@ -11308,13 +12478,13 @@
         <x:v>RGB-/Lichtsensor vergleicht Lichtquellen; keine direkte Sonnenmessung</x:v>
       </x:c>
       <x:c r="K18" s="60" t="str">
-        <x:v>as_k10_st14_sonnenstrahlung_spektrum_aktivitat_und_weltraumwetter</x:v>
+        <x:v>as_k10_st14_sonnenstrahlung_spektrum_aktivitaet_und_weltraumwetter</x:v>
       </x:c>
       <x:c r="L18" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/054_sonne_aufbau.jpg</x:v>
       </x:c>
       <x:c r="M18" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/as10_stunde_14_sonnenstrahlung_spektrum_aktivitaet_und_weltraumwetter.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/as_k10_st14_sonnenstrahlung_spektrum_aktivitaet_und_weltraumwetter_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N18" s="159" t="e">
         <x:f>HYPERLINK("lehrer/astronomie/as_k10_st14_sonnenstrahlung_spektrum_aktivitat_und_weltraumwetter_orga.html","Vorbereitung öffnen")</x:f>
@@ -11353,13 +12523,13 @@
         <x:v>zwei Temperatursensoren vergleichen Oberflächen</x:v>
       </x:c>
       <x:c r="K19" s="60" t="str">
-        <x:v>as_k10_st15_planeten_klassifizieren_und_bedingungen_fur_leben</x:v>
+        <x:v>as_k10_st15_planeten_klassifizieren_und_bedingungen_fuer_leben</x:v>
       </x:c>
       <x:c r="L19" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/004_sonnensystem.jpg</x:v>
       </x:c>
       <x:c r="M19" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/as10_stunde_15_planeten_klassifizieren_und_bedingungen_fuer_leben.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/as_k10_st15_planeten_klassifizieren_und_bedingungen_fuer_leben_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N19" s="159" t="e">
         <x:f>HYPERLINK("lehrer/astronomie/as_k10_st15_planeten_klassifizieren_und_bedingungen_fur_leben_orga.html","Vorbereitung öffnen")</x:f>
@@ -11398,13 +12568,13 @@
         <x:v>Beschleunigungssensor misst Aufprallstärke im Modell</x:v>
       </x:c>
       <x:c r="K20" s="60" t="str">
-        <x:v>as_k10_st16_mondoberflache_gezeiten_und_raumfahrt</x:v>
+        <x:v>as_k10_st16_mondoberflaeche_gezeiten_und_raumfahrt</x:v>
       </x:c>
       <x:c r="L20" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/009_mondphasen.jpg</x:v>
       </x:c>
       <x:c r="M20" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/as10_stunde_16_mondoberflaeche_gezeiten_und_raumfahrt.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/as_k10_st16_mondoberflaeche_gezeiten_und_raumfahrt_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N20" s="159" t="e">
         <x:f>HYPERLINK("lehrer/astronomie/as_k10_st16_mondoberflache_gezeiten_und_raumfahrt_orga.html","Vorbereitung öffnen")</x:f>
@@ -11449,7 +12619,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/077_lichtjahr.jpg</x:v>
       </x:c>
       <x:c r="M21" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/as10_stunde_17_lichtjahr_blick_in_die_vergangenheit_und_scheinbare_helligkeit.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/as_k10_st17_lichtjahr_blick_in_die_vergangenheit_und_scheinbare_helligkeit_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N21" s="159" t="e">
         <x:f>HYPERLINK("lehrer/astronomie/as_k10_st17_lichtjahr_blick_in_die_vergangenheit_und_scheinbare_helligkeit_orga.html","Vorbereitung öffnen")</x:f>
@@ -11494,7 +12664,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/049_teleskop.jpg</x:v>
       </x:c>
       <x:c r="M22" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/as10_stunde_18_astronomische_entfernungsbestimmung_durch_parallaxe.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/as_k10_st18_astronomische_entfernungsbestimmung_durch_parallaxe_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N22" s="159" t="e">
         <x:f>HYPERLINK("lehrer/astronomie/as_k10_st18_astronomische_entfernungsbestimmung_durch_parallaxe_orga.html","Vorbereitung öffnen")</x:f>
@@ -11539,7 +12709,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/046_sterne_spektrum.jpg</x:v>
       </x:c>
       <x:c r="M23" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/as10_stunde_19_sternspektren_farben_und_temperaturen.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/as_k10_st19_sternspektren_farben_und_temperaturen_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N23" s="159" t="e">
         <x:f>HYPERLINK("lehrer/astronomie/as_k10_st19_sternspektren_farben_und_temperaturen_orga.html","Vorbereitung öffnen")</x:f>
@@ -11584,7 +12754,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/046_sterne_spektrum.jpg</x:v>
       </x:c>
       <x:c r="M24" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/as10_stunde_20_hertzsprung_russell_diagramm.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/as_k10_st20_hertzsprung_russell_diagramm_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N24" s="159" t="e">
         <x:f>HYPERLINK("lehrer/astronomie/as_k10_st20_hertzsprung_russell_diagramm_orga.html","Vorbereitung öffnen")</x:f>
@@ -11623,13 +12793,13 @@
         <x:v>nein</x:v>
       </x:c>
       <x:c r="K25" s="60" t="str">
-        <x:v>as_k10_st21_entstehung_und_entwicklung_sonnenahnlicher_sterne</x:v>
+        <x:v>as_k10_st21_entstehung_und_entwicklung_sonnenaehnlicher_sterne</x:v>
       </x:c>
       <x:c r="L25" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/078_sternentwicklung.jpg</x:v>
       </x:c>
       <x:c r="M25" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/as10_stunde_21_entstehung_und_entwicklung_sonnenaehnlicher_sterne.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/as_k10_st21_entstehung_und_entwicklung_sonnenaehnlicher_sterne_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N25" s="159" t="e">
         <x:f>HYPERLINK("lehrer/astronomie/as_k10_st21_entstehung_und_entwicklung_sonnenahnlicher_sterne_orga.html","Vorbereitung öffnen")</x:f>
@@ -11674,7 +12844,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/078_sternentwicklung.jpg</x:v>
       </x:c>
       <x:c r="M26" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/as10_stunde_22_massereiche_sterne_und_endstadien.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/as_k10_st22_massereiche_sterne_und_endstadien_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N26" s="159" t="e">
         <x:f>HYPERLINK("lehrer/astronomie/as_k10_st22_massereiche_sterne_und_endstadien_orga.html","Vorbereitung öffnen")</x:f>
@@ -11713,13 +12883,13 @@
         <x:v>Schrittmotor dreht Spiralgalaxienmodell</x:v>
       </x:c>
       <x:c r="K27" s="60" t="str">
-        <x:v>as_k10_st23_milchstrae_galaxien_und_groraumige_strukturen</x:v>
+        <x:v>as_k10_st23_milchstrasse_galaxien_und_grossraeumige_strukturen</x:v>
       </x:c>
       <x:c r="L27" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/047_galaxien.jpg</x:v>
       </x:c>
       <x:c r="M27" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/as10_stunde_23_milchstrasse_galaxien_und_grossraeumige_strukturen.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/as_k10_st23_milchstrasse_galaxien_und_grossraeumige_strukturen_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N27" s="159" t="e">
         <x:f>HYPERLINK("lehrer/astronomie/as_k10_st23_milchstrae_galaxien_und_groraumige_strukturen_orga.html","Vorbereitung öffnen")</x:f>
@@ -11764,11 +12934,287 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/087_universum_entstehung.jpg</x:v>
       </x:c>
       <x:c r="M28" s="160" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/as10_stunde_24_urknall_expansion_rotverschiebung_und_kosmische_hintergrundstrahlung.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/as_k10_st24_urknall_expansion_rotverschiebung_und_kosmische_hintergrundstrahlung_app.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N28" s="161" t="e">
         <x:f>HYPERLINK("lehrer/astronomie/as_k10_st24_urknall_expansion_rotverschiebung_und_kosmische_hintergrundstrahlung_orga.html","Vorbereitung öffnen")</x:f>
       </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="M29" s="51"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="M30" s="51"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="M31" s="51"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="M32" s="51"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="M33" s="51"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="M34" s="51"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="M35" s="51"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="M36" s="51"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="M37" s="51"/>
+    </x:row>
+    <x:row r="38">
+      <x:c r="M38" s="51"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="M39" s="51"/>
+    </x:row>
+    <x:row r="40">
+      <x:c r="M40" s="51"/>
+    </x:row>
+    <x:row r="41">
+      <x:c r="M41" s="51"/>
+    </x:row>
+    <x:row r="42">
+      <x:c r="M42" s="51"/>
+    </x:row>
+    <x:row r="43">
+      <x:c r="M43" s="51"/>
+    </x:row>
+    <x:row r="44">
+      <x:c r="M44" s="51"/>
+    </x:row>
+    <x:row r="45">
+      <x:c r="M45" s="51"/>
+    </x:row>
+    <x:row r="46">
+      <x:c r="M46" s="51"/>
+    </x:row>
+    <x:row r="47">
+      <x:c r="M47" s="51"/>
+    </x:row>
+    <x:row r="48">
+      <x:c r="M48" s="51"/>
+    </x:row>
+    <x:row r="49">
+      <x:c r="M49" s="51"/>
+    </x:row>
+    <x:row r="50">
+      <x:c r="M50" s="51"/>
+    </x:row>
+    <x:row r="51">
+      <x:c r="M51" s="51"/>
+    </x:row>
+    <x:row r="52">
+      <x:c r="M52" s="51"/>
+    </x:row>
+    <x:row r="53">
+      <x:c r="M53" s="51"/>
+    </x:row>
+    <x:row r="54">
+      <x:c r="M54" s="51"/>
+    </x:row>
+    <x:row r="55">
+      <x:c r="M55" s="51"/>
+    </x:row>
+    <x:row r="56">
+      <x:c r="M56" s="51"/>
+    </x:row>
+    <x:row r="57">
+      <x:c r="M57" s="51"/>
+    </x:row>
+    <x:row r="58">
+      <x:c r="M58" s="51"/>
+    </x:row>
+    <x:row r="59">
+      <x:c r="M59" s="51"/>
+    </x:row>
+    <x:row r="60">
+      <x:c r="M60" s="51"/>
+    </x:row>
+    <x:row r="61">
+      <x:c r="M61" s="51"/>
+    </x:row>
+    <x:row r="62">
+      <x:c r="M62" s="51"/>
+    </x:row>
+    <x:row r="63">
+      <x:c r="M63" s="51"/>
+    </x:row>
+    <x:row r="64">
+      <x:c r="M64" s="51"/>
+    </x:row>
+    <x:row r="65">
+      <x:c r="M65" s="51"/>
+    </x:row>
+    <x:row r="66">
+      <x:c r="M66" s="51"/>
+    </x:row>
+    <x:row r="67">
+      <x:c r="M67" s="51"/>
+    </x:row>
+    <x:row r="68">
+      <x:c r="M68" s="51"/>
+    </x:row>
+    <x:row r="69">
+      <x:c r="M69" s="51"/>
+    </x:row>
+    <x:row r="70">
+      <x:c r="M70" s="51"/>
+    </x:row>
+    <x:row r="71">
+      <x:c r="M71" s="51"/>
+    </x:row>
+    <x:row r="72">
+      <x:c r="M72" s="51"/>
+    </x:row>
+    <x:row r="73">
+      <x:c r="M73" s="51"/>
+    </x:row>
+    <x:row r="74">
+      <x:c r="M74" s="51"/>
+    </x:row>
+    <x:row r="75">
+      <x:c r="M75" s="51"/>
+    </x:row>
+    <x:row r="76">
+      <x:c r="M76" s="51"/>
+    </x:row>
+    <x:row r="77">
+      <x:c r="M77" s="51"/>
+    </x:row>
+    <x:row r="78">
+      <x:c r="M78" s="51"/>
+    </x:row>
+    <x:row r="79">
+      <x:c r="M79" s="51"/>
+    </x:row>
+    <x:row r="80">
+      <x:c r="M80" s="51"/>
+    </x:row>
+    <x:row r="81">
+      <x:c r="M81" s="51"/>
+    </x:row>
+    <x:row r="82">
+      <x:c r="M82" s="51"/>
+    </x:row>
+    <x:row r="83">
+      <x:c r="M83" s="51"/>
+    </x:row>
+    <x:row r="84">
+      <x:c r="M84" s="51"/>
+    </x:row>
+    <x:row r="85">
+      <x:c r="M85" s="51"/>
+    </x:row>
+    <x:row r="86">
+      <x:c r="M86" s="51"/>
+    </x:row>
+    <x:row r="87">
+      <x:c r="M87" s="51"/>
+    </x:row>
+    <x:row r="88">
+      <x:c r="M88" s="51"/>
+    </x:row>
+    <x:row r="89">
+      <x:c r="M89" s="51"/>
+    </x:row>
+    <x:row r="90">
+      <x:c r="M90" s="51"/>
+    </x:row>
+    <x:row r="91">
+      <x:c r="M91" s="51"/>
+    </x:row>
+    <x:row r="92">
+      <x:c r="M92" s="51"/>
+    </x:row>
+    <x:row r="93">
+      <x:c r="M93" s="51"/>
+    </x:row>
+    <x:row r="94">
+      <x:c r="M94" s="51"/>
+    </x:row>
+    <x:row r="95">
+      <x:c r="M95" s="51"/>
+    </x:row>
+    <x:row r="96">
+      <x:c r="M96" s="51"/>
+    </x:row>
+    <x:row r="97">
+      <x:c r="M97" s="51"/>
+    </x:row>
+    <x:row r="98">
+      <x:c r="M98" s="51"/>
+    </x:row>
+    <x:row r="99">
+      <x:c r="M99" s="51"/>
+    </x:row>
+    <x:row r="100">
+      <x:c r="M100" s="51"/>
+    </x:row>
+    <x:row r="101">
+      <x:c r="M101" s="51"/>
+    </x:row>
+    <x:row r="102">
+      <x:c r="M102" s="51"/>
+    </x:row>
+    <x:row r="103">
+      <x:c r="M103" s="51"/>
+    </x:row>
+    <x:row r="104">
+      <x:c r="M104" s="51"/>
+    </x:row>
+    <x:row r="105">
+      <x:c r="M105" s="51"/>
+    </x:row>
+    <x:row r="106">
+      <x:c r="M106" s="51"/>
+    </x:row>
+    <x:row r="107">
+      <x:c r="M107" s="51"/>
+    </x:row>
+    <x:row r="108">
+      <x:c r="M108" s="51"/>
+    </x:row>
+    <x:row r="109">
+      <x:c r="M109" s="51"/>
+    </x:row>
+    <x:row r="110">
+      <x:c r="M110" s="51"/>
+    </x:row>
+    <x:row r="111">
+      <x:c r="M111" s="51"/>
+    </x:row>
+    <x:row r="112">
+      <x:c r="M112" s="51"/>
+    </x:row>
+    <x:row r="113">
+      <x:c r="M113" s="51"/>
+    </x:row>
+    <x:row r="114">
+      <x:c r="M114" s="51"/>
+    </x:row>
+    <x:row r="115">
+      <x:c r="M115" s="51"/>
+    </x:row>
+    <x:row r="116">
+      <x:c r="M116" s="51"/>
+    </x:row>
+    <x:row r="117">
+      <x:c r="M117" s="51"/>
+    </x:row>
+    <x:row r="118">
+      <x:c r="M118" s="51"/>
+    </x:row>
+    <x:row r="119">
+      <x:c r="M119" s="51"/>
+    </x:row>
+    <x:row r="120">
+      <x:c r="M120" s="51"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -11777,7 +13223,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd35913e5d3dc4c12"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R72281e62d3ee4315"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11890,7 +13336,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd5c0a94cfd5641b6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R622362d2c9f24cce"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/physik/svphysik.xlsx
+++ b/physik/svphysik.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Übersicht" sheetId="1" r:id="Rd6c2765e854a452d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gesamtplan Physik" sheetId="2" r:id="Rb486fcc6283d47d7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Physik 7" sheetId="3" r:id="R54eb322bbaba4137"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Physik 8" sheetId="4" r:id="R55906025aec74ba6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Physik 9" sheetId="5" r:id="Rb06684665ed64a9c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Physik 10" sheetId="6" r:id="R8df82953b64f454e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Astronomie 10" sheetId="7" r:id="R12522782c7ec4058"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quellen" sheetId="8" r:id="Rc4e5e0f42c984d95"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Übersicht" sheetId="1" r:id="Ra0fff5dc053448a0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gesamtplan Physik" sheetId="2" r:id="R995ec4d7e5a44428"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Physik 7" sheetId="3" r:id="R85efe047f0ab4a64"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Physik 8" sheetId="4" r:id="R63d4341e2dba4c66"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Physik 9" sheetId="5" r:id="R64adf585f3e44990"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Physik 10" sheetId="6" r:id="R4701a496c458424d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Astronomie 10" sheetId="7" r:id="Rb2dda9fec54d4913"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quellen" sheetId="8" r:id="R2e02c7e3f51e44ed"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -962,7 +962,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R72860fcbacb44250"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R119824900c964f42"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1476,7 +1476,7 @@
     <x:mergeCell ref="A3:H3"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbb7d8a48b4f34861"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb100f990b1b54e92"/>
 </x:worksheet>
 </file>
 
@@ -1613,13 +1613,13 @@
         <x:v>keiner</x:v>
       </x:c>
       <x:c r="K5" s="57" t="str">
-        <x:v>ph_k7_st01_was_ist_physik</x:v>
+        <x:v>ph_k7_st01_was_ist_physik_beobachten_und_beschreiben</x:v>
       </x:c>
       <x:c r="L5" s="57" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/096_physik_titelseite.jpg</x:v>
       </x:c>
       <x:c r="M5" s="156" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st01_was_ist_physik_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_01_was_ist_physik.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N5" s="157" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st01_was_ist_physik_beobachten_und_beschreiben_orga.html","Vorbereitung öffnen")</x:f>
@@ -1658,13 +1658,13 @@
         <x:v>Reaktionszeitmessung mit Taster und LED als Vergleichsstation</x:v>
       </x:c>
       <x:c r="K6" s="60" t="str">
-        <x:v>ph_k7_st02_messen_und_protokollieren</x:v>
+        <x:v>ph_k7_st02_messen_und_protokollieren_die_reaktionszeit</x:v>
       </x:c>
       <x:c r="L6" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/074_messgeraete.jpg</x:v>
       </x:c>
       <x:c r="M6" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st02_messen_und_protokollieren_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_02_messen_und_protokollieren.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N6" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st02_messen_und_protokollieren_die_reaktionszeit_orga.html","Vorbereitung öffnen")</x:f>
@@ -1703,13 +1703,13 @@
         <x:v>keiner</x:v>
       </x:c>
       <x:c r="K7" s="60" t="str">
-        <x:v>ph_k7_st03_lichtquellen_und_lichtausbreitung</x:v>
+        <x:v>ph_k7_st03_lichtquellen_und_die_geradlinige_ausbreitung_des_lichts</x:v>
       </x:c>
       <x:c r="L7" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/034_arduino_licht_optik.jpg</x:v>
       </x:c>
       <x:c r="M7" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st03_lichtquellen_und_lichtausbreitung_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_03_lichtquellen_und_lichtausbreitung.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N7" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st03_lichtquellen_und_die_geradlinige_ausbreitung_des_lichts_orga.html","Vorbereitung öffnen")</x:f>
@@ -1748,13 +1748,13 @@
         <x:v>Helligkeitsmessung in Kernschatten, Halbschatten und beleuchteter Fläche (Lehrerdemonstration)</x:v>
       </x:c>
       <x:c r="K8" s="60" t="str">
-        <x:v>ph_k7_st04_licht_und_schatten</x:v>
+        <x:v>ph_k7_st04_licht_und_schatten_kernschatten_und_halbschatten</x:v>
       </x:c>
       <x:c r="L8" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/034_arduino_licht_optik.jpg</x:v>
       </x:c>
       <x:c r="M8" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st04_licht_und_schatten_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_04_licht_und_schatten.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N8" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st04_licht_und_schatten_kernschatten_und_halbschatten_orga.html","Vorbereitung öffnen")</x:f>
@@ -1793,13 +1793,13 @@
         <x:v>keiner</x:v>
       </x:c>
       <x:c r="K9" s="60" t="str">
-        <x:v>ph_k7_st05_mondphasen</x:v>
+        <x:v>ph_k7_st05_mondphasen_und_finsternisse_schatten_im_weltall</x:v>
       </x:c>
       <x:c r="L9" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/009_mondphasen.jpg</x:v>
       </x:c>
       <x:c r="M9" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st05_mondphasen_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_05_mondphasen_und_finsternisse.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N9" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st05_mondphasen_und_finsternisse_schatten_im_weltall_orga.html","Vorbereitung öffnen")</x:f>
@@ -1838,13 +1838,13 @@
         <x:v>keiner</x:v>
       </x:c>
       <x:c r="K10" s="60" t="str">
-        <x:v>ph_k7_st06_reflexion</x:v>
+        <x:v>ph_k7_st06_reflexion_und_das_spiegelgesetz_lichtstrahlen_andern_die_richtung</x:v>
       </x:c>
       <x:c r="L10" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/035_reflexion_spiegel.jpg</x:v>
       </x:c>
       <x:c r="M10" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st06_reflexion_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_06_reflexion_spiegelgesetz.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N10" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st06_reflexion_und_das_spiegelgesetz_lichtstrahlen_andern_die_richtung_orga.html","Vorbereitung öffnen")</x:f>
@@ -1883,13 +1883,13 @@
         <x:v>keiner</x:v>
       </x:c>
       <x:c r="K11" s="60" t="str">
-        <x:v>ph_k7_st07_spiegelbilder</x:v>
+        <x:v>ph_k7_st07_spiegelbilder_wie_entsteht_das_bild_im_spiegel</x:v>
       </x:c>
       <x:c r="L11" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/035_reflexion_spiegel.jpg</x:v>
       </x:c>
       <x:c r="M11" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st07_spiegelbilder_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_07_spiegelbilder.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N11" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st07_spiegelbilder_wie_entsteht_das_bild_im_spiegel_orga.html","Vorbereitung öffnen")</x:f>
@@ -1928,13 +1928,13 @@
         <x:v>keiner</x:v>
       </x:c>
       <x:c r="K12" s="60" t="str">
-        <x:v>ph_k7_st08_brechung</x:v>
+        <x:v>ph_k7_st08_brechung_und_linsen_licht_andert_die_richtung_in_glas</x:v>
       </x:c>
       <x:c r="L12" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/006_lichtbrechung.jpg</x:v>
       </x:c>
       <x:c r="M12" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st08_brechung_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_08_brechung_linsen.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N12" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st08_brechung_und_linsen_licht_andert_die_richtung_in_glas_orga.html","Vorbereitung öffnen")</x:f>
@@ -1973,13 +1973,13 @@
         <x:v>keiner</x:v>
       </x:c>
       <x:c r="K13" s="60" t="str">
-        <x:v>ph_k7_st09_waerme</x:v>
+        <x:v>ph_k7_st09_warme_und_temperatur_zwei_verschiedene_groen</x:v>
       </x:c>
       <x:c r="L13" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/026_temperatur_waerme.jpg</x:v>
       </x:c>
       <x:c r="M13" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st09_waerme_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_09_waerme_temperatur.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N13" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st09_warme_und_temperatur_zwei_verschiedene_groen_orga.html","Vorbereitung öffnen")</x:f>
@@ -2018,13 +2018,13 @@
         <x:v>keiner</x:v>
       </x:c>
       <x:c r="K14" s="60" t="str">
-        <x:v>ph_k7_st10_waermeleitung</x:v>
+        <x:v>ph_k7_st10_warmeleitung_und_warmestrahlung_wie_warme_sich_ausbreitet</x:v>
       </x:c>
       <x:c r="L14" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/042_radioaktivitaet.jpg</x:v>
       </x:c>
       <x:c r="M14" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st10_waermeleitung_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_10_waermeleitung_waermestrahlung.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N14" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st10_warmeleitung_und_warmestrahlung_wie_warme_sich_ausbreitet_orga.html","Vorbereitung öffnen")</x:f>
@@ -2063,13 +2063,13 @@
         <x:v>nein</x:v>
       </x:c>
       <x:c r="K15" s="60" t="str">
-        <x:v>ph_k7_st11_stromkreis</x:v>
+        <x:v>ph_k7_st11_der_stromkreis_und_der_schalter</x:v>
       </x:c>
       <x:c r="L15" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/001_stromkreis.jpg</x:v>
       </x:c>
       <x:c r="M15" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st11_stromkreis_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_11_stromkreis.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N15" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st11_der_stromkreis_und_der_schalter_orga.html","Vorbereitung öffnen")</x:f>
@@ -2108,13 +2108,13 @@
         <x:v>nein</x:v>
       </x:c>
       <x:c r="K16" s="60" t="str">
-        <x:v>ph_k7_st12_reihen_parallel</x:v>
+        <x:v>ph_k7_st12_reihen_und_parallelschaltung</x:v>
       </x:c>
       <x:c r="L16" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/012_parallelschaltung.jpg</x:v>
       </x:c>
       <x:c r="M16" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st12_reihen_parallel_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_12_reihen_parallel.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N16" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st12_reihen_und_parallelschaltung_orga.html","Vorbereitung öffnen")</x:f>
@@ -2153,13 +2153,13 @@
         <x:v>nein</x:v>
       </x:c>
       <x:c r="K17" s="60" t="str">
-        <x:v>ph_k7_st13_leistung</x:v>
+        <x:v>ph_k7_st13_elektrische_leistung_wie_viel_energie_verbrauchen_gerate</x:v>
       </x:c>
       <x:c r="L17" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/038_arbeit_leistung.jpg</x:v>
       </x:c>
       <x:c r="M17" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st13_leistung_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_13_leistung.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N17" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st13_elektrische_leistung_wie_viel_energie_verbrauchen_gerate_orga.html","Vorbereitung öffnen")</x:f>
@@ -2198,13 +2198,13 @@
         <x:v>nein</x:v>
       </x:c>
       <x:c r="K18" s="60" t="str">
-        <x:v>ph_k7_st14_sicherheit</x:v>
+        <x:v>ph_k7_st14_sicherheit_im_stromkreis_schutz_vor_uberlastung_und_kurzschluss</x:v>
       </x:c>
       <x:c r="L18" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/001_stromkreis.jpg</x:v>
       </x:c>
       <x:c r="M18" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st14_sicherheit_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_14_sicherheit.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N18" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st14_sicherheit_im_stromkreis_schutz_vor_uberlastung_und_kurzschluss_orga.html","Vorbereitung öffnen")</x:f>
@@ -2243,13 +2243,13 @@
         <x:v>entfällt</x:v>
       </x:c>
       <x:c r="K19" s="60" t="str">
-        <x:v>ph_k7_st19_mechanische_arbeit</x:v>
+        <x:v>ph_k7_st19_die_mechanische_arbeit_kraft_mal_weg</x:v>
       </x:c>
       <x:c r="L19" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/021_kraft_gewicht.jpg</x:v>
       </x:c>
       <x:c r="M19" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st19_mechanische_arbeit_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_19_mechanische_arbeit.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N19" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st19_die_mechanische_arbeit_kraft_mal_weg_orga.html","Vorbereitung öffnen")</x:f>
@@ -2288,13 +2288,13 @@
         <x:v>Automatische Zeitmessung des Hubvorgangs zwischen zwei Höhenschwellen zur Berechnung der Leistung (Lehrerdemonstration)</x:v>
       </x:c>
       <x:c r="K20" s="60" t="str">
-        <x:v>ph_k7_st20_leistung</x:v>
+        <x:v>ph_k7_st20_die_leistung_arbeit_pro_zeit</x:v>
       </x:c>
       <x:c r="L20" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/038_arbeit_leistung.jpg</x:v>
       </x:c>
       <x:c r="M20" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st20_leistung_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_20_leistung.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N20" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st20_die_leistung_arbeit_pro_zeit_orga.html","Vorbereitung öffnen")</x:f>
@@ -2333,13 +2333,13 @@
         <x:v>entfällt</x:v>
       </x:c>
       <x:c r="K21" s="60" t="str">
-        <x:v>ph_k7_st21_energieformen</x:v>
+        <x:v>ph_k7_st21_energie_und_energieformen_lageenergie_und_bewegungsenergie</x:v>
       </x:c>
       <x:c r="L21" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/023_gleichfoermige_bewegung.jpg</x:v>
       </x:c>
       <x:c r="M21" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st21_energieformen_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_21_energieformen.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N21" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st21_energie_und_energieformen_lageenergie_und_bewegungsenergie_orga.html","Vorbereitung öffnen")</x:f>
@@ -2378,13 +2378,13 @@
         <x:v>Helligkeitsmessung zweier Leuchtmittel mit stark unterschiedlicher Leistung bei gleichem Abstand (Lehrerdemonstration)</x:v>
       </x:c>
       <x:c r="K22" s="60" t="str">
-        <x:v>ph_k7_st22_energiesparen</x:v>
+        <x:v>ph_k7_st22_energie_sparen_im_alltag_leuchtmittel_im_vergleich</x:v>
       </x:c>
       <x:c r="L22" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/090_physik_klassenraum.jpg</x:v>
       </x:c>
       <x:c r="M22" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st22_energiesparen_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_22_energiesparen.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N22" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st22_energie_sparen_im_alltag_leuchtmittel_im_vergleich_orga.html","Vorbereitung öffnen")</x:f>
@@ -2423,13 +2423,13 @@
         <x:v>entfällt</x:v>
       </x:c>
       <x:c r="K23" s="60" t="str">
-        <x:v>ph_k7_st23_wiederholung</x:v>
+        <x:v>ph_k7_st23_wiederholung_und_vertiefung_arbeit_leistung_energie</x:v>
       </x:c>
       <x:c r="L23" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/038_arbeit_leistung.jpg</x:v>
       </x:c>
       <x:c r="M23" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st23_wiederholung_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_23_wiederholung.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N23" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st23_wiederholung_und_vertiefung_arbeit_leistung_energie_orga.html","Vorbereitung öffnen")</x:f>
@@ -2468,13 +2468,13 @@
         <x:v>Automatisierte Messung des Wasserstands vor und nach dem Eintauchen eines Körpers zur Bestimmung seines Volumens (Schülerexperiment)</x:v>
       </x:c>
       <x:c r="K24" s="60" t="str">
-        <x:v>ph_k7_st24_dichte</x:v>
+        <x:v>ph_k7_st24_masse_volumen_und_dichte</x:v>
       </x:c>
       <x:c r="L24" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/025_dichte_experiment.jpg</x:v>
       </x:c>
       <x:c r="M24" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st24_dichte_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_24_dichte.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N24" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st24_masse_volumen_und_dichte_orga.html","Vorbereitung öffnen")</x:f>
@@ -2513,13 +2513,13 @@
         <x:v>entfällt</x:v>
       </x:c>
       <x:c r="K25" s="60" t="str">
-        <x:v>ph_k7_st25_auftrieb</x:v>
+        <x:v>ph_k7_st25_auftrieb_warum_schwimmen_manche_dinge</x:v>
       </x:c>
       <x:c r="L25" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/081_auftrieb.jpg</x:v>
       </x:c>
       <x:c r="M25" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st25_auftrieb_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_25_auftrieb.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N25" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st25_auftrieb_warum_schwimmen_manche_dinge_orga.html","Vorbereitung öffnen")</x:f>
@@ -2558,13 +2558,13 @@
         <x:v>entfällt</x:v>
       </x:c>
       <x:c r="K26" s="60" t="str">
-        <x:v>ph_k8_st01_geschwindigkeit</x:v>
+        <x:v>ph_k8_st01_geschwindigkeit_was_bedeutet_schnell</x:v>
       </x:c>
       <x:c r="L26" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/023_gleichfoermige_bewegung.jpg</x:v>
       </x:c>
       <x:c r="M26" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st01_geschwindigkeit_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_01_geschwindigkeit.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N26" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st01_geschwindigkeit_was_bedeutet_schnell_orga.html","Vorbereitung öffnen")</x:f>
@@ -2603,13 +2603,13 @@
         <x:v>Fortlaufende Positionsmessung eines Wagens zur Erstellung eines Weg-Zeit-Diagramms (Lehrerdemonstration)</x:v>
       </x:c>
       <x:c r="K27" s="60" t="str">
-        <x:v>ph_k8_st02_weg_zeit_diagramm</x:v>
+        <x:v>ph_k8_st02_bewegungsarten_und_das_weg_zeit_diagramm</x:v>
       </x:c>
       <x:c r="L27" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/023_gleichfoermige_bewegung.jpg</x:v>
       </x:c>
       <x:c r="M27" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st02_weg_zeit_diagramm_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_02_weg_zeit_diagramm.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N27" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st02_bewegungsarten_und_das_weg_zeit_diagramm_orga.html","Vorbereitung öffnen")</x:f>
@@ -2648,13 +2648,13 @@
         <x:v>entfällt</x:v>
       </x:c>
       <x:c r="K28" s="60" t="str">
-        <x:v>ph_k8_st03_durchschnitt_moment</x:v>
+        <x:v>ph_k8_st03_durchschnitts_und_momentangeschwindigkeit</x:v>
       </x:c>
       <x:c r="L28" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/023_gleichfoermige_bewegung.jpg</x:v>
       </x:c>
       <x:c r="M28" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st03_durchschnitt_moment_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_03_durchschnitt_moment.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N28" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st03_durchschnitts_und_momentangeschwindigkeit_orga.html","Vorbereitung öffnen")</x:f>
@@ -2693,13 +2693,13 @@
         <x:v>Fortlaufende Positionsmessung zur Berechnung der Geschwindigkeitszunahme und daraus der Beschleunigung (Schülerexperiment)</x:v>
       </x:c>
       <x:c r="K29" s="60" t="str">
-        <x:v>ph_k8_st04_beschleunigung</x:v>
+        <x:v>ph_k8_st04_beschleunigung_wenn_sich_die_geschwindigkeit_andert</x:v>
       </x:c>
       <x:c r="L29" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/092_beschleunigung.jpg</x:v>
       </x:c>
       <x:c r="M29" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st04_beschleunigung_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_04_beschleunigung.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N29" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st04_beschleunigung_wenn_sich_die_geschwindigkeit_andert_orga.html","Vorbereitung öffnen")</x:f>
@@ -2744,7 +2744,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/097_formeln_uebersicht.jpg</x:v>
       </x:c>
       <x:c r="M30" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st09_wiederholung_dynamik_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_09_wiederholung_dynamik.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N30" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st09_wiederholung_dynamik_orga.html","Vorbereitung öffnen")</x:f>
@@ -2783,13 +2783,13 @@
         <x:v>Automatisierte Temperaturaufzeichnung beim Erhitzen von Eis bis zum Sieden zur Erstellung einer Erhitzungskurve (Lehrerdemonstration)</x:v>
       </x:c>
       <x:c r="K31" s="60" t="str">
-        <x:v>ph_k8_st10_aggregatzustaende</x:v>
+        <x:v>ph_k8_st10_aggregatzustande</x:v>
       </x:c>
       <x:c r="L31" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/026_temperatur_waerme.jpg</x:v>
       </x:c>
       <x:c r="M31" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st10_aggregatzustaende_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_10_aggregatzustaende.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N31" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st10_aggregatzustande_orga.html","Vorbereitung öffnen")</x:f>
@@ -2828,13 +2828,13 @@
         <x:v>entfällt</x:v>
       </x:c>
       <x:c r="K32" s="60" t="str">
-        <x:v>ph_k8_st11_waermeausdehnung</x:v>
+        <x:v>ph_k8_st11_warmeausdehnung</x:v>
       </x:c>
       <x:c r="L32" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/026_temperatur_waerme.jpg</x:v>
       </x:c>
       <x:c r="M32" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st11_waermeausdehnung_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_11_waermeausdehnung.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N32" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st11_warmeausdehnung_orga.html","Vorbereitung öffnen")</x:f>
@@ -2873,13 +2873,13 @@
         <x:v>Gleichzeitige, automatisierte Temperaturmessung zweier Stoffe zur Bestimmung der unterschiedlichen spezifischen Wärmekapazität (Schülerexperiment)</x:v>
       </x:c>
       <x:c r="K33" s="60" t="str">
-        <x:v>ph_k8_st12_waermekapazitaet</x:v>
+        <x:v>ph_k8_st12_warmemenge_und_spezifische_warmekapazitat</x:v>
       </x:c>
       <x:c r="L33" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/026_temperatur_waerme.jpg</x:v>
       </x:c>
       <x:c r="M33" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st12_waermekapazitaet_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_12_waermekapazitaet.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N33" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st12_warmemenge_und_spezifische_warmekapazitat_orga.html","Vorbereitung öffnen")</x:f>
@@ -2924,7 +2924,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/090_physik_klassenraum.jpg</x:v>
       </x:c>
       <x:c r="M34" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st17_magnetismus_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_17_magnetismus.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N34" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st17_magnetismus_orga.html","Vorbereitung öffnen")</x:f>
@@ -2969,7 +2969,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/018_kompass_erdmagnetfeld.jpg</x:v>
       </x:c>
       <x:c r="M35" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st18_kompass_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_18_kompass.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N35" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st18_kompass_orga.html","Vorbereitung öffnen")</x:f>
@@ -3014,7 +3014,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/019_elektromagnet.jpg</x:v>
       </x:c>
       <x:c r="M36" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st19_elektromagnet_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_19_elektromagnet.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N36" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st19_elektromagnet_orga.html","Vorbereitung öffnen")</x:f>
@@ -3059,7 +3059,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/043_induktion.jpg</x:v>
       </x:c>
       <x:c r="M37" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st20_induktion_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_20_induktion.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N37" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st20_induktion_orga.html","Vorbereitung öffnen")</x:f>
@@ -3104,7 +3104,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/097_formeln_uebersicht.jpg</x:v>
       </x:c>
       <x:c r="M38" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st21_wiederholung_magnetismus_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_21_wiederholung_magnetismus.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N38" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st21_wiederholung_magnetismus_orga.html","Vorbereitung öffnen")</x:f>
@@ -3149,7 +3149,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/005_tafelbild_ohm.jpg</x:v>
       </x:c>
       <x:c r="M39" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st22_ohmsches_gesetz_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_22_ohmsches_gesetz.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N39" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st22_ohmsches_gesetz_orga.html","Vorbereitung öffnen")</x:f>
@@ -3194,7 +3194,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/090_physik_klassenraum.jpg</x:v>
       </x:c>
       <x:c r="M40" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st23_reihe_parallel_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_23_reihe_parallel.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N40" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st23_reihe_parallel_orga.html","Vorbereitung öffnen")</x:f>
@@ -3239,7 +3239,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/038_arbeit_leistung.jpg</x:v>
       </x:c>
       <x:c r="M41" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st24_leistung_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_24_leistung.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N41" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st24_leistung_orga.html","Vorbereitung öffnen")</x:f>
@@ -3284,7 +3284,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/097_formeln_uebersicht.jpg</x:v>
       </x:c>
       <x:c r="M42" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st25_wiederholung_elektrizitaet_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_25_wiederholung_elektrizitaet.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N42" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st25_wiederholung_elektrizitaet_orga.html","Vorbereitung öffnen")</x:f>
@@ -3329,7 +3329,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/006_lichtbrechung.jpg</x:v>
       </x:c>
       <x:c r="M43" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st26_lichtbrechung_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_26_lichtbrechung.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N43" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st26_lichtbrechung_orga.html","Vorbereitung öffnen")</x:f>
@@ -3374,7 +3374,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/093_optische_instrumente.jpg</x:v>
       </x:c>
       <x:c r="M44" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st27_linsen_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_27_linsen.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N44" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st27_linsen_orga.html","Vorbereitung öffnen")</x:f>
@@ -3419,7 +3419,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/093_optische_instrumente.jpg</x:v>
       </x:c>
       <x:c r="M45" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st28_auge_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_28_auge.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N45" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st28_auge_orga.html","Vorbereitung öffnen")</x:f>
@@ -3464,7 +3464,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/097_formeln_uebersicht.jpg</x:v>
       </x:c>
       <x:c r="M46" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st29_wiederholung_optik_vertieft_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_29_wiederholung_optik_vertieft.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N46" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st29_wiederholung_optik_vertieft_orga.html","Vorbereitung öffnen")</x:f>
@@ -3509,7 +3509,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/097_formeln_uebersicht.jpg</x:v>
       </x:c>
       <x:c r="M47" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st30_gesamtwiederholung_klasse_8_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_30_gesamtwiederholung_klasse_8.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N47" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st30_gesamtwiederholung_klasse_8_orga.html","Vorbereitung öffnen")</x:f>
@@ -3554,7 +3554,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/017_magnet_feldlinien.jpg</x:v>
       </x:c>
       <x:c r="M48" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st01_magnetische_pole_und_kraftwirkungen_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_01_magnetische_pole_und_kraftwirkungen.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N48" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st01_magnetische_pole_und_kraftwirkungen_orga.html","Vorbereitung öffnen")</x:f>
@@ -3599,7 +3599,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/017_magnet_feldlinien.jpg</x:v>
       </x:c>
       <x:c r="M49" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st02_magnetfeld_und_feldlinienmodell_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_02_magnetfeld_und_feldlinienmodell.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N49" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st02_magnetfeld_und_feldlinienmodell_orga.html","Vorbereitung öffnen")</x:f>
@@ -3644,7 +3644,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/018_kompass_erdmagnetfeld.jpg</x:v>
       </x:c>
       <x:c r="M50" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st03_erdmagnetfeld_und_kompass_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_03_erdmagnetfeld_und_kompass.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N50" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st03_erdmagnetfeld_und_kompass_orga.html","Vorbereitung öffnen")</x:f>
@@ -3689,7 +3689,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/090_physik_klassenraum.jpg</x:v>
       </x:c>
       <x:c r="M51" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st04_elektrisches_und_magnetisches_feld_vergleichen_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_04_elektrisches_und_magnetisches_feld_vergleichen.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N51" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st04_elektrisches_und_magnetisches_feld_vergleichen_orga.html","Vorbereitung öffnen")</x:f>
@@ -3734,7 +3734,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/019_elektromagnet.jpg</x:v>
       </x:c>
       <x:c r="M52" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st05_elektromagnet_aufbau_und_wirkungsweise_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_05_elektromagnet_aufbau_und_wirkungsweise.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N52" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st05_elektromagnet_aufbau_und_wirkungsweise_orga.html","Vorbereitung öffnen")</x:f>
@@ -3773,13 +3773,13 @@
         <x:v>PWM-Stufen und Hall-Sensor zur relativen Feldmessung nutzen</x:v>
       </x:c>
       <x:c r="K53" s="60" t="str">
-        <x:v>ph_k9_st06_staerke_eines_elektromagneten_untersuchen</x:v>
+        <x:v>ph_k9_st06_starke_eines_elektromagneten_untersuchen</x:v>
       </x:c>
       <x:c r="L53" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/019_elektromagnet.jpg</x:v>
       </x:c>
       <x:c r="M53" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st06_staerke_eines_elektromagneten_untersuchen_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_06_staerke_eines_elektromagneten_untersuchen.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N53" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st06_starke_eines_elektromagneten_untersuchen_orga.html","Vorbereitung öffnen")</x:f>
@@ -3824,7 +3824,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/017_magnet_feldlinien.jpg</x:v>
       </x:c>
       <x:c r="M54" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st07_kraft_auf_einen_stromdurchflossenen_leiter_im_magnetfeld_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_07_kraft_auf_einen_stromdurchflossenen_leiter_im_magnetfeld.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N54" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st07_kraft_auf_einen_stromdurchflossenen_leiter_im_magnetfeld_orga.html","Vorbereitung öffnen")</x:f>
@@ -3869,7 +3869,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/044_generator_motor.jpg</x:v>
       </x:c>
       <x:c r="M55" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st08_elektromotor_elektrische_energie_erzeugt_bewegung_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_08_elektromotor_elektrische_energie_erzeugt_bewegung.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N55" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st08_elektromotor_elektrische_energie_erzeugt_bewegung_orga.html","Vorbereitung öffnen")</x:f>
@@ -3908,13 +3908,13 @@
         <x:v>Relaismodul mit Taster und Status-LED steuern</x:v>
       </x:c>
       <x:c r="K56" s="60" t="str">
-        <x:v>ph_k9_st09_relais_und_elektromagnetischer_tueroeffner</x:v>
+        <x:v>ph_k9_st09_relais_und_elektromagnetischer_turoffner</x:v>
       </x:c>
       <x:c r="L56" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/044_generator_motor.jpg</x:v>
       </x:c>
       <x:c r="M56" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st09_relais_und_elektromagnetischer_tueroeffner_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_09_relais_und_elektromagnetischer_tueroeffner.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N56" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st09_relais_und_elektromagnetischer_turoffner_orga.html","Vorbereitung öffnen")</x:f>
@@ -3959,7 +3959,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/044_generator_motor.jpg</x:v>
       </x:c>
       <x:c r="M57" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st10_lautsprecher_und_anwendungen_des_elektromagnetismus_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_10_lautsprecher_und_anwendungen_des_elektromagnetismus.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N57" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st10_lautsprecher_und_anwendungen_des_elektromagnetismus_orga.html","Vorbereitung öffnen")</x:f>
@@ -4004,7 +4004,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/023_gleichfoermige_bewegung.jpg</x:v>
       </x:c>
       <x:c r="M58" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st11_bewegung_bezugssystem_weg_und_zeit_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_11_bewegung_bezugssystem_weg_und_zeit.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N58" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st11_bewegung_bezugssystem_weg_und_zeit_orga.html","Vorbereitung öffnen")</x:f>
@@ -4049,7 +4049,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/023_gleichfoermige_bewegung.jpg</x:v>
       </x:c>
       <x:c r="M59" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st12_geschwindigkeit_messen_und_berechnen_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_12_geschwindigkeit_messen_und_berechnen.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N59" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st12_geschwindigkeit_messen_und_berechnen_orga.html","Vorbereitung öffnen")</x:f>
@@ -4088,13 +4088,13 @@
         <x:v>Weg-Zeit-Daten mit HC-SR04 protokollieren</x:v>
       </x:c>
       <x:c r="K60" s="60" t="str">
-        <x:v>ph_k9_st13_geradlinig_gleichfoermige_bewegung_und_s_t_diagramm</x:v>
+        <x:v>ph_k9_st13_geradlinig_gleichformige_bewegung_und_s_t_diagramm</x:v>
       </x:c>
       <x:c r="L60" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/023_gleichfoermige_bewegung.jpg</x:v>
       </x:c>
       <x:c r="M60" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st13_geradlinig_gleichfoermige_bewegung_und_s_t_diagramm_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_13_geradlinig_gleichfoermige_bewegung_und_s_t_diagramm.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N60" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st13_geradlinig_gleichformige_bewegung_und_s_t_diagramm_orga.html","Vorbereitung öffnen")</x:f>
@@ -4133,13 +4133,13 @@
         <x:v>—</x:v>
       </x:c>
       <x:c r="K61" s="60" t="str">
-        <x:v>ph_k9_st14_gleichfoermige_bewegung_gleichungen_und_diagramme_anwenden</x:v>
+        <x:v>ph_k9_st14_gleichformige_bewegung_gleichungen_und_diagramme_anwenden</x:v>
       </x:c>
       <x:c r="L61" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/023_gleichfoermige_bewegung.jpg</x:v>
       </x:c>
       <x:c r="M61" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st14_gleichfoermige_bewegung_gleichungen_und_diagramme_anwenden_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_14_gleichfoermige_bewegung_gleichungen_und_diagramme_anwenden.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N61" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st14_gleichformige_bewegung_gleichungen_und_diagramme_anwenden_orga.html","Vorbereitung öffnen")</x:f>
@@ -4178,13 +4178,13 @@
         <x:v>Beschleunigungswerte mit MPU6050 als Rohdaten erfassen</x:v>
       </x:c>
       <x:c r="K62" s="60" t="str">
-        <x:v>ph_k9_st15_beschleunigung_als_aenderung_der_geschwindigkeit</x:v>
+        <x:v>ph_k9_st15_beschleunigung_als_anderung_der_geschwindigkeit</x:v>
       </x:c>
       <x:c r="L62" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/092_beschleunigung.jpg</x:v>
       </x:c>
       <x:c r="M62" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st15_beschleunigung_als_aenderung_der_geschwindigkeit_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_15_beschleunigung_als_aenderung_der_geschwindigkeit.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N62" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st15_beschleunigung_als_anderung_der_geschwindigkeit_orga.html","Vorbereitung öffnen")</x:f>
@@ -4223,13 +4223,13 @@
         <x:v>Beschleunigungsdaten mit MPU6050 aufzeichnen und mitteln</x:v>
       </x:c>
       <x:c r="K63" s="60" t="str">
-        <x:v>ph_k9_st16_geradlinig_gleichmaessig_beschleunigte_bewegung</x:v>
+        <x:v>ph_k9_st16_geradlinig_gleichmaig_beschleunigte_bewegung</x:v>
       </x:c>
       <x:c r="L63" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/023_gleichfoermige_bewegung.jpg</x:v>
       </x:c>
       <x:c r="M63" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st16_geradlinig_gleichmaessig_beschleunigte_bewegung_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_16_geradlinig_gleichmaessig_beschleunigte_bewegung.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N63" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st16_geradlinig_gleichmaig_beschleunigte_bewegung_orga.html","Vorbereitung öffnen")</x:f>
@@ -4274,7 +4274,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/092_beschleunigung.jpg</x:v>
       </x:c>
       <x:c r="M64" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st17_freier_fall_als_beschleunigte_bewegung_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_17_freier_fall_als_beschleunigte_bewegung.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N64" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st17_freier_fall_als_beschleunigte_bewegung_orga.html","Vorbereitung öffnen")</x:f>
@@ -4319,7 +4319,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/023_gleichfoermige_bewegung.jpg</x:v>
       </x:c>
       <x:c r="M65" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st18_bewegungsformen_bewegungsarten_und_verkehrssicherheit_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_18_bewegungsformen_bewegungsarten_und_verkehrssicherheit.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N65" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st18_bewegungsformen_bewegungsarten_und_verkehrssicherheit_orga.html","Vorbereitung öffnen")</x:f>
@@ -4358,13 +4358,13 @@
         <x:v>Kraft mit Wägezelle und HX711 nach Kalibrierung messen</x:v>
       </x:c>
       <x:c r="K66" s="60" t="str">
-        <x:v>ph_k9_st19_kraft_als_wechselwirkung_und_physikalische_groesse</x:v>
+        <x:v>ph_k9_st19_kraft_als_wechselwirkung_und_physikalische_groe</x:v>
       </x:c>
       <x:c r="L66" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/024_newton_krafte.jpg</x:v>
       </x:c>
       <x:c r="M66" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st19_kraft_als_wechselwirkung_und_physikalische_groesse_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_19_kraft_als_wechselwirkung_und_physikalische_groesse.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N66" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st19_kraft_als_wechselwirkung_und_physikalische_groe_orga.html","Vorbereitung öffnen")</x:f>
@@ -4403,13 +4403,13 @@
         <x:v>—</x:v>
       </x:c>
       <x:c r="K67" s="60" t="str">
-        <x:v>ph_k9_st20_erstes_newtonsches_gesetz_traegheit</x:v>
+        <x:v>ph_k9_st20_erstes_newtonsches_gesetz_tragheit</x:v>
       </x:c>
       <x:c r="L67" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/024_newton_krafte.jpg</x:v>
       </x:c>
       <x:c r="M67" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st20_erstes_newtonsches_gesetz_traegheit_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_20_erstes_newtonsches_gesetz_traegheit.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N67" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st20_erstes_newtonsches_gesetz_tragheit_orga.html","Vorbereitung öffnen")</x:f>
@@ -4454,7 +4454,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/092_beschleunigung.jpg</x:v>
       </x:c>
       <x:c r="M68" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st21_zweites_newtonsches_gesetz_kraft_masse_und_beschleunigung_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_21_zweites_newtonsches_gesetz_kraft_masse_und_beschleunigung.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N68" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st21_zweites_newtonsches_gesetz_kraft_masse_und_beschleunigung_orga.html","Vorbereitung öffnen")</x:f>
@@ -4499,7 +4499,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/024_newton_krafte.jpg</x:v>
       </x:c>
       <x:c r="M69" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st22_drittes_newtonsches_gesetz_actio_und_reactio_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_22_drittes_newtonsches_gesetz_actio_und_reactio.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N69" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st22_drittes_newtonsches_gesetz_actio_und_reactio_orga.html","Vorbereitung öffnen")</x:f>
@@ -4544,7 +4544,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/091_gravitation.jpg</x:v>
       </x:c>
       <x:c r="M70" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st23_gravitation_masse_und_gewichtskraft_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_23_gravitation_masse_und_gewichtskraft.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N70" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st23_gravitation_masse_und_gewichtskraft_orga.html","Vorbereitung öffnen")</x:f>
@@ -4583,13 +4583,13 @@
         <x:v>Wahlstationen mit Ultraschall, Lichtschranke oder Wägezelle</x:v>
       </x:c>
       <x:c r="K71" s="60" t="str">
-        <x:v>ph_k9_st24_projekt_und_lernkontrolle_bewegungen_und_kraefte_im_alltag</x:v>
+        <x:v>ph_k9_st24_projekt_und_lernkontrolle_bewegungen_und_krafte_im_alltag</x:v>
       </x:c>
       <x:c r="L71" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/023_gleichfoermige_bewegung.jpg</x:v>
       </x:c>
       <x:c r="M71" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st24_projekt_und_lernkontrolle_bewegungen_und_kraefte_im_alltag_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_24_projekt_und_lernkontrolle_bewegungen_und_kraefte_im_alltag.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N71" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st24_projekt_und_lernkontrolle_bewegungen_und_krafte_im_alltag_orga.html","Vorbereitung öffnen")</x:f>
@@ -4628,13 +4628,13 @@
         <x:v>Magnetfeld mit linearem Hall-Sensor erfassen</x:v>
       </x:c>
       <x:c r="K72" s="60" t="str">
-        <x:v>ph_k10_st01_magnetische_pole_kraefte_und_erdmagnetfeld</x:v>
+        <x:v>ph_k10_st01_magnetische_pole_krafte_und_erdmagnetfeld</x:v>
       </x:c>
       <x:c r="L72" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/018_kompass_erdmagnetfeld.jpg</x:v>
       </x:c>
       <x:c r="M72" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st01_magnetische_pole_kraefte_und_erdmagnetfeld_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_01_magnetische_pole_kraefte_und_erdmagnetfeld.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N72" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st01_magnetische_pole_krafte_und_erdmagnetfeld_orga.html","Vorbereitung öffnen")</x:f>
@@ -4679,7 +4679,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/090_physik_klassenraum.jpg</x:v>
       </x:c>
       <x:c r="M73" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st02_elektrisches_und_magnetisches_feld_vergleichen_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_02_elektrisches_und_magnetisches_feld_vergleichen.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N73" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st02_elektrisches_und_magnetisches_feld_vergleichen_orga.html","Vorbereitung öffnen")</x:f>
@@ -4718,13 +4718,13 @@
         <x:v>zeitgesteuerte Ansteuerung über MOSFET-Modul und Strommessung</x:v>
       </x:c>
       <x:c r="K74" s="60" t="str">
-        <x:v>ph_k10_st03_elektromagnet_windungszahl_stromstaerke_und_eisenkern</x:v>
+        <x:v>ph_k10_st03_elektromagnet_windungszahl_stromstarke_und_eisenkern</x:v>
       </x:c>
       <x:c r="L74" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/019_elektromagnet.jpg</x:v>
       </x:c>
       <x:c r="M74" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st03_elektromagnet_windungszahl_stromstaerke_und_eisenkern_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_03_elektromagnet_windungszahl_stromstaerke_und_eisenkern.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N74" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st03_elektromagnet_windungszahl_stromstarke_und_eisenkern_orga.html","Vorbereitung öffnen")</x:f>
@@ -4769,7 +4769,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/019_elektromagnet.jpg</x:v>
       </x:c>
       <x:c r="M75" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st04_kraft_auf_einen_stromdurchflossenen_leiter_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_04_kraft_auf_einen_stromdurchflossenen_leiter.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N75" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st04_kraft_auf_einen_stromdurchflossenen_leiter_orga.html","Vorbereitung öffnen")</x:f>
@@ -4814,7 +4814,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/044_generator_motor.jpg</x:v>
       </x:c>
       <x:c r="M76" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st05_elektromotor_lautsprecher_und_relais_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_05_elektromotor_lautsprecher_und_relais.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N76" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st05_elektromotor_lautsprecher_und_relais_orga.html","Vorbereitung öffnen")</x:f>
@@ -4859,7 +4859,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/043_induktion.jpg</x:v>
       </x:c>
       <x:c r="M77" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st06_elektromagnetische_induktion_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_06_elektromagnetische_induktion.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N77" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st06_elektromagnetische_induktion_orga.html","Vorbereitung öffnen")</x:f>
@@ -4904,7 +4904,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/044_generator_motor.jpg</x:v>
       </x:c>
       <x:c r="M78" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st07_generator_und_wechselspannung_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_07_generator_und_wechselspannung.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N78" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st07_generator_und_wechselspannung_orga.html","Vorbereitung öffnen")</x:f>
@@ -4949,7 +4949,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/045_transformator.jpg</x:v>
       </x:c>
       <x:c r="M79" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st08_transformator_und_stromverbundnetz_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_08_transformator_und_stromverbundnetz.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N79" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st08_transformator_und_stromverbundnetz_orga.html","Vorbereitung öffnen")</x:f>
@@ -4994,7 +4994,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/023_gleichfoermige_bewegung.jpg</x:v>
       </x:c>
       <x:c r="M80" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st09_bewegung_bezugssystem_weg_zeit_und_geschwindigkeit_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_09_bewegung_bezugssystem_weg_zeit_und_geschwindigkeit.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N80" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st09_bewegung_bezugssystem_weg_zeit_und_geschwindigkeit_orga.html","Vorbereitung öffnen")</x:f>
@@ -5033,13 +5033,13 @@
         <x:v>Ultraschall-Datenlogger</x:v>
       </x:c>
       <x:c r="K81" s="60" t="str">
-        <x:v>ph_k10_st10_geradlinig_gleichfoermige_bewegung_und_diagramme</x:v>
+        <x:v>ph_k10_st10_geradlinig_gleichformige_bewegung_und_diagramme</x:v>
       </x:c>
       <x:c r="L81" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/023_gleichfoermige_bewegung.jpg</x:v>
       </x:c>
       <x:c r="M81" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st10_geradlinig_gleichfoermige_bewegung_und_diagramme_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_10_geradlinig_gleichfoermige_bewegung_und_diagramme.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N81" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st10_geradlinig_gleichformige_bewegung_und_diagramme_orga.html","Vorbereitung öffnen")</x:f>
@@ -5078,13 +5078,13 @@
         <x:v>Ultraschall-Datenlogger</x:v>
       </x:c>
       <x:c r="K82" s="60" t="str">
-        <x:v>ph_k10_st11_geradlinig_gleichmaessig_beschleunigte_bewegung</x:v>
+        <x:v>ph_k10_st11_geradlinig_gleichmaig_beschleunigte_bewegung</x:v>
       </x:c>
       <x:c r="L82" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/023_gleichfoermige_bewegung.jpg</x:v>
       </x:c>
       <x:c r="M82" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st11_geradlinig_gleichmaessig_beschleunigte_bewegung_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_11_geradlinig_gleichmaessig_beschleunigte_bewegung.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N82" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st11_geradlinig_gleichmaig_beschleunigte_bewegung_orga.html","Vorbereitung öffnen")</x:f>
@@ -5129,7 +5129,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/092_beschleunigung.jpg</x:v>
       </x:c>
       <x:c r="M83" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st12_freier_fall_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_12_freier_fall.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N83" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st12_freier_fall_orga.html","Vorbereitung öffnen")</x:f>
@@ -5168,13 +5168,13 @@
         <x:v>nein</x:v>
       </x:c>
       <x:c r="K84" s="60" t="str">
-        <x:v>ph_k10_st13_erstes_newtonsches_gesetz_und_traegheit</x:v>
+        <x:v>ph_k10_st13_erstes_newtonsches_gesetz_und_tragheit</x:v>
       </x:c>
       <x:c r="L84" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/024_newton_krafte.jpg</x:v>
       </x:c>
       <x:c r="M84" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st13_erstes_newtonsches_gesetz_und_traegheit_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_13_erstes_newtonsches_gesetz_und_traegheit.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N84" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st13_erstes_newtonsches_gesetz_und_tragheit_orga.html","Vorbereitung öffnen")</x:f>
@@ -5219,7 +5219,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/024_newton_krafte.jpg</x:v>
       </x:c>
       <x:c r="M85" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st14_zweites_newtonsches_gesetz_f_m_a_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_14_zweites_newtonsches_gesetz_f_m_a.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N85" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st14_zweites_newtonsches_gesetz_f_m_a_orga.html","Vorbereitung öffnen")</x:f>
@@ -5264,7 +5264,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/024_newton_krafte.jpg</x:v>
       </x:c>
       <x:c r="M86" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st15_drittes_newtonsches_gesetz_actio_und_reactio_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_15_drittes_newtonsches_gesetz_actio_und_reactio.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N86" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st15_drittes_newtonsches_gesetz_actio_und_reactio_orga.html","Vorbereitung öffnen")</x:f>
@@ -5309,7 +5309,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/004_sonnensystem.jpg</x:v>
       </x:c>
       <x:c r="M87" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st16_gravitation_gewichtskraft_und_planetenbewegung_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_16_gravitation_gewichtskraft_und_planetenbewegung.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N87" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st16_gravitation_gewichtskraft_und_planetenbewegung_orga.html","Vorbereitung öffnen")</x:f>
@@ -5348,13 +5348,13 @@
         <x:v>Drehzahlmessung mit Hall-Sensor</x:v>
       </x:c>
       <x:c r="K88" s="60" t="str">
-        <x:v>ph_k10_st17_gleichfoermige_kreisbewegung</x:v>
+        <x:v>ph_k10_st17_gleichformige_kreisbewegung</x:v>
       </x:c>
       <x:c r="L88" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/023_gleichfoermige_bewegung.jpg</x:v>
       </x:c>
       <x:c r="M88" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st17_gleichfoermige_kreisbewegung_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_17_gleichfoermige_kreisbewegung.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N88" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st17_gleichformige_kreisbewegung_orga.html","Vorbereitung öffnen")</x:f>
@@ -5393,13 +5393,13 @@
         <x:v>Abstandssensor zeichnet Schwingung auf</x:v>
       </x:c>
       <x:c r="K89" s="60" t="str">
-        <x:v>ph_k10_st18_schwingungen_und_ihre_kenngroessen</x:v>
+        <x:v>ph_k10_st18_schwingungen_und_ihre_kenngroen</x:v>
       </x:c>
       <x:c r="L89" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/094_schwingung_welle.jpg</x:v>
       </x:c>
       <x:c r="M89" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st18_schwingungen_und_ihre_kenngroessen_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_18_schwingungen_und_ihre_kenngroessen.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N89" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st18_schwingungen_und_ihre_kenngroen_orga.html","Vorbereitung öffnen")</x:f>
@@ -5444,7 +5444,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/094_schwingung_welle.jpg</x:v>
       </x:c>
       <x:c r="M90" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st19_schwingungsdauer_des_fadenpendels_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_19_schwingungsdauer_des_fadenpendels.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N90" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st19_schwingungsdauer_des_fadenpendels_orga.html","Vorbereitung öffnen")</x:f>
@@ -5489,7 +5489,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/094_schwingung_welle.jpg</x:v>
       </x:c>
       <x:c r="M91" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st20_wellen_als_ausbreitung_von_schwingungen_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_20_wellen_als_ausbreitung_von_schwingungen.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N91" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st20_wellen_als_ausbreitung_von_schwingungen_orga.html","Vorbereitung öffnen")</x:f>
@@ -5528,13 +5528,13 @@
         <x:v>Piezo-Ausgabe und Mikrofonmodul</x:v>
       </x:c>
       <x:c r="K92" s="60" t="str">
-        <x:v>ph_k10_st21_schall_frequenz_tonhoehe_und_laermschutz</x:v>
+        <x:v>ph_k10_st21_schall_frequenz_tonhohe_und_larmschutz</x:v>
       </x:c>
       <x:c r="L92" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/031_schall_wellen.jpg</x:v>
       </x:c>
       <x:c r="M92" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st21_schall_frequenz_tonhoehe_und_laermschutz_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_21_schall_frequenz_tonhoehe_und_laermschutz.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N92" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st21_schall_frequenz_tonhohe_und_larmschutz_orga.html","Vorbereitung öffnen")</x:f>
@@ -5573,13 +5573,13 @@
         <x:v>Kraftsensor und Wegsensor</x:v>
       </x:c>
       <x:c r="K93" s="60" t="str">
-        <x:v>ph_k10_st22_arbeit_energieformen_und_energie_als_zustandsgroesse</x:v>
+        <x:v>ph_k10_st22_arbeit_energieformen_und_energie_als_zustandsgroe</x:v>
       </x:c>
       <x:c r="L93" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/038_arbeit_leistung.jpg</x:v>
       </x:c>
       <x:c r="M93" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st22_arbeit_energieformen_und_energie_als_zustandsgroesse_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_22_arbeit_energieformen_und_energie_als_zustandsgroesse.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N93" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st22_arbeit_energieformen_und_energie_als_zustandsgroe_orga.html","Vorbereitung öffnen")</x:f>
@@ -5624,7 +5624,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/036_energie_formen.jpg</x:v>
       </x:c>
       <x:c r="M94" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st23_allgemeiner_energieerhaltungssatz_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_23_allgemeiner_energieerhaltungssatz.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N94" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st23_allgemeiner_energieerhaltungssatz_orga.html","Vorbereitung öffnen")</x:f>
@@ -5669,7 +5669,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/064_elektrische_energie.jpg</x:v>
       </x:c>
       <x:c r="M95" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st24_wirkungsgrad_und_versorgung_mit_elektrischer_energie_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_24_wirkungsgrad_und_versorgung_mit_elektrischer_energie.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N95" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st24_wirkungsgrad_und_versorgung_mit_elektrischer_energie_orga.html","Vorbereitung öffnen")</x:f>
@@ -5714,7 +5714,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/042_radioaktivitaet.jpg</x:v>
       </x:c>
       <x:c r="M96" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st25_atomkern_und_nuklidschreibweise_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_25_atomkern_und_nuklidschreibweise.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N96" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st25_atomkern_und_nuklidschreibweise_orga.html","Vorbereitung öffnen")</x:f>
@@ -5759,7 +5759,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/042_radioaktivitaet.jpg</x:v>
       </x:c>
       <x:c r="M97" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st26_und_strahlung_eigenschaften_nachweis_und_abschirmung_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_26_und_strahlung_eigenschaften_nachweis_und_abschirmung.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N97" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st26_und_strahlung_eigenschaften_nachweis_und_abschirmung_orga.html","Vorbereitung öffnen")</x:f>
@@ -5804,7 +5804,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/042_radioaktivitaet.jpg</x:v>
       </x:c>
       <x:c r="M98" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st27_radioaktiver_zerfall_und_halbwertszeit_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_27_radioaktiver_zerfall_und_halbwertszeit.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N98" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st27_radioaktiver_zerfall_und_halbwertszeit_orga.html","Vorbereitung öffnen")</x:f>
@@ -5849,74 +5849,11 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/054_sonne_aufbau.jpg</x:v>
       </x:c>
       <x:c r="M99" s="160" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st28_anwendungen_strahlenschutz_kernspaltung_und_kernfusion_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_28_anwendungen_strahlenschutz_kernspaltung_und_kernfusion.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N99" s="161" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st28_anwendungen_strahlenschutz_kernspaltung_und_kernfusion_orga.html","Vorbereitung öffnen")</x:f>
       </x:c>
-    </x:row>
-    <x:row r="100">
-      <x:c r="M100" s="51"/>
-    </x:row>
-    <x:row r="101">
-      <x:c r="M101" s="51"/>
-    </x:row>
-    <x:row r="102">
-      <x:c r="M102" s="51"/>
-    </x:row>
-    <x:row r="103">
-      <x:c r="M103" s="51"/>
-    </x:row>
-    <x:row r="104">
-      <x:c r="M104" s="51"/>
-    </x:row>
-    <x:row r="105">
-      <x:c r="M105" s="51"/>
-    </x:row>
-    <x:row r="106">
-      <x:c r="M106" s="51"/>
-    </x:row>
-    <x:row r="107">
-      <x:c r="M107" s="51"/>
-    </x:row>
-    <x:row r="108">
-      <x:c r="M108" s="51"/>
-    </x:row>
-    <x:row r="109">
-      <x:c r="M109" s="51"/>
-    </x:row>
-    <x:row r="110">
-      <x:c r="M110" s="51"/>
-    </x:row>
-    <x:row r="111">
-      <x:c r="M111" s="51"/>
-    </x:row>
-    <x:row r="112">
-      <x:c r="M112" s="51"/>
-    </x:row>
-    <x:row r="113">
-      <x:c r="M113" s="51"/>
-    </x:row>
-    <x:row r="114">
-      <x:c r="M114" s="51"/>
-    </x:row>
-    <x:row r="115">
-      <x:c r="M115" s="51"/>
-    </x:row>
-    <x:row r="116">
-      <x:c r="M116" s="51"/>
-    </x:row>
-    <x:row r="117">
-      <x:c r="M117" s="51"/>
-    </x:row>
-    <x:row r="118">
-      <x:c r="M118" s="51"/>
-    </x:row>
-    <x:row r="119">
-      <x:c r="M119" s="51"/>
-    </x:row>
-    <x:row r="120">
-      <x:c r="M120" s="51"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -5925,7 +5862,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R28473391f4874eca"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8f9586a887be459a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6063,13 +6000,13 @@
         <x:v>keiner</x:v>
       </x:c>
       <x:c r="K5" s="57" t="str">
-        <x:v>ph_k7_st01_was_ist_physik</x:v>
+        <x:v>ph_k7_st01_was_ist_physik_beobachten_und_beschreiben</x:v>
       </x:c>
       <x:c r="L5" s="57" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/096_physik_titelseite.jpg</x:v>
       </x:c>
       <x:c r="M5" s="156" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st01_was_ist_physik_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_01_was_ist_physik.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N5" s="157" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st01_was_ist_physik_beobachten_und_beschreiben_orga.html","Vorbereitung öffnen")</x:f>
@@ -6108,13 +6045,13 @@
         <x:v>Reaktionszeitmessung mit Taster und LED als Vergleichsstation</x:v>
       </x:c>
       <x:c r="K6" s="60" t="str">
-        <x:v>ph_k7_st02_messen_und_protokollieren</x:v>
+        <x:v>ph_k7_st02_messen_und_protokollieren_die_reaktionszeit</x:v>
       </x:c>
       <x:c r="L6" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/074_messgeraete.jpg</x:v>
       </x:c>
       <x:c r="M6" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st02_messen_und_protokollieren_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_02_messen_und_protokollieren.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N6" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st02_messen_und_protokollieren_die_reaktionszeit_orga.html","Vorbereitung öffnen")</x:f>
@@ -6153,13 +6090,13 @@
         <x:v>keiner</x:v>
       </x:c>
       <x:c r="K7" s="60" t="str">
-        <x:v>ph_k7_st03_lichtquellen_und_lichtausbreitung</x:v>
+        <x:v>ph_k7_st03_lichtquellen_und_die_geradlinige_ausbreitung_des_lichts</x:v>
       </x:c>
       <x:c r="L7" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/034_arduino_licht_optik.jpg</x:v>
       </x:c>
       <x:c r="M7" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st03_lichtquellen_und_lichtausbreitung_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_03_lichtquellen_und_lichtausbreitung.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N7" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st03_lichtquellen_und_die_geradlinige_ausbreitung_des_lichts_orga.html","Vorbereitung öffnen")</x:f>
@@ -6198,13 +6135,13 @@
         <x:v>Helligkeitsmessung in Kernschatten, Halbschatten und beleuchteter Fläche (Lehrerdemonstration)</x:v>
       </x:c>
       <x:c r="K8" s="60" t="str">
-        <x:v>ph_k7_st04_licht_und_schatten</x:v>
+        <x:v>ph_k7_st04_licht_und_schatten_kernschatten_und_halbschatten</x:v>
       </x:c>
       <x:c r="L8" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/034_arduino_licht_optik.jpg</x:v>
       </x:c>
       <x:c r="M8" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st04_licht_und_schatten_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_04_licht_und_schatten.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N8" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st04_licht_und_schatten_kernschatten_und_halbschatten_orga.html","Vorbereitung öffnen")</x:f>
@@ -6243,13 +6180,13 @@
         <x:v>keiner</x:v>
       </x:c>
       <x:c r="K9" s="60" t="str">
-        <x:v>ph_k7_st05_mondphasen</x:v>
+        <x:v>ph_k7_st05_mondphasen_und_finsternisse_schatten_im_weltall</x:v>
       </x:c>
       <x:c r="L9" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/009_mondphasen.jpg</x:v>
       </x:c>
       <x:c r="M9" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st05_mondphasen_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_05_mondphasen_und_finsternisse.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N9" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st05_mondphasen_und_finsternisse_schatten_im_weltall_orga.html","Vorbereitung öffnen")</x:f>
@@ -6288,13 +6225,13 @@
         <x:v>keiner</x:v>
       </x:c>
       <x:c r="K10" s="60" t="str">
-        <x:v>ph_k7_st06_reflexion</x:v>
+        <x:v>ph_k7_st06_reflexion_und_das_spiegelgesetz_lichtstrahlen_andern_die_richtung</x:v>
       </x:c>
       <x:c r="L10" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/035_reflexion_spiegel.jpg</x:v>
       </x:c>
       <x:c r="M10" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st06_reflexion_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_06_reflexion_spiegelgesetz.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N10" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st06_reflexion_und_das_spiegelgesetz_lichtstrahlen_andern_die_richtung_orga.html","Vorbereitung öffnen")</x:f>
@@ -6333,13 +6270,13 @@
         <x:v>keiner</x:v>
       </x:c>
       <x:c r="K11" s="60" t="str">
-        <x:v>ph_k7_st07_spiegelbilder</x:v>
+        <x:v>ph_k7_st07_spiegelbilder_wie_entsteht_das_bild_im_spiegel</x:v>
       </x:c>
       <x:c r="L11" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/035_reflexion_spiegel.jpg</x:v>
       </x:c>
       <x:c r="M11" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st07_spiegelbilder_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_07_spiegelbilder.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N11" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st07_spiegelbilder_wie_entsteht_das_bild_im_spiegel_orga.html","Vorbereitung öffnen")</x:f>
@@ -6378,13 +6315,13 @@
         <x:v>keiner</x:v>
       </x:c>
       <x:c r="K12" s="60" t="str">
-        <x:v>ph_k7_st08_brechung</x:v>
+        <x:v>ph_k7_st08_brechung_und_linsen_licht_andert_die_richtung_in_glas</x:v>
       </x:c>
       <x:c r="L12" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/006_lichtbrechung.jpg</x:v>
       </x:c>
       <x:c r="M12" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st08_brechung_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_08_brechung_linsen.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N12" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st08_brechung_und_linsen_licht_andert_die_richtung_in_glas_orga.html","Vorbereitung öffnen")</x:f>
@@ -6423,13 +6360,13 @@
         <x:v>keiner</x:v>
       </x:c>
       <x:c r="K13" s="60" t="str">
-        <x:v>ph_k7_st09_waerme</x:v>
+        <x:v>ph_k7_st09_warme_und_temperatur_zwei_verschiedene_groen</x:v>
       </x:c>
       <x:c r="L13" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/026_temperatur_waerme.jpg</x:v>
       </x:c>
       <x:c r="M13" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st09_waerme_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_09_waerme_temperatur.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N13" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st09_warme_und_temperatur_zwei_verschiedene_groen_orga.html","Vorbereitung öffnen")</x:f>
@@ -6468,13 +6405,13 @@
         <x:v>keiner</x:v>
       </x:c>
       <x:c r="K14" s="60" t="str">
-        <x:v>ph_k7_st10_waermeleitung</x:v>
+        <x:v>ph_k7_st10_warmeleitung_und_warmestrahlung_wie_warme_sich_ausbreitet</x:v>
       </x:c>
       <x:c r="L14" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/042_radioaktivitaet.jpg</x:v>
       </x:c>
       <x:c r="M14" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st10_waermeleitung_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_10_waermeleitung_waermestrahlung.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N14" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st10_warmeleitung_und_warmestrahlung_wie_warme_sich_ausbreitet_orga.html","Vorbereitung öffnen")</x:f>
@@ -6513,13 +6450,13 @@
         <x:v>nein</x:v>
       </x:c>
       <x:c r="K15" s="60" t="str">
-        <x:v>ph_k7_st11_stromkreis</x:v>
+        <x:v>ph_k7_st11_der_stromkreis_und_der_schalter</x:v>
       </x:c>
       <x:c r="L15" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/001_stromkreis.jpg</x:v>
       </x:c>
       <x:c r="M15" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st11_stromkreis_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_11_stromkreis.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N15" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st11_der_stromkreis_und_der_schalter_orga.html","Vorbereitung öffnen")</x:f>
@@ -6558,13 +6495,13 @@
         <x:v>nein</x:v>
       </x:c>
       <x:c r="K16" s="60" t="str">
-        <x:v>ph_k7_st12_reihen_parallel</x:v>
+        <x:v>ph_k7_st12_reihen_und_parallelschaltung</x:v>
       </x:c>
       <x:c r="L16" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/012_parallelschaltung.jpg</x:v>
       </x:c>
       <x:c r="M16" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st12_reihen_parallel_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_12_reihen_parallel.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N16" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st12_reihen_und_parallelschaltung_orga.html","Vorbereitung öffnen")</x:f>
@@ -6603,13 +6540,13 @@
         <x:v>nein</x:v>
       </x:c>
       <x:c r="K17" s="60" t="str">
-        <x:v>ph_k7_st13_leistung</x:v>
+        <x:v>ph_k7_st13_elektrische_leistung_wie_viel_energie_verbrauchen_gerate</x:v>
       </x:c>
       <x:c r="L17" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/038_arbeit_leistung.jpg</x:v>
       </x:c>
       <x:c r="M17" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st13_leistung_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_13_leistung.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N17" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st13_elektrische_leistung_wie_viel_energie_verbrauchen_gerate_orga.html","Vorbereitung öffnen")</x:f>
@@ -6648,13 +6585,13 @@
         <x:v>nein</x:v>
       </x:c>
       <x:c r="K18" s="60" t="str">
-        <x:v>ph_k7_st14_sicherheit</x:v>
+        <x:v>ph_k7_st14_sicherheit_im_stromkreis_schutz_vor_uberlastung_und_kurzschluss</x:v>
       </x:c>
       <x:c r="L18" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/001_stromkreis.jpg</x:v>
       </x:c>
       <x:c r="M18" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st14_sicherheit_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_14_sicherheit.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N18" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st14_sicherheit_im_stromkreis_schutz_vor_uberlastung_und_kurzschluss_orga.html","Vorbereitung öffnen")</x:f>
@@ -6693,13 +6630,13 @@
         <x:v>entfällt</x:v>
       </x:c>
       <x:c r="K19" s="60" t="str">
-        <x:v>ph_k7_st19_mechanische_arbeit</x:v>
+        <x:v>ph_k7_st19_die_mechanische_arbeit_kraft_mal_weg</x:v>
       </x:c>
       <x:c r="L19" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/021_kraft_gewicht.jpg</x:v>
       </x:c>
       <x:c r="M19" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st19_mechanische_arbeit_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_19_mechanische_arbeit.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N19" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st19_die_mechanische_arbeit_kraft_mal_weg_orga.html","Vorbereitung öffnen")</x:f>
@@ -6738,13 +6675,13 @@
         <x:v>Automatische Zeitmessung des Hubvorgangs zwischen zwei Höhenschwellen zur Berechnung der Leistung (Lehrerdemonstration)</x:v>
       </x:c>
       <x:c r="K20" s="60" t="str">
-        <x:v>ph_k7_st20_leistung</x:v>
+        <x:v>ph_k7_st20_die_leistung_arbeit_pro_zeit</x:v>
       </x:c>
       <x:c r="L20" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/038_arbeit_leistung.jpg</x:v>
       </x:c>
       <x:c r="M20" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st20_leistung_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_20_leistung.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N20" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st20_die_leistung_arbeit_pro_zeit_orga.html","Vorbereitung öffnen")</x:f>
@@ -6783,13 +6720,13 @@
         <x:v>entfällt</x:v>
       </x:c>
       <x:c r="K21" s="60" t="str">
-        <x:v>ph_k7_st21_energieformen</x:v>
+        <x:v>ph_k7_st21_energie_und_energieformen_lageenergie_und_bewegungsenergie</x:v>
       </x:c>
       <x:c r="L21" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/023_gleichfoermige_bewegung.jpg</x:v>
       </x:c>
       <x:c r="M21" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st21_energieformen_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_21_energieformen.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N21" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st21_energie_und_energieformen_lageenergie_und_bewegungsenergie_orga.html","Vorbereitung öffnen")</x:f>
@@ -6828,13 +6765,13 @@
         <x:v>Helligkeitsmessung zweier Leuchtmittel mit stark unterschiedlicher Leistung bei gleichem Abstand (Lehrerdemonstration)</x:v>
       </x:c>
       <x:c r="K22" s="60" t="str">
-        <x:v>ph_k7_st22_energiesparen</x:v>
+        <x:v>ph_k7_st22_energie_sparen_im_alltag_leuchtmittel_im_vergleich</x:v>
       </x:c>
       <x:c r="L22" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/090_physik_klassenraum.jpg</x:v>
       </x:c>
       <x:c r="M22" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st22_energiesparen_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_22_energiesparen.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N22" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st22_energie_sparen_im_alltag_leuchtmittel_im_vergleich_orga.html","Vorbereitung öffnen")</x:f>
@@ -6873,13 +6810,13 @@
         <x:v>entfällt</x:v>
       </x:c>
       <x:c r="K23" s="60" t="str">
-        <x:v>ph_k7_st23_wiederholung</x:v>
+        <x:v>ph_k7_st23_wiederholung_und_vertiefung_arbeit_leistung_energie</x:v>
       </x:c>
       <x:c r="L23" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/038_arbeit_leistung.jpg</x:v>
       </x:c>
       <x:c r="M23" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st23_wiederholung_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_23_wiederholung.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N23" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st23_wiederholung_und_vertiefung_arbeit_leistung_energie_orga.html","Vorbereitung öffnen")</x:f>
@@ -6918,13 +6855,13 @@
         <x:v>Automatisierte Messung des Wasserstands vor und nach dem Eintauchen eines Körpers zur Bestimmung seines Volumens (Schülerexperiment)</x:v>
       </x:c>
       <x:c r="K24" s="60" t="str">
-        <x:v>ph_k7_st24_dichte</x:v>
+        <x:v>ph_k7_st24_masse_volumen_und_dichte</x:v>
       </x:c>
       <x:c r="L24" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/025_dichte_experiment.jpg</x:v>
       </x:c>
       <x:c r="M24" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st24_dichte_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_24_dichte.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N24" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st24_masse_volumen_und_dichte_orga.html","Vorbereitung öffnen")</x:f>
@@ -6963,302 +6900,17 @@
         <x:v>entfällt</x:v>
       </x:c>
       <x:c r="K25" s="63" t="str">
-        <x:v>ph_k7_st25_auftrieb</x:v>
+        <x:v>ph_k7_st25_auftrieb_warum_schwimmen_manche_dinge</x:v>
       </x:c>
       <x:c r="L25" s="63" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/081_auftrieb.jpg</x:v>
       </x:c>
       <x:c r="M25" s="160" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k7_st25_auftrieb_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph7_stunde_25_auftrieb.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N25" s="161" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k7_st25_auftrieb_warum_schwimmen_manche_dinge_orga.html","Vorbereitung öffnen")</x:f>
       </x:c>
-    </x:row>
-    <x:row r="26">
-      <x:c r="M26" s="51"/>
-    </x:row>
-    <x:row r="27">
-      <x:c r="M27" s="51"/>
-    </x:row>
-    <x:row r="28">
-      <x:c r="M28" s="51"/>
-    </x:row>
-    <x:row r="29">
-      <x:c r="M29" s="51"/>
-    </x:row>
-    <x:row r="30">
-      <x:c r="M30" s="51"/>
-    </x:row>
-    <x:row r="31">
-      <x:c r="M31" s="51"/>
-    </x:row>
-    <x:row r="32">
-      <x:c r="M32" s="51"/>
-    </x:row>
-    <x:row r="33">
-      <x:c r="M33" s="51"/>
-    </x:row>
-    <x:row r="34">
-      <x:c r="M34" s="51"/>
-    </x:row>
-    <x:row r="35">
-      <x:c r="M35" s="51"/>
-    </x:row>
-    <x:row r="36">
-      <x:c r="M36" s="51"/>
-    </x:row>
-    <x:row r="37">
-      <x:c r="M37" s="51"/>
-    </x:row>
-    <x:row r="38">
-      <x:c r="M38" s="51"/>
-    </x:row>
-    <x:row r="39">
-      <x:c r="M39" s="51"/>
-    </x:row>
-    <x:row r="40">
-      <x:c r="M40" s="51"/>
-    </x:row>
-    <x:row r="41">
-      <x:c r="M41" s="51"/>
-    </x:row>
-    <x:row r="42">
-      <x:c r="M42" s="51"/>
-    </x:row>
-    <x:row r="43">
-      <x:c r="M43" s="51"/>
-    </x:row>
-    <x:row r="44">
-      <x:c r="M44" s="51"/>
-    </x:row>
-    <x:row r="45">
-      <x:c r="M45" s="51"/>
-    </x:row>
-    <x:row r="46">
-      <x:c r="M46" s="51"/>
-    </x:row>
-    <x:row r="47">
-      <x:c r="M47" s="51"/>
-    </x:row>
-    <x:row r="48">
-      <x:c r="M48" s="51"/>
-    </x:row>
-    <x:row r="49">
-      <x:c r="M49" s="51"/>
-    </x:row>
-    <x:row r="50">
-      <x:c r="M50" s="51"/>
-    </x:row>
-    <x:row r="51">
-      <x:c r="M51" s="51"/>
-    </x:row>
-    <x:row r="52">
-      <x:c r="M52" s="51"/>
-    </x:row>
-    <x:row r="53">
-      <x:c r="M53" s="51"/>
-    </x:row>
-    <x:row r="54">
-      <x:c r="M54" s="51"/>
-    </x:row>
-    <x:row r="55">
-      <x:c r="M55" s="51"/>
-    </x:row>
-    <x:row r="56">
-      <x:c r="M56" s="51"/>
-    </x:row>
-    <x:row r="57">
-      <x:c r="M57" s="51"/>
-    </x:row>
-    <x:row r="58">
-      <x:c r="M58" s="51"/>
-    </x:row>
-    <x:row r="59">
-      <x:c r="M59" s="51"/>
-    </x:row>
-    <x:row r="60">
-      <x:c r="M60" s="51"/>
-    </x:row>
-    <x:row r="61">
-      <x:c r="M61" s="51"/>
-    </x:row>
-    <x:row r="62">
-      <x:c r="M62" s="51"/>
-    </x:row>
-    <x:row r="63">
-      <x:c r="M63" s="51"/>
-    </x:row>
-    <x:row r="64">
-      <x:c r="M64" s="51"/>
-    </x:row>
-    <x:row r="65">
-      <x:c r="M65" s="51"/>
-    </x:row>
-    <x:row r="66">
-      <x:c r="M66" s="51"/>
-    </x:row>
-    <x:row r="67">
-      <x:c r="M67" s="51"/>
-    </x:row>
-    <x:row r="68">
-      <x:c r="M68" s="51"/>
-    </x:row>
-    <x:row r="69">
-      <x:c r="M69" s="51"/>
-    </x:row>
-    <x:row r="70">
-      <x:c r="M70" s="51"/>
-    </x:row>
-    <x:row r="71">
-      <x:c r="M71" s="51"/>
-    </x:row>
-    <x:row r="72">
-      <x:c r="M72" s="51"/>
-    </x:row>
-    <x:row r="73">
-      <x:c r="M73" s="51"/>
-    </x:row>
-    <x:row r="74">
-      <x:c r="M74" s="51"/>
-    </x:row>
-    <x:row r="75">
-      <x:c r="M75" s="51"/>
-    </x:row>
-    <x:row r="76">
-      <x:c r="M76" s="51"/>
-    </x:row>
-    <x:row r="77">
-      <x:c r="M77" s="51"/>
-    </x:row>
-    <x:row r="78">
-      <x:c r="M78" s="51"/>
-    </x:row>
-    <x:row r="79">
-      <x:c r="M79" s="51"/>
-    </x:row>
-    <x:row r="80">
-      <x:c r="M80" s="51"/>
-    </x:row>
-    <x:row r="81">
-      <x:c r="M81" s="51"/>
-    </x:row>
-    <x:row r="82">
-      <x:c r="M82" s="51"/>
-    </x:row>
-    <x:row r="83">
-      <x:c r="M83" s="51"/>
-    </x:row>
-    <x:row r="84">
-      <x:c r="M84" s="51"/>
-    </x:row>
-    <x:row r="85">
-      <x:c r="M85" s="51"/>
-    </x:row>
-    <x:row r="86">
-      <x:c r="M86" s="51"/>
-    </x:row>
-    <x:row r="87">
-      <x:c r="M87" s="51"/>
-    </x:row>
-    <x:row r="88">
-      <x:c r="M88" s="51"/>
-    </x:row>
-    <x:row r="89">
-      <x:c r="M89" s="51"/>
-    </x:row>
-    <x:row r="90">
-      <x:c r="M90" s="51"/>
-    </x:row>
-    <x:row r="91">
-      <x:c r="M91" s="51"/>
-    </x:row>
-    <x:row r="92">
-      <x:c r="M92" s="51"/>
-    </x:row>
-    <x:row r="93">
-      <x:c r="M93" s="51"/>
-    </x:row>
-    <x:row r="94">
-      <x:c r="M94" s="51"/>
-    </x:row>
-    <x:row r="95">
-      <x:c r="M95" s="51"/>
-    </x:row>
-    <x:row r="96">
-      <x:c r="M96" s="51"/>
-    </x:row>
-    <x:row r="97">
-      <x:c r="M97" s="51"/>
-    </x:row>
-    <x:row r="98">
-      <x:c r="M98" s="51"/>
-    </x:row>
-    <x:row r="99">
-      <x:c r="M99" s="51"/>
-    </x:row>
-    <x:row r="100">
-      <x:c r="M100" s="51"/>
-    </x:row>
-    <x:row r="101">
-      <x:c r="M101" s="51"/>
-    </x:row>
-    <x:row r="102">
-      <x:c r="M102" s="51"/>
-    </x:row>
-    <x:row r="103">
-      <x:c r="M103" s="51"/>
-    </x:row>
-    <x:row r="104">
-      <x:c r="M104" s="51"/>
-    </x:row>
-    <x:row r="105">
-      <x:c r="M105" s="51"/>
-    </x:row>
-    <x:row r="106">
-      <x:c r="M106" s="51"/>
-    </x:row>
-    <x:row r="107">
-      <x:c r="M107" s="51"/>
-    </x:row>
-    <x:row r="108">
-      <x:c r="M108" s="51"/>
-    </x:row>
-    <x:row r="109">
-      <x:c r="M109" s="51"/>
-    </x:row>
-    <x:row r="110">
-      <x:c r="M110" s="51"/>
-    </x:row>
-    <x:row r="111">
-      <x:c r="M111" s="51"/>
-    </x:row>
-    <x:row r="112">
-      <x:c r="M112" s="51"/>
-    </x:row>
-    <x:row r="113">
-      <x:c r="M113" s="51"/>
-    </x:row>
-    <x:row r="114">
-      <x:c r="M114" s="51"/>
-    </x:row>
-    <x:row r="115">
-      <x:c r="M115" s="51"/>
-    </x:row>
-    <x:row r="116">
-      <x:c r="M116" s="51"/>
-    </x:row>
-    <x:row r="117">
-      <x:c r="M117" s="51"/>
-    </x:row>
-    <x:row r="118">
-      <x:c r="M118" s="51"/>
-    </x:row>
-    <x:row r="119">
-      <x:c r="M119" s="51"/>
-    </x:row>
-    <x:row r="120">
-      <x:c r="M120" s="51"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -7267,7 +6919,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R59022c507f2747c1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R88382ea432784924"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7405,13 +7057,13 @@
         <x:v>entfällt</x:v>
       </x:c>
       <x:c r="K5" s="57" t="str">
-        <x:v>ph_k8_st01_geschwindigkeit</x:v>
+        <x:v>ph_k8_st01_geschwindigkeit_was_bedeutet_schnell</x:v>
       </x:c>
       <x:c r="L5" s="57" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/023_gleichfoermige_bewegung.jpg</x:v>
       </x:c>
       <x:c r="M5" s="156" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st01_geschwindigkeit_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_01_geschwindigkeit.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N5" s="157" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st01_geschwindigkeit_was_bedeutet_schnell_orga.html","Vorbereitung öffnen")</x:f>
@@ -7450,13 +7102,13 @@
         <x:v>Fortlaufende Positionsmessung eines Wagens zur Erstellung eines Weg-Zeit-Diagramms (Lehrerdemonstration)</x:v>
       </x:c>
       <x:c r="K6" s="60" t="str">
-        <x:v>ph_k8_st02_weg_zeit_diagramm</x:v>
+        <x:v>ph_k8_st02_bewegungsarten_und_das_weg_zeit_diagramm</x:v>
       </x:c>
       <x:c r="L6" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/023_gleichfoermige_bewegung.jpg</x:v>
       </x:c>
       <x:c r="M6" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st02_weg_zeit_diagramm_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_02_weg_zeit_diagramm.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N6" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st02_bewegungsarten_und_das_weg_zeit_diagramm_orga.html","Vorbereitung öffnen")</x:f>
@@ -7495,13 +7147,13 @@
         <x:v>entfällt</x:v>
       </x:c>
       <x:c r="K7" s="60" t="str">
-        <x:v>ph_k8_st03_durchschnitt_moment</x:v>
+        <x:v>ph_k8_st03_durchschnitts_und_momentangeschwindigkeit</x:v>
       </x:c>
       <x:c r="L7" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/023_gleichfoermige_bewegung.jpg</x:v>
       </x:c>
       <x:c r="M7" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st03_durchschnitt_moment_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_03_durchschnitt_moment.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N7" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st03_durchschnitts_und_momentangeschwindigkeit_orga.html","Vorbereitung öffnen")</x:f>
@@ -7540,13 +7192,13 @@
         <x:v>Fortlaufende Positionsmessung zur Berechnung der Geschwindigkeitszunahme und daraus der Beschleunigung (Schülerexperiment)</x:v>
       </x:c>
       <x:c r="K8" s="60" t="str">
-        <x:v>ph_k8_st04_beschleunigung</x:v>
+        <x:v>ph_k8_st04_beschleunigung_wenn_sich_die_geschwindigkeit_andert</x:v>
       </x:c>
       <x:c r="L8" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/092_beschleunigung.jpg</x:v>
       </x:c>
       <x:c r="M8" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st04_beschleunigung_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_04_beschleunigung.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N8" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st04_beschleunigung_wenn_sich_die_geschwindigkeit_andert_orga.html","Vorbereitung öffnen")</x:f>
@@ -7591,7 +7243,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/097_formeln_uebersicht.jpg</x:v>
       </x:c>
       <x:c r="M9" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st09_wiederholung_dynamik_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_09_wiederholung_dynamik.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N9" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st09_wiederholung_dynamik_orga.html","Vorbereitung öffnen")</x:f>
@@ -7630,13 +7282,13 @@
         <x:v>Automatisierte Temperaturaufzeichnung beim Erhitzen von Eis bis zum Sieden zur Erstellung einer Erhitzungskurve (Lehrerdemonstration)</x:v>
       </x:c>
       <x:c r="K10" s="60" t="str">
-        <x:v>ph_k8_st10_aggregatzustaende</x:v>
+        <x:v>ph_k8_st10_aggregatzustande</x:v>
       </x:c>
       <x:c r="L10" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/026_temperatur_waerme.jpg</x:v>
       </x:c>
       <x:c r="M10" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st10_aggregatzustaende_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_10_aggregatzustaende.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N10" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st10_aggregatzustande_orga.html","Vorbereitung öffnen")</x:f>
@@ -7675,13 +7327,13 @@
         <x:v>entfällt</x:v>
       </x:c>
       <x:c r="K11" s="60" t="str">
-        <x:v>ph_k8_st11_waermeausdehnung</x:v>
+        <x:v>ph_k8_st11_warmeausdehnung</x:v>
       </x:c>
       <x:c r="L11" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/026_temperatur_waerme.jpg</x:v>
       </x:c>
       <x:c r="M11" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st11_waermeausdehnung_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_11_waermeausdehnung.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N11" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st11_warmeausdehnung_orga.html","Vorbereitung öffnen")</x:f>
@@ -7720,13 +7372,13 @@
         <x:v>Gleichzeitige, automatisierte Temperaturmessung zweier Stoffe zur Bestimmung der unterschiedlichen spezifischen Wärmekapazität (Schülerexperiment)</x:v>
       </x:c>
       <x:c r="K12" s="60" t="str">
-        <x:v>ph_k8_st12_waermekapazitaet</x:v>
+        <x:v>ph_k8_st12_warmemenge_und_spezifische_warmekapazitat</x:v>
       </x:c>
       <x:c r="L12" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/026_temperatur_waerme.jpg</x:v>
       </x:c>
       <x:c r="M12" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st12_waermekapazitaet_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_12_waermekapazitaet.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N12" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st12_warmemenge_und_spezifische_warmekapazitat_orga.html","Vorbereitung öffnen")</x:f>
@@ -7771,7 +7423,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/090_physik_klassenraum.jpg</x:v>
       </x:c>
       <x:c r="M13" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st17_magnetismus_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_17_magnetismus.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N13" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st17_magnetismus_orga.html","Vorbereitung öffnen")</x:f>
@@ -7816,7 +7468,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/018_kompass_erdmagnetfeld.jpg</x:v>
       </x:c>
       <x:c r="M14" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st18_kompass_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_18_kompass.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N14" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st18_kompass_orga.html","Vorbereitung öffnen")</x:f>
@@ -7861,7 +7513,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/019_elektromagnet.jpg</x:v>
       </x:c>
       <x:c r="M15" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st19_elektromagnet_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_19_elektromagnet.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N15" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st19_elektromagnet_orga.html","Vorbereitung öffnen")</x:f>
@@ -7906,7 +7558,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/043_induktion.jpg</x:v>
       </x:c>
       <x:c r="M16" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st20_induktion_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_20_induktion.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N16" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st20_induktion_orga.html","Vorbereitung öffnen")</x:f>
@@ -7951,7 +7603,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/097_formeln_uebersicht.jpg</x:v>
       </x:c>
       <x:c r="M17" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st21_wiederholung_magnetismus_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_21_wiederholung_magnetismus.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N17" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st21_wiederholung_magnetismus_orga.html","Vorbereitung öffnen")</x:f>
@@ -7996,7 +7648,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/005_tafelbild_ohm.jpg</x:v>
       </x:c>
       <x:c r="M18" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st22_ohmsches_gesetz_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_22_ohmsches_gesetz.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N18" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st22_ohmsches_gesetz_orga.html","Vorbereitung öffnen")</x:f>
@@ -8041,7 +7693,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/090_physik_klassenraum.jpg</x:v>
       </x:c>
       <x:c r="M19" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st23_reihe_parallel_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_23_reihe_parallel.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N19" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st23_reihe_parallel_orga.html","Vorbereitung öffnen")</x:f>
@@ -8086,7 +7738,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/038_arbeit_leistung.jpg</x:v>
       </x:c>
       <x:c r="M20" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st24_leistung_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_24_leistung.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N20" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st24_leistung_orga.html","Vorbereitung öffnen")</x:f>
@@ -8131,7 +7783,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/097_formeln_uebersicht.jpg</x:v>
       </x:c>
       <x:c r="M21" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st25_wiederholung_elektrizitaet_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_25_wiederholung_elektrizitaet.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N21" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st25_wiederholung_elektrizitaet_orga.html","Vorbereitung öffnen")</x:f>
@@ -8176,7 +7828,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/006_lichtbrechung.jpg</x:v>
       </x:c>
       <x:c r="M22" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st26_lichtbrechung_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_26_lichtbrechung.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N22" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st26_lichtbrechung_orga.html","Vorbereitung öffnen")</x:f>
@@ -8221,7 +7873,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/093_optische_instrumente.jpg</x:v>
       </x:c>
       <x:c r="M23" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st27_linsen_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_27_linsen.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N23" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st27_linsen_orga.html","Vorbereitung öffnen")</x:f>
@@ -8266,7 +7918,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/093_optische_instrumente.jpg</x:v>
       </x:c>
       <x:c r="M24" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st28_auge_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_28_auge.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N24" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st28_auge_orga.html","Vorbereitung öffnen")</x:f>
@@ -8311,7 +7963,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/097_formeln_uebersicht.jpg</x:v>
       </x:c>
       <x:c r="M25" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st29_wiederholung_optik_vertieft_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_29_wiederholung_optik_vertieft.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N25" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st29_wiederholung_optik_vertieft_orga.html","Vorbereitung öffnen")</x:f>
@@ -8356,293 +8008,11 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/097_formeln_uebersicht.jpg</x:v>
       </x:c>
       <x:c r="M26" s="160" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k8_st30_gesamtwiederholung_klasse_8_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph8_stunde_30_gesamtwiederholung_klasse_8.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N26" s="161" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k8_st30_gesamtwiederholung_klasse_8_orga.html","Vorbereitung öffnen")</x:f>
       </x:c>
-    </x:row>
-    <x:row r="27">
-      <x:c r="M27" s="51"/>
-    </x:row>
-    <x:row r="28">
-      <x:c r="M28" s="51"/>
-    </x:row>
-    <x:row r="29">
-      <x:c r="M29" s="51"/>
-    </x:row>
-    <x:row r="30">
-      <x:c r="M30" s="51"/>
-    </x:row>
-    <x:row r="31">
-      <x:c r="M31" s="51"/>
-    </x:row>
-    <x:row r="32">
-      <x:c r="M32" s="51"/>
-    </x:row>
-    <x:row r="33">
-      <x:c r="M33" s="51"/>
-    </x:row>
-    <x:row r="34">
-      <x:c r="M34" s="51"/>
-    </x:row>
-    <x:row r="35">
-      <x:c r="M35" s="51"/>
-    </x:row>
-    <x:row r="36">
-      <x:c r="M36" s="51"/>
-    </x:row>
-    <x:row r="37">
-      <x:c r="M37" s="51"/>
-    </x:row>
-    <x:row r="38">
-      <x:c r="M38" s="51"/>
-    </x:row>
-    <x:row r="39">
-      <x:c r="M39" s="51"/>
-    </x:row>
-    <x:row r="40">
-      <x:c r="M40" s="51"/>
-    </x:row>
-    <x:row r="41">
-      <x:c r="M41" s="51"/>
-    </x:row>
-    <x:row r="42">
-      <x:c r="M42" s="51"/>
-    </x:row>
-    <x:row r="43">
-      <x:c r="M43" s="51"/>
-    </x:row>
-    <x:row r="44">
-      <x:c r="M44" s="51"/>
-    </x:row>
-    <x:row r="45">
-      <x:c r="M45" s="51"/>
-    </x:row>
-    <x:row r="46">
-      <x:c r="M46" s="51"/>
-    </x:row>
-    <x:row r="47">
-      <x:c r="M47" s="51"/>
-    </x:row>
-    <x:row r="48">
-      <x:c r="M48" s="51"/>
-    </x:row>
-    <x:row r="49">
-      <x:c r="M49" s="51"/>
-    </x:row>
-    <x:row r="50">
-      <x:c r="M50" s="51"/>
-    </x:row>
-    <x:row r="51">
-      <x:c r="M51" s="51"/>
-    </x:row>
-    <x:row r="52">
-      <x:c r="M52" s="51"/>
-    </x:row>
-    <x:row r="53">
-      <x:c r="M53" s="51"/>
-    </x:row>
-    <x:row r="54">
-      <x:c r="M54" s="51"/>
-    </x:row>
-    <x:row r="55">
-      <x:c r="M55" s="51"/>
-    </x:row>
-    <x:row r="56">
-      <x:c r="M56" s="51"/>
-    </x:row>
-    <x:row r="57">
-      <x:c r="M57" s="51"/>
-    </x:row>
-    <x:row r="58">
-      <x:c r="M58" s="51"/>
-    </x:row>
-    <x:row r="59">
-      <x:c r="M59" s="51"/>
-    </x:row>
-    <x:row r="60">
-      <x:c r="M60" s="51"/>
-    </x:row>
-    <x:row r="61">
-      <x:c r="M61" s="51"/>
-    </x:row>
-    <x:row r="62">
-      <x:c r="M62" s="51"/>
-    </x:row>
-    <x:row r="63">
-      <x:c r="M63" s="51"/>
-    </x:row>
-    <x:row r="64">
-      <x:c r="M64" s="51"/>
-    </x:row>
-    <x:row r="65">
-      <x:c r="M65" s="51"/>
-    </x:row>
-    <x:row r="66">
-      <x:c r="M66" s="51"/>
-    </x:row>
-    <x:row r="67">
-      <x:c r="M67" s="51"/>
-    </x:row>
-    <x:row r="68">
-      <x:c r="M68" s="51"/>
-    </x:row>
-    <x:row r="69">
-      <x:c r="M69" s="51"/>
-    </x:row>
-    <x:row r="70">
-      <x:c r="M70" s="51"/>
-    </x:row>
-    <x:row r="71">
-      <x:c r="M71" s="51"/>
-    </x:row>
-    <x:row r="72">
-      <x:c r="M72" s="51"/>
-    </x:row>
-    <x:row r="73">
-      <x:c r="M73" s="51"/>
-    </x:row>
-    <x:row r="74">
-      <x:c r="M74" s="51"/>
-    </x:row>
-    <x:row r="75">
-      <x:c r="M75" s="51"/>
-    </x:row>
-    <x:row r="76">
-      <x:c r="M76" s="51"/>
-    </x:row>
-    <x:row r="77">
-      <x:c r="M77" s="51"/>
-    </x:row>
-    <x:row r="78">
-      <x:c r="M78" s="51"/>
-    </x:row>
-    <x:row r="79">
-      <x:c r="M79" s="51"/>
-    </x:row>
-    <x:row r="80">
-      <x:c r="M80" s="51"/>
-    </x:row>
-    <x:row r="81">
-      <x:c r="M81" s="51"/>
-    </x:row>
-    <x:row r="82">
-      <x:c r="M82" s="51"/>
-    </x:row>
-    <x:row r="83">
-      <x:c r="M83" s="51"/>
-    </x:row>
-    <x:row r="84">
-      <x:c r="M84" s="51"/>
-    </x:row>
-    <x:row r="85">
-      <x:c r="M85" s="51"/>
-    </x:row>
-    <x:row r="86">
-      <x:c r="M86" s="51"/>
-    </x:row>
-    <x:row r="87">
-      <x:c r="M87" s="51"/>
-    </x:row>
-    <x:row r="88">
-      <x:c r="M88" s="51"/>
-    </x:row>
-    <x:row r="89">
-      <x:c r="M89" s="51"/>
-    </x:row>
-    <x:row r="90">
-      <x:c r="M90" s="51"/>
-    </x:row>
-    <x:row r="91">
-      <x:c r="M91" s="51"/>
-    </x:row>
-    <x:row r="92">
-      <x:c r="M92" s="51"/>
-    </x:row>
-    <x:row r="93">
-      <x:c r="M93" s="51"/>
-    </x:row>
-    <x:row r="94">
-      <x:c r="M94" s="51"/>
-    </x:row>
-    <x:row r="95">
-      <x:c r="M95" s="51"/>
-    </x:row>
-    <x:row r="96">
-      <x:c r="M96" s="51"/>
-    </x:row>
-    <x:row r="97">
-      <x:c r="M97" s="51"/>
-    </x:row>
-    <x:row r="98">
-      <x:c r="M98" s="51"/>
-    </x:row>
-    <x:row r="99">
-      <x:c r="M99" s="51"/>
-    </x:row>
-    <x:row r="100">
-      <x:c r="M100" s="51"/>
-    </x:row>
-    <x:row r="101">
-      <x:c r="M101" s="51"/>
-    </x:row>
-    <x:row r="102">
-      <x:c r="M102" s="51"/>
-    </x:row>
-    <x:row r="103">
-      <x:c r="M103" s="51"/>
-    </x:row>
-    <x:row r="104">
-      <x:c r="M104" s="51"/>
-    </x:row>
-    <x:row r="105">
-      <x:c r="M105" s="51"/>
-    </x:row>
-    <x:row r="106">
-      <x:c r="M106" s="51"/>
-    </x:row>
-    <x:row r="107">
-      <x:c r="M107" s="51"/>
-    </x:row>
-    <x:row r="108">
-      <x:c r="M108" s="51"/>
-    </x:row>
-    <x:row r="109">
-      <x:c r="M109" s="51"/>
-    </x:row>
-    <x:row r="110">
-      <x:c r="M110" s="51"/>
-    </x:row>
-    <x:row r="111">
-      <x:c r="M111" s="51"/>
-    </x:row>
-    <x:row r="112">
-      <x:c r="M112" s="51"/>
-    </x:row>
-    <x:row r="113">
-      <x:c r="M113" s="51"/>
-    </x:row>
-    <x:row r="114">
-      <x:c r="M114" s="51"/>
-    </x:row>
-    <x:row r="115">
-      <x:c r="M115" s="51"/>
-    </x:row>
-    <x:row r="116">
-      <x:c r="M116" s="51"/>
-    </x:row>
-    <x:row r="117">
-      <x:c r="M117" s="51"/>
-    </x:row>
-    <x:row r="118">
-      <x:c r="M118" s="51"/>
-    </x:row>
-    <x:row r="119">
-      <x:c r="M119" s="51"/>
-    </x:row>
-    <x:row r="120">
-      <x:c r="M120" s="51"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -8651,7 +8021,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfaa4e41eff2c431a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb450b11738dc4ca6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8795,7 +8165,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/017_magnet_feldlinien.jpg</x:v>
       </x:c>
       <x:c r="M5" s="156" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st01_magnetische_pole_und_kraftwirkungen_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_01_magnetische_pole_und_kraftwirkungen.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N5" s="157" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st01_magnetische_pole_und_kraftwirkungen_orga.html","Vorbereitung öffnen")</x:f>
@@ -8840,7 +8210,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/017_magnet_feldlinien.jpg</x:v>
       </x:c>
       <x:c r="M6" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st02_magnetfeld_und_feldlinienmodell_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_02_magnetfeld_und_feldlinienmodell.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N6" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st02_magnetfeld_und_feldlinienmodell_orga.html","Vorbereitung öffnen")</x:f>
@@ -8885,7 +8255,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/018_kompass_erdmagnetfeld.jpg</x:v>
       </x:c>
       <x:c r="M7" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st03_erdmagnetfeld_und_kompass_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_03_erdmagnetfeld_und_kompass.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N7" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st03_erdmagnetfeld_und_kompass_orga.html","Vorbereitung öffnen")</x:f>
@@ -8930,7 +8300,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/090_physik_klassenraum.jpg</x:v>
       </x:c>
       <x:c r="M8" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st04_elektrisches_und_magnetisches_feld_vergleichen_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_04_elektrisches_und_magnetisches_feld_vergleichen.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N8" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st04_elektrisches_und_magnetisches_feld_vergleichen_orga.html","Vorbereitung öffnen")</x:f>
@@ -8975,7 +8345,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/019_elektromagnet.jpg</x:v>
       </x:c>
       <x:c r="M9" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st05_elektromagnet_aufbau_und_wirkungsweise_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_05_elektromagnet_aufbau_und_wirkungsweise.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N9" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st05_elektromagnet_aufbau_und_wirkungsweise_orga.html","Vorbereitung öffnen")</x:f>
@@ -9014,13 +8384,13 @@
         <x:v>PWM-Stufen und Hall-Sensor zur relativen Feldmessung nutzen</x:v>
       </x:c>
       <x:c r="K10" s="60" t="str">
-        <x:v>ph_k9_st06_staerke_eines_elektromagneten_untersuchen</x:v>
+        <x:v>ph_k9_st06_starke_eines_elektromagneten_untersuchen</x:v>
       </x:c>
       <x:c r="L10" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/019_elektromagnet.jpg</x:v>
       </x:c>
       <x:c r="M10" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st06_staerke_eines_elektromagneten_untersuchen_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_06_staerke_eines_elektromagneten_untersuchen.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N10" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st06_starke_eines_elektromagneten_untersuchen_orga.html","Vorbereitung öffnen")</x:f>
@@ -9065,7 +8435,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/017_magnet_feldlinien.jpg</x:v>
       </x:c>
       <x:c r="M11" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st07_kraft_auf_einen_stromdurchflossenen_leiter_im_magnetfeld_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_07_kraft_auf_einen_stromdurchflossenen_leiter_im_magnetfeld.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N11" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st07_kraft_auf_einen_stromdurchflossenen_leiter_im_magnetfeld_orga.html","Vorbereitung öffnen")</x:f>
@@ -9110,7 +8480,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/044_generator_motor.jpg</x:v>
       </x:c>
       <x:c r="M12" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st08_elektromotor_elektrische_energie_erzeugt_bewegung_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_08_elektromotor_elektrische_energie_erzeugt_bewegung.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N12" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st08_elektromotor_elektrische_energie_erzeugt_bewegung_orga.html","Vorbereitung öffnen")</x:f>
@@ -9149,13 +8519,13 @@
         <x:v>Relaismodul mit Taster und Status-LED steuern</x:v>
       </x:c>
       <x:c r="K13" s="60" t="str">
-        <x:v>ph_k9_st09_relais_und_elektromagnetischer_tueroeffner</x:v>
+        <x:v>ph_k9_st09_relais_und_elektromagnetischer_turoffner</x:v>
       </x:c>
       <x:c r="L13" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/044_generator_motor.jpg</x:v>
       </x:c>
       <x:c r="M13" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st09_relais_und_elektromagnetischer_tueroeffner_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_09_relais_und_elektromagnetischer_tueroeffner.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N13" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st09_relais_und_elektromagnetischer_turoffner_orga.html","Vorbereitung öffnen")</x:f>
@@ -9200,7 +8570,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/044_generator_motor.jpg</x:v>
       </x:c>
       <x:c r="M14" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st10_lautsprecher_und_anwendungen_des_elektromagnetismus_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_10_lautsprecher_und_anwendungen_des_elektromagnetismus.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N14" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st10_lautsprecher_und_anwendungen_des_elektromagnetismus_orga.html","Vorbereitung öffnen")</x:f>
@@ -9245,7 +8615,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/023_gleichfoermige_bewegung.jpg</x:v>
       </x:c>
       <x:c r="M15" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st11_bewegung_bezugssystem_weg_und_zeit_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_11_bewegung_bezugssystem_weg_und_zeit.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N15" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st11_bewegung_bezugssystem_weg_und_zeit_orga.html","Vorbereitung öffnen")</x:f>
@@ -9290,7 +8660,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/023_gleichfoermige_bewegung.jpg</x:v>
       </x:c>
       <x:c r="M16" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st12_geschwindigkeit_messen_und_berechnen_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_12_geschwindigkeit_messen_und_berechnen.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N16" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st12_geschwindigkeit_messen_und_berechnen_orga.html","Vorbereitung öffnen")</x:f>
@@ -9329,13 +8699,13 @@
         <x:v>Weg-Zeit-Daten mit HC-SR04 protokollieren</x:v>
       </x:c>
       <x:c r="K17" s="60" t="str">
-        <x:v>ph_k9_st13_geradlinig_gleichfoermige_bewegung_und_s_t_diagramm</x:v>
+        <x:v>ph_k9_st13_geradlinig_gleichformige_bewegung_und_s_t_diagramm</x:v>
       </x:c>
       <x:c r="L17" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/023_gleichfoermige_bewegung.jpg</x:v>
       </x:c>
       <x:c r="M17" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st13_geradlinig_gleichfoermige_bewegung_und_s_t_diagramm_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_13_geradlinig_gleichfoermige_bewegung_und_s_t_diagramm.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N17" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st13_geradlinig_gleichformige_bewegung_und_s_t_diagramm_orga.html","Vorbereitung öffnen")</x:f>
@@ -9374,13 +8744,13 @@
         <x:v>—</x:v>
       </x:c>
       <x:c r="K18" s="60" t="str">
-        <x:v>ph_k9_st14_gleichfoermige_bewegung_gleichungen_und_diagramme_anwenden</x:v>
+        <x:v>ph_k9_st14_gleichformige_bewegung_gleichungen_und_diagramme_anwenden</x:v>
       </x:c>
       <x:c r="L18" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/023_gleichfoermige_bewegung.jpg</x:v>
       </x:c>
       <x:c r="M18" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st14_gleichfoermige_bewegung_gleichungen_und_diagramme_anwenden_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_14_gleichfoermige_bewegung_gleichungen_und_diagramme_anwenden.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N18" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st14_gleichformige_bewegung_gleichungen_und_diagramme_anwenden_orga.html","Vorbereitung öffnen")</x:f>
@@ -9419,13 +8789,13 @@
         <x:v>Beschleunigungswerte mit MPU6050 als Rohdaten erfassen</x:v>
       </x:c>
       <x:c r="K19" s="60" t="str">
-        <x:v>ph_k9_st15_beschleunigung_als_aenderung_der_geschwindigkeit</x:v>
+        <x:v>ph_k9_st15_beschleunigung_als_anderung_der_geschwindigkeit</x:v>
       </x:c>
       <x:c r="L19" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/092_beschleunigung.jpg</x:v>
       </x:c>
       <x:c r="M19" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st15_beschleunigung_als_aenderung_der_geschwindigkeit_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_15_beschleunigung_als_aenderung_der_geschwindigkeit.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N19" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st15_beschleunigung_als_anderung_der_geschwindigkeit_orga.html","Vorbereitung öffnen")</x:f>
@@ -9464,13 +8834,13 @@
         <x:v>Beschleunigungsdaten mit MPU6050 aufzeichnen und mitteln</x:v>
       </x:c>
       <x:c r="K20" s="60" t="str">
-        <x:v>ph_k9_st16_geradlinig_gleichmaessig_beschleunigte_bewegung</x:v>
+        <x:v>ph_k9_st16_geradlinig_gleichmaig_beschleunigte_bewegung</x:v>
       </x:c>
       <x:c r="L20" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/023_gleichfoermige_bewegung.jpg</x:v>
       </x:c>
       <x:c r="M20" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st16_geradlinig_gleichmaessig_beschleunigte_bewegung_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_16_geradlinig_gleichmaessig_beschleunigte_bewegung.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N20" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st16_geradlinig_gleichmaig_beschleunigte_bewegung_orga.html","Vorbereitung öffnen")</x:f>
@@ -9515,7 +8885,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/092_beschleunigung.jpg</x:v>
       </x:c>
       <x:c r="M21" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st17_freier_fall_als_beschleunigte_bewegung_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_17_freier_fall_als_beschleunigte_bewegung.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N21" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st17_freier_fall_als_beschleunigte_bewegung_orga.html","Vorbereitung öffnen")</x:f>
@@ -9560,7 +8930,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/023_gleichfoermige_bewegung.jpg</x:v>
       </x:c>
       <x:c r="M22" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st18_bewegungsformen_bewegungsarten_und_verkehrssicherheit_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_18_bewegungsformen_bewegungsarten_und_verkehrssicherheit.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N22" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st18_bewegungsformen_bewegungsarten_und_verkehrssicherheit_orga.html","Vorbereitung öffnen")</x:f>
@@ -9599,13 +8969,13 @@
         <x:v>Kraft mit Wägezelle und HX711 nach Kalibrierung messen</x:v>
       </x:c>
       <x:c r="K23" s="60" t="str">
-        <x:v>ph_k9_st19_kraft_als_wechselwirkung_und_physikalische_groesse</x:v>
+        <x:v>ph_k9_st19_kraft_als_wechselwirkung_und_physikalische_groe</x:v>
       </x:c>
       <x:c r="L23" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/024_newton_krafte.jpg</x:v>
       </x:c>
       <x:c r="M23" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st19_kraft_als_wechselwirkung_und_physikalische_groesse_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_19_kraft_als_wechselwirkung_und_physikalische_groesse.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N23" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st19_kraft_als_wechselwirkung_und_physikalische_groe_orga.html","Vorbereitung öffnen")</x:f>
@@ -9644,13 +9014,13 @@
         <x:v>—</x:v>
       </x:c>
       <x:c r="K24" s="60" t="str">
-        <x:v>ph_k9_st20_erstes_newtonsches_gesetz_traegheit</x:v>
+        <x:v>ph_k9_st20_erstes_newtonsches_gesetz_tragheit</x:v>
       </x:c>
       <x:c r="L24" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/024_newton_krafte.jpg</x:v>
       </x:c>
       <x:c r="M24" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st20_erstes_newtonsches_gesetz_traegheit_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_20_erstes_newtonsches_gesetz_traegheit.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N24" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st20_erstes_newtonsches_gesetz_tragheit_orga.html","Vorbereitung öffnen")</x:f>
@@ -9695,7 +9065,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/092_beschleunigung.jpg</x:v>
       </x:c>
       <x:c r="M25" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st21_zweites_newtonsches_gesetz_kraft_masse_und_beschleunigung_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_21_zweites_newtonsches_gesetz_kraft_masse_und_beschleunigung.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N25" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st21_zweites_newtonsches_gesetz_kraft_masse_und_beschleunigung_orga.html","Vorbereitung öffnen")</x:f>
@@ -9740,7 +9110,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/024_newton_krafte.jpg</x:v>
       </x:c>
       <x:c r="M26" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st22_drittes_newtonsches_gesetz_actio_und_reactio_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_22_drittes_newtonsches_gesetz_actio_und_reactio.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N26" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st22_drittes_newtonsches_gesetz_actio_und_reactio_orga.html","Vorbereitung öffnen")</x:f>
@@ -9785,7 +9155,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/091_gravitation.jpg</x:v>
       </x:c>
       <x:c r="M27" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st23_gravitation_masse_und_gewichtskraft_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_23_gravitation_masse_und_gewichtskraft.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N27" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st23_gravitation_masse_und_gewichtskraft_orga.html","Vorbereitung öffnen")</x:f>
@@ -9824,293 +9194,17 @@
         <x:v>Wahlstationen mit Ultraschall, Lichtschranke oder Wägezelle</x:v>
       </x:c>
       <x:c r="K28" s="63" t="str">
-        <x:v>ph_k9_st24_projekt_und_lernkontrolle_bewegungen_und_kraefte_im_alltag</x:v>
+        <x:v>ph_k9_st24_projekt_und_lernkontrolle_bewegungen_und_krafte_im_alltag</x:v>
       </x:c>
       <x:c r="L28" s="63" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/023_gleichfoermige_bewegung.jpg</x:v>
       </x:c>
       <x:c r="M28" s="160" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k9_st24_projekt_und_lernkontrolle_bewegungen_und_kraefte_im_alltag_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph9_stunde_24_projekt_und_lernkontrolle_bewegungen_und_kraefte_im_alltag.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N28" s="161" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k9_st24_projekt_und_lernkontrolle_bewegungen_und_krafte_im_alltag_orga.html","Vorbereitung öffnen")</x:f>
       </x:c>
-    </x:row>
-    <x:row r="29">
-      <x:c r="M29" s="51"/>
-    </x:row>
-    <x:row r="30">
-      <x:c r="M30" s="51"/>
-    </x:row>
-    <x:row r="31">
-      <x:c r="M31" s="51"/>
-    </x:row>
-    <x:row r="32">
-      <x:c r="M32" s="51"/>
-    </x:row>
-    <x:row r="33">
-      <x:c r="M33" s="51"/>
-    </x:row>
-    <x:row r="34">
-      <x:c r="M34" s="51"/>
-    </x:row>
-    <x:row r="35">
-      <x:c r="M35" s="51"/>
-    </x:row>
-    <x:row r="36">
-      <x:c r="M36" s="51"/>
-    </x:row>
-    <x:row r="37">
-      <x:c r="M37" s="51"/>
-    </x:row>
-    <x:row r="38">
-      <x:c r="M38" s="51"/>
-    </x:row>
-    <x:row r="39">
-      <x:c r="M39" s="51"/>
-    </x:row>
-    <x:row r="40">
-      <x:c r="M40" s="51"/>
-    </x:row>
-    <x:row r="41">
-      <x:c r="M41" s="51"/>
-    </x:row>
-    <x:row r="42">
-      <x:c r="M42" s="51"/>
-    </x:row>
-    <x:row r="43">
-      <x:c r="M43" s="51"/>
-    </x:row>
-    <x:row r="44">
-      <x:c r="M44" s="51"/>
-    </x:row>
-    <x:row r="45">
-      <x:c r="M45" s="51"/>
-    </x:row>
-    <x:row r="46">
-      <x:c r="M46" s="51"/>
-    </x:row>
-    <x:row r="47">
-      <x:c r="M47" s="51"/>
-    </x:row>
-    <x:row r="48">
-      <x:c r="M48" s="51"/>
-    </x:row>
-    <x:row r="49">
-      <x:c r="M49" s="51"/>
-    </x:row>
-    <x:row r="50">
-      <x:c r="M50" s="51"/>
-    </x:row>
-    <x:row r="51">
-      <x:c r="M51" s="51"/>
-    </x:row>
-    <x:row r="52">
-      <x:c r="M52" s="51"/>
-    </x:row>
-    <x:row r="53">
-      <x:c r="M53" s="51"/>
-    </x:row>
-    <x:row r="54">
-      <x:c r="M54" s="51"/>
-    </x:row>
-    <x:row r="55">
-      <x:c r="M55" s="51"/>
-    </x:row>
-    <x:row r="56">
-      <x:c r="M56" s="51"/>
-    </x:row>
-    <x:row r="57">
-      <x:c r="M57" s="51"/>
-    </x:row>
-    <x:row r="58">
-      <x:c r="M58" s="51"/>
-    </x:row>
-    <x:row r="59">
-      <x:c r="M59" s="51"/>
-    </x:row>
-    <x:row r="60">
-      <x:c r="M60" s="51"/>
-    </x:row>
-    <x:row r="61">
-      <x:c r="M61" s="51"/>
-    </x:row>
-    <x:row r="62">
-      <x:c r="M62" s="51"/>
-    </x:row>
-    <x:row r="63">
-      <x:c r="M63" s="51"/>
-    </x:row>
-    <x:row r="64">
-      <x:c r="M64" s="51"/>
-    </x:row>
-    <x:row r="65">
-      <x:c r="M65" s="51"/>
-    </x:row>
-    <x:row r="66">
-      <x:c r="M66" s="51"/>
-    </x:row>
-    <x:row r="67">
-      <x:c r="M67" s="51"/>
-    </x:row>
-    <x:row r="68">
-      <x:c r="M68" s="51"/>
-    </x:row>
-    <x:row r="69">
-      <x:c r="M69" s="51"/>
-    </x:row>
-    <x:row r="70">
-      <x:c r="M70" s="51"/>
-    </x:row>
-    <x:row r="71">
-      <x:c r="M71" s="51"/>
-    </x:row>
-    <x:row r="72">
-      <x:c r="M72" s="51"/>
-    </x:row>
-    <x:row r="73">
-      <x:c r="M73" s="51"/>
-    </x:row>
-    <x:row r="74">
-      <x:c r="M74" s="51"/>
-    </x:row>
-    <x:row r="75">
-      <x:c r="M75" s="51"/>
-    </x:row>
-    <x:row r="76">
-      <x:c r="M76" s="51"/>
-    </x:row>
-    <x:row r="77">
-      <x:c r="M77" s="51"/>
-    </x:row>
-    <x:row r="78">
-      <x:c r="M78" s="51"/>
-    </x:row>
-    <x:row r="79">
-      <x:c r="M79" s="51"/>
-    </x:row>
-    <x:row r="80">
-      <x:c r="M80" s="51"/>
-    </x:row>
-    <x:row r="81">
-      <x:c r="M81" s="51"/>
-    </x:row>
-    <x:row r="82">
-      <x:c r="M82" s="51"/>
-    </x:row>
-    <x:row r="83">
-      <x:c r="M83" s="51"/>
-    </x:row>
-    <x:row r="84">
-      <x:c r="M84" s="51"/>
-    </x:row>
-    <x:row r="85">
-      <x:c r="M85" s="51"/>
-    </x:row>
-    <x:row r="86">
-      <x:c r="M86" s="51"/>
-    </x:row>
-    <x:row r="87">
-      <x:c r="M87" s="51"/>
-    </x:row>
-    <x:row r="88">
-      <x:c r="M88" s="51"/>
-    </x:row>
-    <x:row r="89">
-      <x:c r="M89" s="51"/>
-    </x:row>
-    <x:row r="90">
-      <x:c r="M90" s="51"/>
-    </x:row>
-    <x:row r="91">
-      <x:c r="M91" s="51"/>
-    </x:row>
-    <x:row r="92">
-      <x:c r="M92" s="51"/>
-    </x:row>
-    <x:row r="93">
-      <x:c r="M93" s="51"/>
-    </x:row>
-    <x:row r="94">
-      <x:c r="M94" s="51"/>
-    </x:row>
-    <x:row r="95">
-      <x:c r="M95" s="51"/>
-    </x:row>
-    <x:row r="96">
-      <x:c r="M96" s="51"/>
-    </x:row>
-    <x:row r="97">
-      <x:c r="M97" s="51"/>
-    </x:row>
-    <x:row r="98">
-      <x:c r="M98" s="51"/>
-    </x:row>
-    <x:row r="99">
-      <x:c r="M99" s="51"/>
-    </x:row>
-    <x:row r="100">
-      <x:c r="M100" s="51"/>
-    </x:row>
-    <x:row r="101">
-      <x:c r="M101" s="51"/>
-    </x:row>
-    <x:row r="102">
-      <x:c r="M102" s="51"/>
-    </x:row>
-    <x:row r="103">
-      <x:c r="M103" s="51"/>
-    </x:row>
-    <x:row r="104">
-      <x:c r="M104" s="51"/>
-    </x:row>
-    <x:row r="105">
-      <x:c r="M105" s="51"/>
-    </x:row>
-    <x:row r="106">
-      <x:c r="M106" s="51"/>
-    </x:row>
-    <x:row r="107">
-      <x:c r="M107" s="51"/>
-    </x:row>
-    <x:row r="108">
-      <x:c r="M108" s="51"/>
-    </x:row>
-    <x:row r="109">
-      <x:c r="M109" s="51"/>
-    </x:row>
-    <x:row r="110">
-      <x:c r="M110" s="51"/>
-    </x:row>
-    <x:row r="111">
-      <x:c r="M111" s="51"/>
-    </x:row>
-    <x:row r="112">
-      <x:c r="M112" s="51"/>
-    </x:row>
-    <x:row r="113">
-      <x:c r="M113" s="51"/>
-    </x:row>
-    <x:row r="114">
-      <x:c r="M114" s="51"/>
-    </x:row>
-    <x:row r="115">
-      <x:c r="M115" s="51"/>
-    </x:row>
-    <x:row r="116">
-      <x:c r="M116" s="51"/>
-    </x:row>
-    <x:row r="117">
-      <x:c r="M117" s="51"/>
-    </x:row>
-    <x:row r="118">
-      <x:c r="M118" s="51"/>
-    </x:row>
-    <x:row r="119">
-      <x:c r="M119" s="51"/>
-    </x:row>
-    <x:row r="120">
-      <x:c r="M120" s="51"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -10119,7 +9213,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdf5d8ef80d69497f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6ce13ec41dae4e61"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10257,13 +9351,13 @@
         <x:v>Magnetfeld mit linearem Hall-Sensor erfassen</x:v>
       </x:c>
       <x:c r="K5" s="57" t="str">
-        <x:v>ph_k10_st01_magnetische_pole_kraefte_und_erdmagnetfeld</x:v>
+        <x:v>ph_k10_st01_magnetische_pole_krafte_und_erdmagnetfeld</x:v>
       </x:c>
       <x:c r="L5" s="57" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/018_kompass_erdmagnetfeld.jpg</x:v>
       </x:c>
       <x:c r="M5" s="156" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st01_magnetische_pole_kraefte_und_erdmagnetfeld_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_01_magnetische_pole_kraefte_und_erdmagnetfeld.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N5" s="157" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st01_magnetische_pole_krafte_und_erdmagnetfeld_orga.html","Vorbereitung öffnen")</x:f>
@@ -10308,7 +9402,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/090_physik_klassenraum.jpg</x:v>
       </x:c>
       <x:c r="M6" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st02_elektrisches_und_magnetisches_feld_vergleichen_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_02_elektrisches_und_magnetisches_feld_vergleichen.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N6" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st02_elektrisches_und_magnetisches_feld_vergleichen_orga.html","Vorbereitung öffnen")</x:f>
@@ -10347,13 +9441,13 @@
         <x:v>zeitgesteuerte Ansteuerung über MOSFET-Modul und Strommessung</x:v>
       </x:c>
       <x:c r="K7" s="60" t="str">
-        <x:v>ph_k10_st03_elektromagnet_windungszahl_stromstaerke_und_eisenkern</x:v>
+        <x:v>ph_k10_st03_elektromagnet_windungszahl_stromstarke_und_eisenkern</x:v>
       </x:c>
       <x:c r="L7" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/019_elektromagnet.jpg</x:v>
       </x:c>
       <x:c r="M7" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st03_elektromagnet_windungszahl_stromstaerke_und_eisenkern_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_03_elektromagnet_windungszahl_stromstaerke_und_eisenkern.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N7" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st03_elektromagnet_windungszahl_stromstarke_und_eisenkern_orga.html","Vorbereitung öffnen")</x:f>
@@ -10398,7 +9492,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/019_elektromagnet.jpg</x:v>
       </x:c>
       <x:c r="M8" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st04_kraft_auf_einen_stromdurchflossenen_leiter_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_04_kraft_auf_einen_stromdurchflossenen_leiter.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N8" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st04_kraft_auf_einen_stromdurchflossenen_leiter_orga.html","Vorbereitung öffnen")</x:f>
@@ -10443,7 +9537,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/044_generator_motor.jpg</x:v>
       </x:c>
       <x:c r="M9" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st05_elektromotor_lautsprecher_und_relais_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_05_elektromotor_lautsprecher_und_relais.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N9" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st05_elektromotor_lautsprecher_und_relais_orga.html","Vorbereitung öffnen")</x:f>
@@ -10488,7 +9582,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/043_induktion.jpg</x:v>
       </x:c>
       <x:c r="M10" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st06_elektromagnetische_induktion_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_06_elektromagnetische_induktion.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N10" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st06_elektromagnetische_induktion_orga.html","Vorbereitung öffnen")</x:f>
@@ -10533,7 +9627,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/044_generator_motor.jpg</x:v>
       </x:c>
       <x:c r="M11" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st07_generator_und_wechselspannung_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_07_generator_und_wechselspannung.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N11" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st07_generator_und_wechselspannung_orga.html","Vorbereitung öffnen")</x:f>
@@ -10578,7 +9672,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/045_transformator.jpg</x:v>
       </x:c>
       <x:c r="M12" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st08_transformator_und_stromverbundnetz_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_08_transformator_und_stromverbundnetz.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N12" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st08_transformator_und_stromverbundnetz_orga.html","Vorbereitung öffnen")</x:f>
@@ -10623,7 +9717,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/023_gleichfoermige_bewegung.jpg</x:v>
       </x:c>
       <x:c r="M13" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st09_bewegung_bezugssystem_weg_zeit_und_geschwindigkeit_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_09_bewegung_bezugssystem_weg_zeit_und_geschwindigkeit.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N13" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st09_bewegung_bezugssystem_weg_zeit_und_geschwindigkeit_orga.html","Vorbereitung öffnen")</x:f>
@@ -10662,13 +9756,13 @@
         <x:v>Ultraschall-Datenlogger</x:v>
       </x:c>
       <x:c r="K14" s="60" t="str">
-        <x:v>ph_k10_st10_geradlinig_gleichfoermige_bewegung_und_diagramme</x:v>
+        <x:v>ph_k10_st10_geradlinig_gleichformige_bewegung_und_diagramme</x:v>
       </x:c>
       <x:c r="L14" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/023_gleichfoermige_bewegung.jpg</x:v>
       </x:c>
       <x:c r="M14" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st10_geradlinig_gleichfoermige_bewegung_und_diagramme_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_10_geradlinig_gleichfoermige_bewegung_und_diagramme.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N14" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st10_geradlinig_gleichformige_bewegung_und_diagramme_orga.html","Vorbereitung öffnen")</x:f>
@@ -10707,13 +9801,13 @@
         <x:v>Ultraschall-Datenlogger</x:v>
       </x:c>
       <x:c r="K15" s="60" t="str">
-        <x:v>ph_k10_st11_geradlinig_gleichmaessig_beschleunigte_bewegung</x:v>
+        <x:v>ph_k10_st11_geradlinig_gleichmaig_beschleunigte_bewegung</x:v>
       </x:c>
       <x:c r="L15" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/023_gleichfoermige_bewegung.jpg</x:v>
       </x:c>
       <x:c r="M15" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st11_geradlinig_gleichmaessig_beschleunigte_bewegung_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_11_geradlinig_gleichmaessig_beschleunigte_bewegung.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N15" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st11_geradlinig_gleichmaig_beschleunigte_bewegung_orga.html","Vorbereitung öffnen")</x:f>
@@ -10758,7 +9852,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/092_beschleunigung.jpg</x:v>
       </x:c>
       <x:c r="M16" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st12_freier_fall_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_12_freier_fall.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N16" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st12_freier_fall_orga.html","Vorbereitung öffnen")</x:f>
@@ -10797,13 +9891,13 @@
         <x:v>nein</x:v>
       </x:c>
       <x:c r="K17" s="60" t="str">
-        <x:v>ph_k10_st13_erstes_newtonsches_gesetz_und_traegheit</x:v>
+        <x:v>ph_k10_st13_erstes_newtonsches_gesetz_und_tragheit</x:v>
       </x:c>
       <x:c r="L17" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/024_newton_krafte.jpg</x:v>
       </x:c>
       <x:c r="M17" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st13_erstes_newtonsches_gesetz_und_traegheit_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_13_erstes_newtonsches_gesetz_und_traegheit.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N17" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st13_erstes_newtonsches_gesetz_und_tragheit_orga.html","Vorbereitung öffnen")</x:f>
@@ -10848,7 +9942,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/024_newton_krafte.jpg</x:v>
       </x:c>
       <x:c r="M18" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st14_zweites_newtonsches_gesetz_f_m_a_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_14_zweites_newtonsches_gesetz_f_m_a.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N18" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st14_zweites_newtonsches_gesetz_f_m_a_orga.html","Vorbereitung öffnen")</x:f>
@@ -10893,7 +9987,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/024_newton_krafte.jpg</x:v>
       </x:c>
       <x:c r="M19" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st15_drittes_newtonsches_gesetz_actio_und_reactio_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_15_drittes_newtonsches_gesetz_actio_und_reactio.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N19" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st15_drittes_newtonsches_gesetz_actio_und_reactio_orga.html","Vorbereitung öffnen")</x:f>
@@ -10938,7 +10032,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/004_sonnensystem.jpg</x:v>
       </x:c>
       <x:c r="M20" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st16_gravitation_gewichtskraft_und_planetenbewegung_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_16_gravitation_gewichtskraft_und_planetenbewegung.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N20" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st16_gravitation_gewichtskraft_und_planetenbewegung_orga.html","Vorbereitung öffnen")</x:f>
@@ -10977,13 +10071,13 @@
         <x:v>Drehzahlmessung mit Hall-Sensor</x:v>
       </x:c>
       <x:c r="K21" s="60" t="str">
-        <x:v>ph_k10_st17_gleichfoermige_kreisbewegung</x:v>
+        <x:v>ph_k10_st17_gleichformige_kreisbewegung</x:v>
       </x:c>
       <x:c r="L21" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/023_gleichfoermige_bewegung.jpg</x:v>
       </x:c>
       <x:c r="M21" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st17_gleichfoermige_kreisbewegung_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_17_gleichfoermige_kreisbewegung.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N21" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st17_gleichformige_kreisbewegung_orga.html","Vorbereitung öffnen")</x:f>
@@ -11022,13 +10116,13 @@
         <x:v>Abstandssensor zeichnet Schwingung auf</x:v>
       </x:c>
       <x:c r="K22" s="60" t="str">
-        <x:v>ph_k10_st18_schwingungen_und_ihre_kenngroessen</x:v>
+        <x:v>ph_k10_st18_schwingungen_und_ihre_kenngroen</x:v>
       </x:c>
       <x:c r="L22" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/094_schwingung_welle.jpg</x:v>
       </x:c>
       <x:c r="M22" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st18_schwingungen_und_ihre_kenngroessen_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_18_schwingungen_und_ihre_kenngroessen.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N22" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st18_schwingungen_und_ihre_kenngroen_orga.html","Vorbereitung öffnen")</x:f>
@@ -11073,7 +10167,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/094_schwingung_welle.jpg</x:v>
       </x:c>
       <x:c r="M23" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st19_schwingungsdauer_des_fadenpendels_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_19_schwingungsdauer_des_fadenpendels.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N23" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st19_schwingungsdauer_des_fadenpendels_orga.html","Vorbereitung öffnen")</x:f>
@@ -11118,7 +10212,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/094_schwingung_welle.jpg</x:v>
       </x:c>
       <x:c r="M24" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st20_wellen_als_ausbreitung_von_schwingungen_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_20_wellen_als_ausbreitung_von_schwingungen.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N24" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st20_wellen_als_ausbreitung_von_schwingungen_orga.html","Vorbereitung öffnen")</x:f>
@@ -11157,13 +10251,13 @@
         <x:v>Piezo-Ausgabe und Mikrofonmodul</x:v>
       </x:c>
       <x:c r="K25" s="60" t="str">
-        <x:v>ph_k10_st21_schall_frequenz_tonhoehe_und_laermschutz</x:v>
+        <x:v>ph_k10_st21_schall_frequenz_tonhohe_und_larmschutz</x:v>
       </x:c>
       <x:c r="L25" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/031_schall_wellen.jpg</x:v>
       </x:c>
       <x:c r="M25" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st21_schall_frequenz_tonhoehe_und_laermschutz_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_21_schall_frequenz_tonhoehe_und_laermschutz.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N25" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st21_schall_frequenz_tonhohe_und_larmschutz_orga.html","Vorbereitung öffnen")</x:f>
@@ -11202,13 +10296,13 @@
         <x:v>Kraftsensor und Wegsensor</x:v>
       </x:c>
       <x:c r="K26" s="60" t="str">
-        <x:v>ph_k10_st22_arbeit_energieformen_und_energie_als_zustandsgroesse</x:v>
+        <x:v>ph_k10_st22_arbeit_energieformen_und_energie_als_zustandsgroe</x:v>
       </x:c>
       <x:c r="L26" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/038_arbeit_leistung.jpg</x:v>
       </x:c>
       <x:c r="M26" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st22_arbeit_energieformen_und_energie_als_zustandsgroesse_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_22_arbeit_energieformen_und_energie_als_zustandsgroesse.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N26" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st22_arbeit_energieformen_und_energie_als_zustandsgroe_orga.html","Vorbereitung öffnen")</x:f>
@@ -11253,7 +10347,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/036_energie_formen.jpg</x:v>
       </x:c>
       <x:c r="M27" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st23_allgemeiner_energieerhaltungssatz_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_23_allgemeiner_energieerhaltungssatz.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N27" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st23_allgemeiner_energieerhaltungssatz_orga.html","Vorbereitung öffnen")</x:f>
@@ -11298,7 +10392,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/064_elektrische_energie.jpg</x:v>
       </x:c>
       <x:c r="M28" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st24_wirkungsgrad_und_versorgung_mit_elektrischer_energie_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_24_wirkungsgrad_und_versorgung_mit_elektrischer_energie.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N28" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st24_wirkungsgrad_und_versorgung_mit_elektrischer_energie_orga.html","Vorbereitung öffnen")</x:f>
@@ -11343,7 +10437,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/042_radioaktivitaet.jpg</x:v>
       </x:c>
       <x:c r="M29" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st25_atomkern_und_nuklidschreibweise_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_25_atomkern_und_nuklidschreibweise.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N29" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st25_atomkern_und_nuklidschreibweise_orga.html","Vorbereitung öffnen")</x:f>
@@ -11388,7 +10482,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/042_radioaktivitaet.jpg</x:v>
       </x:c>
       <x:c r="M30" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st26_und_strahlung_eigenschaften_nachweis_und_abschirmung_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_26_und_strahlung_eigenschaften_nachweis_und_abschirmung.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N30" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st26_und_strahlung_eigenschaften_nachweis_und_abschirmung_orga.html","Vorbereitung öffnen")</x:f>
@@ -11433,7 +10527,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/042_radioaktivitaet.jpg</x:v>
       </x:c>
       <x:c r="M31" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st27_radioaktiver_zerfall_und_halbwertszeit_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_27_radioaktiver_zerfall_und_halbwertszeit.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N31" s="159" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st27_radioaktiver_zerfall_und_halbwertszeit_orga.html","Vorbereitung öffnen")</x:f>
@@ -11478,275 +10572,11 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/054_sonne_aufbau.jpg</x:v>
       </x:c>
       <x:c r="M32" s="160" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/ph_k10_st28_anwendungen_strahlenschutz_kernspaltung_und_kernfusion_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/ph10_stunde_28_anwendungen_strahlenschutz_kernspaltung_und_kernfusion.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N32" s="161" t="e">
         <x:f>HYPERLINK("lehrer/physik/ph_k10_st28_anwendungen_strahlenschutz_kernspaltung_und_kernfusion_orga.html","Vorbereitung öffnen")</x:f>
       </x:c>
-    </x:row>
-    <x:row r="33">
-      <x:c r="M33" s="51"/>
-    </x:row>
-    <x:row r="34">
-      <x:c r="M34" s="51"/>
-    </x:row>
-    <x:row r="35">
-      <x:c r="M35" s="51"/>
-    </x:row>
-    <x:row r="36">
-      <x:c r="M36" s="51"/>
-    </x:row>
-    <x:row r="37">
-      <x:c r="M37" s="51"/>
-    </x:row>
-    <x:row r="38">
-      <x:c r="M38" s="51"/>
-    </x:row>
-    <x:row r="39">
-      <x:c r="M39" s="51"/>
-    </x:row>
-    <x:row r="40">
-      <x:c r="M40" s="51"/>
-    </x:row>
-    <x:row r="41">
-      <x:c r="M41" s="51"/>
-    </x:row>
-    <x:row r="42">
-      <x:c r="M42" s="51"/>
-    </x:row>
-    <x:row r="43">
-      <x:c r="M43" s="51"/>
-    </x:row>
-    <x:row r="44">
-      <x:c r="M44" s="51"/>
-    </x:row>
-    <x:row r="45">
-      <x:c r="M45" s="51"/>
-    </x:row>
-    <x:row r="46">
-      <x:c r="M46" s="51"/>
-    </x:row>
-    <x:row r="47">
-      <x:c r="M47" s="51"/>
-    </x:row>
-    <x:row r="48">
-      <x:c r="M48" s="51"/>
-    </x:row>
-    <x:row r="49">
-      <x:c r="M49" s="51"/>
-    </x:row>
-    <x:row r="50">
-      <x:c r="M50" s="51"/>
-    </x:row>
-    <x:row r="51">
-      <x:c r="M51" s="51"/>
-    </x:row>
-    <x:row r="52">
-      <x:c r="M52" s="51"/>
-    </x:row>
-    <x:row r="53">
-      <x:c r="M53" s="51"/>
-    </x:row>
-    <x:row r="54">
-      <x:c r="M54" s="51"/>
-    </x:row>
-    <x:row r="55">
-      <x:c r="M55" s="51"/>
-    </x:row>
-    <x:row r="56">
-      <x:c r="M56" s="51"/>
-    </x:row>
-    <x:row r="57">
-      <x:c r="M57" s="51"/>
-    </x:row>
-    <x:row r="58">
-      <x:c r="M58" s="51"/>
-    </x:row>
-    <x:row r="59">
-      <x:c r="M59" s="51"/>
-    </x:row>
-    <x:row r="60">
-      <x:c r="M60" s="51"/>
-    </x:row>
-    <x:row r="61">
-      <x:c r="M61" s="51"/>
-    </x:row>
-    <x:row r="62">
-      <x:c r="M62" s="51"/>
-    </x:row>
-    <x:row r="63">
-      <x:c r="M63" s="51"/>
-    </x:row>
-    <x:row r="64">
-      <x:c r="M64" s="51"/>
-    </x:row>
-    <x:row r="65">
-      <x:c r="M65" s="51"/>
-    </x:row>
-    <x:row r="66">
-      <x:c r="M66" s="51"/>
-    </x:row>
-    <x:row r="67">
-      <x:c r="M67" s="51"/>
-    </x:row>
-    <x:row r="68">
-      <x:c r="M68" s="51"/>
-    </x:row>
-    <x:row r="69">
-      <x:c r="M69" s="51"/>
-    </x:row>
-    <x:row r="70">
-      <x:c r="M70" s="51"/>
-    </x:row>
-    <x:row r="71">
-      <x:c r="M71" s="51"/>
-    </x:row>
-    <x:row r="72">
-      <x:c r="M72" s="51"/>
-    </x:row>
-    <x:row r="73">
-      <x:c r="M73" s="51"/>
-    </x:row>
-    <x:row r="74">
-      <x:c r="M74" s="51"/>
-    </x:row>
-    <x:row r="75">
-      <x:c r="M75" s="51"/>
-    </x:row>
-    <x:row r="76">
-      <x:c r="M76" s="51"/>
-    </x:row>
-    <x:row r="77">
-      <x:c r="M77" s="51"/>
-    </x:row>
-    <x:row r="78">
-      <x:c r="M78" s="51"/>
-    </x:row>
-    <x:row r="79">
-      <x:c r="M79" s="51"/>
-    </x:row>
-    <x:row r="80">
-      <x:c r="M80" s="51"/>
-    </x:row>
-    <x:row r="81">
-      <x:c r="M81" s="51"/>
-    </x:row>
-    <x:row r="82">
-      <x:c r="M82" s="51"/>
-    </x:row>
-    <x:row r="83">
-      <x:c r="M83" s="51"/>
-    </x:row>
-    <x:row r="84">
-      <x:c r="M84" s="51"/>
-    </x:row>
-    <x:row r="85">
-      <x:c r="M85" s="51"/>
-    </x:row>
-    <x:row r="86">
-      <x:c r="M86" s="51"/>
-    </x:row>
-    <x:row r="87">
-      <x:c r="M87" s="51"/>
-    </x:row>
-    <x:row r="88">
-      <x:c r="M88" s="51"/>
-    </x:row>
-    <x:row r="89">
-      <x:c r="M89" s="51"/>
-    </x:row>
-    <x:row r="90">
-      <x:c r="M90" s="51"/>
-    </x:row>
-    <x:row r="91">
-      <x:c r="M91" s="51"/>
-    </x:row>
-    <x:row r="92">
-      <x:c r="M92" s="51"/>
-    </x:row>
-    <x:row r="93">
-      <x:c r="M93" s="51"/>
-    </x:row>
-    <x:row r="94">
-      <x:c r="M94" s="51"/>
-    </x:row>
-    <x:row r="95">
-      <x:c r="M95" s="51"/>
-    </x:row>
-    <x:row r="96">
-      <x:c r="M96" s="51"/>
-    </x:row>
-    <x:row r="97">
-      <x:c r="M97" s="51"/>
-    </x:row>
-    <x:row r="98">
-      <x:c r="M98" s="51"/>
-    </x:row>
-    <x:row r="99">
-      <x:c r="M99" s="51"/>
-    </x:row>
-    <x:row r="100">
-      <x:c r="M100" s="51"/>
-    </x:row>
-    <x:row r="101">
-      <x:c r="M101" s="51"/>
-    </x:row>
-    <x:row r="102">
-      <x:c r="M102" s="51"/>
-    </x:row>
-    <x:row r="103">
-      <x:c r="M103" s="51"/>
-    </x:row>
-    <x:row r="104">
-      <x:c r="M104" s="51"/>
-    </x:row>
-    <x:row r="105">
-      <x:c r="M105" s="51"/>
-    </x:row>
-    <x:row r="106">
-      <x:c r="M106" s="51"/>
-    </x:row>
-    <x:row r="107">
-      <x:c r="M107" s="51"/>
-    </x:row>
-    <x:row r="108">
-      <x:c r="M108" s="51"/>
-    </x:row>
-    <x:row r="109">
-      <x:c r="M109" s="51"/>
-    </x:row>
-    <x:row r="110">
-      <x:c r="M110" s="51"/>
-    </x:row>
-    <x:row r="111">
-      <x:c r="M111" s="51"/>
-    </x:row>
-    <x:row r="112">
-      <x:c r="M112" s="51"/>
-    </x:row>
-    <x:row r="113">
-      <x:c r="M113" s="51"/>
-    </x:row>
-    <x:row r="114">
-      <x:c r="M114" s="51"/>
-    </x:row>
-    <x:row r="115">
-      <x:c r="M115" s="51"/>
-    </x:row>
-    <x:row r="116">
-      <x:c r="M116" s="51"/>
-    </x:row>
-    <x:row r="117">
-      <x:c r="M117" s="51"/>
-    </x:row>
-    <x:row r="118">
-      <x:c r="M118" s="51"/>
-    </x:row>
-    <x:row r="119">
-      <x:c r="M119" s="51"/>
-    </x:row>
-    <x:row r="120">
-      <x:c r="M120" s="51"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -11755,7 +10585,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc37991fb22d3441f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4db60e4a693a487b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11899,7 +10729,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/084_elektromagnetisches_spektrum.jpg</x:v>
       </x:c>
       <x:c r="M5" s="156" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/as_k10_st01_astronomie_als_beobachtungswissenschaft_und_elektromagnetisches_spektrum_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/as10_stunde_01_astronomie_als_beobachtungswissenschaft_und_elektromagnetisches_spektrum.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N5" s="157" t="e">
         <x:f>HYPERLINK("lehrer/astronomie/as_k10_st01_astronomie_als_beobachtungswissenschaft_und_elektromagnetisches_spektrum_orga.html","Vorbereitung öffnen")</x:f>
@@ -11944,7 +10774,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/049_teleskop.jpg</x:v>
       </x:c>
       <x:c r="M6" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/as_k10_st02_himmelskugel_horizont_und_orientierung_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/as10_stunde_02_himmelskugel_horizont_und_orientierung.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N6" s="159" t="e">
         <x:f>HYPERLINK("lehrer/astronomie/as_k10_st02_himmelskugel_horizont_und_orientierung_orga.html","Vorbereitung öffnen")</x:f>
@@ -11989,7 +10819,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/049_teleskop.jpg</x:v>
       </x:c>
       <x:c r="M7" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/as_k10_st03_drehbare_sternkarte_und_jahreszeitliche_sternbilder_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/as10_stunde_03_drehbare_sternkarte_und_jahreszeitliche_sternbilder.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N7" s="159" t="e">
         <x:f>HYPERLINK("lehrer/astronomie/as_k10_st03_drehbare_sternkarte_und_jahreszeitliche_sternbilder_orga.html","Vorbereitung öffnen")</x:f>
@@ -12034,7 +10864,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/049_teleskop.jpg</x:v>
       </x:c>
       <x:c r="M8" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/as_k10_st04_polarstern_erdrotation_und_scheinbare_himmelsbewegung_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/as10_stunde_04_polarstern_erdrotation_und_scheinbare_himmelsbewegung.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N8" s="159" t="e">
         <x:f>HYPERLINK("lehrer/astronomie/as_k10_st04_polarstern_erdrotation_und_scheinbare_himmelsbewegung_orga.html","Vorbereitung öffnen")</x:f>
@@ -12079,7 +10909,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/049_teleskop.jpg</x:v>
       </x:c>
       <x:c r="M9" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/as_k10_st05_astronomische_beobachtung_planen_und_dokumentieren_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/as10_stunde_05_astronomische_beobachtung_planen_und_dokumentieren.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N9" s="159" t="e">
         <x:f>HYPERLINK("lehrer/astronomie/as_k10_st05_astronomische_beobachtung_planen_und_dokumentieren_orga.html","Vorbereitung öffnen")</x:f>
@@ -12124,7 +10954,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/090_physik_klassenraum.jpg</x:v>
       </x:c>
       <x:c r="M10" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/as_k10_st06_vom_geozentrischen_zum_heliozentrischen_weltbild_schattenstab_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/as10_stunde_06_vom_geozentrischen_zum_heliozentrischen_weltbild_schattenstab.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N10" s="159" t="e">
         <x:f>HYPERLINK("lehrer/astronomie/as_k10_st06_vom_geozentrischen_zum_heliozentrischen_weltbild_schattenstab_orga.html","Vorbereitung öffnen")</x:f>
@@ -12163,13 +10993,13 @@
         <x:v>nein</x:v>
       </x:c>
       <x:c r="K11" s="60" t="str">
-        <x:v>as_k10_st07_entstehung_raeumlicher_aufbau_und_klassen_von_himmelskoerpern</x:v>
+        <x:v>as_k10_st07_entstehung_raumlicher_aufbau_und_klassen_von_himmelskorpern</x:v>
       </x:c>
       <x:c r="L11" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/004_sonnensystem.jpg</x:v>
       </x:c>
       <x:c r="M11" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/as_k10_st07_entstehung_raeumlicher_aufbau_und_klassen_von_himmelskoerpern_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/as10_stunde_07_entstehung_raeumlicher_aufbau_und_klassen_von_himmelskoerpern.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N11" s="159" t="e">
         <x:f>HYPERLINK("lehrer/astronomie/as_k10_st07_entstehung_raumlicher_aufbau_und_klassen_von_himmelskorpern_orga.html","Vorbereitung öffnen")</x:f>
@@ -12208,13 +11038,13 @@
         <x:v>Ultraschallsensor als Distanzanzeige im Modell</x:v>
       </x:c>
       <x:c r="K12" s="60" t="str">
-        <x:v>as_k10_st08_groessen_und_entfernungen_im_sonnensystem</x:v>
+        <x:v>as_k10_st08_groen_und_entfernungen_im_sonnensystem</x:v>
       </x:c>
       <x:c r="L12" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/054_sonne_aufbau.jpg</x:v>
       </x:c>
       <x:c r="M12" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/as_k10_st08_groessen_und_entfernungen_im_sonnensystem_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/as10_stunde_08_groessen_und_entfernungen_im_sonnensystem.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N12" s="159" t="e">
         <x:f>HYPERLINK("lehrer/astronomie/as_k10_st08_groen_und_entfernungen_im_sonnensystem_orga.html","Vorbereitung öffnen")</x:f>
@@ -12259,7 +11089,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/048_jahreszeiten.jpg</x:v>
       </x:c>
       <x:c r="M13" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/as_k10_st09_erdrotation_erdrevolution_und_jahreszeiten_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/as10_stunde_09_erdrotation_erdrevolution_und_jahreszeiten.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N13" s="159" t="e">
         <x:f>HYPERLINK("lehrer/astronomie/as_k10_st09_erdrotation_erdrevolution_und_jahreszeiten_orga.html","Vorbereitung öffnen")</x:f>
@@ -12304,7 +11134,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/009_mondphasen.jpg</x:v>
       </x:c>
       <x:c r="M14" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/as_k10_st10_mondphasen_und_finsternisse_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/as10_stunde_10_mondphasen_und_finsternisse.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N14" s="159" t="e">
         <x:f>HYPERLINK("lehrer/astronomie/as_k10_st10_mondphasen_und_finsternisse_orga.html","Vorbereitung öffnen")</x:f>
@@ -12349,7 +11179,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/055_keplergesetze.jpg</x:v>
       </x:c>
       <x:c r="M15" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/as_k10_st11_keplersche_gesetze_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/as10_stunde_11_keplersche_gesetze.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N15" s="159" t="e">
         <x:f>HYPERLINK("lehrer/astronomie/as_k10_st11_keplersche_gesetze_orga.html","Vorbereitung öffnen")</x:f>
@@ -12394,7 +11224,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/091_gravitation.jpg</x:v>
       </x:c>
       <x:c r="M16" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/as_k10_st12_gravitation_und_umlaufbahnen_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/as10_stunde_12_gravitation_und_umlaufbahnen.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N16" s="159" t="e">
         <x:f>HYPERLINK("lehrer/astronomie/as_k10_st12_gravitation_und_umlaufbahnen_orga.html","Vorbereitung öffnen")</x:f>
@@ -12439,7 +11269,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/054_sonne_aufbau.jpg</x:v>
       </x:c>
       <x:c r="M17" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/as_k10_st13_aufbau_der_sonne_kernfusion_und_energietransport_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/as10_stunde_13_aufbau_der_sonne_kernfusion_und_energietransport.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N17" s="159" t="e">
         <x:f>HYPERLINK("lehrer/astronomie/as_k10_st13_aufbau_der_sonne_kernfusion_und_energietransport_orga.html","Vorbereitung öffnen")</x:f>
@@ -12478,13 +11308,13 @@
         <x:v>RGB-/Lichtsensor vergleicht Lichtquellen; keine direkte Sonnenmessung</x:v>
       </x:c>
       <x:c r="K18" s="60" t="str">
-        <x:v>as_k10_st14_sonnenstrahlung_spektrum_aktivitaet_und_weltraumwetter</x:v>
+        <x:v>as_k10_st14_sonnenstrahlung_spektrum_aktivitat_und_weltraumwetter</x:v>
       </x:c>
       <x:c r="L18" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/054_sonne_aufbau.jpg</x:v>
       </x:c>
       <x:c r="M18" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/as_k10_st14_sonnenstrahlung_spektrum_aktivitaet_und_weltraumwetter_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/as10_stunde_14_sonnenstrahlung_spektrum_aktivitaet_und_weltraumwetter.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N18" s="159" t="e">
         <x:f>HYPERLINK("lehrer/astronomie/as_k10_st14_sonnenstrahlung_spektrum_aktivitat_und_weltraumwetter_orga.html","Vorbereitung öffnen")</x:f>
@@ -12523,13 +11353,13 @@
         <x:v>zwei Temperatursensoren vergleichen Oberflächen</x:v>
       </x:c>
       <x:c r="K19" s="60" t="str">
-        <x:v>as_k10_st15_planeten_klassifizieren_und_bedingungen_fuer_leben</x:v>
+        <x:v>as_k10_st15_planeten_klassifizieren_und_bedingungen_fur_leben</x:v>
       </x:c>
       <x:c r="L19" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/004_sonnensystem.jpg</x:v>
       </x:c>
       <x:c r="M19" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/as_k10_st15_planeten_klassifizieren_und_bedingungen_fuer_leben_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/as10_stunde_15_planeten_klassifizieren_und_bedingungen_fuer_leben.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N19" s="159" t="e">
         <x:f>HYPERLINK("lehrer/astronomie/as_k10_st15_planeten_klassifizieren_und_bedingungen_fur_leben_orga.html","Vorbereitung öffnen")</x:f>
@@ -12568,13 +11398,13 @@
         <x:v>Beschleunigungssensor misst Aufprallstärke im Modell</x:v>
       </x:c>
       <x:c r="K20" s="60" t="str">
-        <x:v>as_k10_st16_mondoberflaeche_gezeiten_und_raumfahrt</x:v>
+        <x:v>as_k10_st16_mondoberflache_gezeiten_und_raumfahrt</x:v>
       </x:c>
       <x:c r="L20" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/009_mondphasen.jpg</x:v>
       </x:c>
       <x:c r="M20" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/as_k10_st16_mondoberflaeche_gezeiten_und_raumfahrt_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/as10_stunde_16_mondoberflaeche_gezeiten_und_raumfahrt.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N20" s="159" t="e">
         <x:f>HYPERLINK("lehrer/astronomie/as_k10_st16_mondoberflache_gezeiten_und_raumfahrt_orga.html","Vorbereitung öffnen")</x:f>
@@ -12619,7 +11449,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/077_lichtjahr.jpg</x:v>
       </x:c>
       <x:c r="M21" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/as_k10_st17_lichtjahr_blick_in_die_vergangenheit_und_scheinbare_helligkeit_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/as10_stunde_17_lichtjahr_blick_in_die_vergangenheit_und_scheinbare_helligkeit.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N21" s="159" t="e">
         <x:f>HYPERLINK("lehrer/astronomie/as_k10_st17_lichtjahr_blick_in_die_vergangenheit_und_scheinbare_helligkeit_orga.html","Vorbereitung öffnen")</x:f>
@@ -12664,7 +11494,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/049_teleskop.jpg</x:v>
       </x:c>
       <x:c r="M22" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/as_k10_st18_astronomische_entfernungsbestimmung_durch_parallaxe_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/as10_stunde_18_astronomische_entfernungsbestimmung_durch_parallaxe.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N22" s="159" t="e">
         <x:f>HYPERLINK("lehrer/astronomie/as_k10_st18_astronomische_entfernungsbestimmung_durch_parallaxe_orga.html","Vorbereitung öffnen")</x:f>
@@ -12709,7 +11539,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/046_sterne_spektrum.jpg</x:v>
       </x:c>
       <x:c r="M23" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/as_k10_st19_sternspektren_farben_und_temperaturen_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/as10_stunde_19_sternspektren_farben_und_temperaturen.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N23" s="159" t="e">
         <x:f>HYPERLINK("lehrer/astronomie/as_k10_st19_sternspektren_farben_und_temperaturen_orga.html","Vorbereitung öffnen")</x:f>
@@ -12754,7 +11584,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/046_sterne_spektrum.jpg</x:v>
       </x:c>
       <x:c r="M24" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/as_k10_st20_hertzsprung_russell_diagramm_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/as10_stunde_20_hertzsprung_russell_diagramm.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N24" s="159" t="e">
         <x:f>HYPERLINK("lehrer/astronomie/as_k10_st20_hertzsprung_russell_diagramm_orga.html","Vorbereitung öffnen")</x:f>
@@ -12793,13 +11623,13 @@
         <x:v>nein</x:v>
       </x:c>
       <x:c r="K25" s="60" t="str">
-        <x:v>as_k10_st21_entstehung_und_entwicklung_sonnenaehnlicher_sterne</x:v>
+        <x:v>as_k10_st21_entstehung_und_entwicklung_sonnenahnlicher_sterne</x:v>
       </x:c>
       <x:c r="L25" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/078_sternentwicklung.jpg</x:v>
       </x:c>
       <x:c r="M25" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/as_k10_st21_entstehung_und_entwicklung_sonnenaehnlicher_sterne_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/as10_stunde_21_entstehung_und_entwicklung_sonnenaehnlicher_sterne.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N25" s="159" t="e">
         <x:f>HYPERLINK("lehrer/astronomie/as_k10_st21_entstehung_und_entwicklung_sonnenahnlicher_sterne_orga.html","Vorbereitung öffnen")</x:f>
@@ -12844,7 +11674,7 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/078_sternentwicklung.jpg</x:v>
       </x:c>
       <x:c r="M26" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/as_k10_st22_massereiche_sterne_und_endstadien_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/as10_stunde_22_massereiche_sterne_und_endstadien.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N26" s="159" t="e">
         <x:f>HYPERLINK("lehrer/astronomie/as_k10_st22_massereiche_sterne_und_endstadien_orga.html","Vorbereitung öffnen")</x:f>
@@ -12883,13 +11713,13 @@
         <x:v>Schrittmotor dreht Spiralgalaxienmodell</x:v>
       </x:c>
       <x:c r="K27" s="60" t="str">
-        <x:v>as_k10_st23_milchstrasse_galaxien_und_grossraeumige_strukturen</x:v>
+        <x:v>as_k10_st23_milchstrae_galaxien_und_groraumige_strukturen</x:v>
       </x:c>
       <x:c r="L27" s="60" t="str">
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/047_galaxien.jpg</x:v>
       </x:c>
       <x:c r="M27" s="158" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/as_k10_st23_milchstrasse_galaxien_und_grossraeumige_strukturen_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/as10_stunde_23_milchstrasse_galaxien_und_grossraeumige_strukturen.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N27" s="159" t="e">
         <x:f>HYPERLINK("lehrer/astronomie/as_k10_st23_milchstrae_galaxien_und_groraumige_strukturen_orga.html","Vorbereitung öffnen")</x:f>
@@ -12934,287 +11764,11 @@
         <x:v>https://raw.githubusercontent.com/burgnetz-wq/froebel/main/bilder/physik/087_universum_entstehung.jpg</x:v>
       </x:c>
       <x:c r="M28" s="160" t="e">
-        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/schueler/as_k10_st24_urknall_expansion_rotverschiebung_und_kosmische_hintergrundstrahlung_app.html","Schüler-Modul öffnen")</x:f>
+        <x:f>HYPERLINK("https://burgnetz-wq.github.io/froebel/physik/html/as10_stunde_24_urknall_expansion_rotverschiebung_und_kosmische_hintergrundstrahlung.html","Schüler-Modul öffnen")</x:f>
       </x:c>
       <x:c r="N28" s="161" t="e">
         <x:f>HYPERLINK("lehrer/astronomie/as_k10_st24_urknall_expansion_rotverschiebung_und_kosmische_hintergrundstrahlung_orga.html","Vorbereitung öffnen")</x:f>
       </x:c>
-    </x:row>
-    <x:row r="29">
-      <x:c r="M29" s="51"/>
-    </x:row>
-    <x:row r="30">
-      <x:c r="M30" s="51"/>
-    </x:row>
-    <x:row r="31">
-      <x:c r="M31" s="51"/>
-    </x:row>
-    <x:row r="32">
-      <x:c r="M32" s="51"/>
-    </x:row>
-    <x:row r="33">
-      <x:c r="M33" s="51"/>
-    </x:row>
-    <x:row r="34">
-      <x:c r="M34" s="51"/>
-    </x:row>
-    <x:row r="35">
-      <x:c r="M35" s="51"/>
-    </x:row>
-    <x:row r="36">
-      <x:c r="M36" s="51"/>
-    </x:row>
-    <x:row r="37">
-      <x:c r="M37" s="51"/>
-    </x:row>
-    <x:row r="38">
-      <x:c r="M38" s="51"/>
-    </x:row>
-    <x:row r="39">
-      <x:c r="M39" s="51"/>
-    </x:row>
-    <x:row r="40">
-      <x:c r="M40" s="51"/>
-    </x:row>
-    <x:row r="41">
-      <x:c r="M41" s="51"/>
-    </x:row>
-    <x:row r="42">
-      <x:c r="M42" s="51"/>
-    </x:row>
-    <x:row r="43">
-      <x:c r="M43" s="51"/>
-    </x:row>
-    <x:row r="44">
-      <x:c r="M44" s="51"/>
-    </x:row>
-    <x:row r="45">
-      <x:c r="M45" s="51"/>
-    </x:row>
-    <x:row r="46">
-      <x:c r="M46" s="51"/>
-    </x:row>
-    <x:row r="47">
-      <x:c r="M47" s="51"/>
-    </x:row>
-    <x:row r="48">
-      <x:c r="M48" s="51"/>
-    </x:row>
-    <x:row r="49">
-      <x:c r="M49" s="51"/>
-    </x:row>
-    <x:row r="50">
-      <x:c r="M50" s="51"/>
-    </x:row>
-    <x:row r="51">
-      <x:c r="M51" s="51"/>
-    </x:row>
-    <x:row r="52">
-      <x:c r="M52" s="51"/>
-    </x:row>
-    <x:row r="53">
-      <x:c r="M53" s="51"/>
-    </x:row>
-    <x:row r="54">
-      <x:c r="M54" s="51"/>
-    </x:row>
-    <x:row r="55">
-      <x:c r="M55" s="51"/>
-    </x:row>
-    <x:row r="56">
-      <x:c r="M56" s="51"/>
-    </x:row>
-    <x:row r="57">
-      <x:c r="M57" s="51"/>
-    </x:row>
-    <x:row r="58">
-      <x:c r="M58" s="51"/>
-    </x:row>
-    <x:row r="59">
-      <x:c r="M59" s="51"/>
-    </x:row>
-    <x:row r="60">
-      <x:c r="M60" s="51"/>
-    </x:row>
-    <x:row r="61">
-      <x:c r="M61" s="51"/>
-    </x:row>
-    <x:row r="62">
-      <x:c r="M62" s="51"/>
-    </x:row>
-    <x:row r="63">
-      <x:c r="M63" s="51"/>
-    </x:row>
-    <x:row r="64">
-      <x:c r="M64" s="51"/>
-    </x:row>
-    <x:row r="65">
-      <x:c r="M65" s="51"/>
-    </x:row>
-    <x:row r="66">
-      <x:c r="M66" s="51"/>
-    </x:row>
-    <x:row r="67">
-      <x:c r="M67" s="51"/>
-    </x:row>
-    <x:row r="68">
-      <x:c r="M68" s="51"/>
-    </x:row>
-    <x:row r="69">
-      <x:c r="M69" s="51"/>
-    </x:row>
-    <x:row r="70">
-      <x:c r="M70" s="51"/>
-    </x:row>
-    <x:row r="71">
-      <x:c r="M71" s="51"/>
-    </x:row>
-    <x:row r="72">
-      <x:c r="M72" s="51"/>
-    </x:row>
-    <x:row r="73">
-      <x:c r="M73" s="51"/>
-    </x:row>
-    <x:row r="74">
-      <x:c r="M74" s="51"/>
-    </x:row>
-    <x:row r="75">
-      <x:c r="M75" s="51"/>
-    </x:row>
-    <x:row r="76">
-      <x:c r="M76" s="51"/>
-    </x:row>
-    <x:row r="77">
-      <x:c r="M77" s="51"/>
-    </x:row>
-    <x:row r="78">
-      <x:c r="M78" s="51"/>
-    </x:row>
-    <x:row r="79">
-      <x:c r="M79" s="51"/>
-    </x:row>
-    <x:row r="80">
-      <x:c r="M80" s="51"/>
-    </x:row>
-    <x:row r="81">
-      <x:c r="M81" s="51"/>
-    </x:row>
-    <x:row r="82">
-      <x:c r="M82" s="51"/>
-    </x:row>
-    <x:row r="83">
-      <x:c r="M83" s="51"/>
-    </x:row>
-    <x:row r="84">
-      <x:c r="M84" s="51"/>
-    </x:row>
-    <x:row r="85">
-      <x:c r="M85" s="51"/>
-    </x:row>
-    <x:row r="86">
-      <x:c r="M86" s="51"/>
-    </x:row>
-    <x:row r="87">
-      <x:c r="M87" s="51"/>
-    </x:row>
-    <x:row r="88">
-      <x:c r="M88" s="51"/>
-    </x:row>
-    <x:row r="89">
-      <x:c r="M89" s="51"/>
-    </x:row>
-    <x:row r="90">
-      <x:c r="M90" s="51"/>
-    </x:row>
-    <x:row r="91">
-      <x:c r="M91" s="51"/>
-    </x:row>
-    <x:row r="92">
-      <x:c r="M92" s="51"/>
-    </x:row>
-    <x:row r="93">
-      <x:c r="M93" s="51"/>
-    </x:row>
-    <x:row r="94">
-      <x:c r="M94" s="51"/>
-    </x:row>
-    <x:row r="95">
-      <x:c r="M95" s="51"/>
-    </x:row>
-    <x:row r="96">
-      <x:c r="M96" s="51"/>
-    </x:row>
-    <x:row r="97">
-      <x:c r="M97" s="51"/>
-    </x:row>
-    <x:row r="98">
-      <x:c r="M98" s="51"/>
-    </x:row>
-    <x:row r="99">
-      <x:c r="M99" s="51"/>
-    </x:row>
-    <x:row r="100">
-      <x:c r="M100" s="51"/>
-    </x:row>
-    <x:row r="101">
-      <x:c r="M101" s="51"/>
-    </x:row>
-    <x:row r="102">
-      <x:c r="M102" s="51"/>
-    </x:row>
-    <x:row r="103">
-      <x:c r="M103" s="51"/>
-    </x:row>
-    <x:row r="104">
-      <x:c r="M104" s="51"/>
-    </x:row>
-    <x:row r="105">
-      <x:c r="M105" s="51"/>
-    </x:row>
-    <x:row r="106">
-      <x:c r="M106" s="51"/>
-    </x:row>
-    <x:row r="107">
-      <x:c r="M107" s="51"/>
-    </x:row>
-    <x:row r="108">
-      <x:c r="M108" s="51"/>
-    </x:row>
-    <x:row r="109">
-      <x:c r="M109" s="51"/>
-    </x:row>
-    <x:row r="110">
-      <x:c r="M110" s="51"/>
-    </x:row>
-    <x:row r="111">
-      <x:c r="M111" s="51"/>
-    </x:row>
-    <x:row r="112">
-      <x:c r="M112" s="51"/>
-    </x:row>
-    <x:row r="113">
-      <x:c r="M113" s="51"/>
-    </x:row>
-    <x:row r="114">
-      <x:c r="M114" s="51"/>
-    </x:row>
-    <x:row r="115">
-      <x:c r="M115" s="51"/>
-    </x:row>
-    <x:row r="116">
-      <x:c r="M116" s="51"/>
-    </x:row>
-    <x:row r="117">
-      <x:c r="M117" s="51"/>
-    </x:row>
-    <x:row r="118">
-      <x:c r="M118" s="51"/>
-    </x:row>
-    <x:row r="119">
-      <x:c r="M119" s="51"/>
-    </x:row>
-    <x:row r="120">
-      <x:c r="M120" s="51"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -13223,7 +11777,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R72281e62d3ee4315"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd35913e5d3dc4c12"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13336,7 +11890,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R622362d2c9f24cce"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd5c0a94cfd5641b6"/>
   </x:tableParts>
 </x:worksheet>
 </file>